--- a/Översikt LESSEBO.xlsx
+++ b/Översikt LESSEBO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE277"/>
+  <dimension ref="A1:AE278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45349</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>46035</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45954</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45954</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45954</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45267</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>46176</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45072</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45954</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52539-2025</t>
+          <t>A 1488-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1713,14 +1713,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45954</v>
+        <v>45670</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1732,19 +1732,14 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1774,147 +1769,152 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 1488-2025 artfynd.xlsx", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 1488-2025 karta.png", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 1488-2025 georefererad karta.tif", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 1488-2025 FSC-klagomål.docx", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 1488-2025 FSC-klagomål mail.docx", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 1488-2025 tillsynsbegäran.docx", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 1488-2025 tillsynsbegäran mail.docx", "A 1488-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 52539-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52539-2025 artfynd.xlsx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52539-2025 karta.png", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52539-2025 georefererad karta.tif", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52539-2025 FSC-klagomål.docx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52539-2025 FSC-klagomål mail.docx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52539-2025 tillsynsbegäran.docx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52539-2025 tillsynsbegäran mail.docx", "A 52539-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 1488-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45670</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Korallrot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 1488-2025 artfynd.xlsx", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 1488-2025 karta.png", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 1488-2025 georefererad karta.tif", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 1488-2025 FSC-klagomål.docx", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 1488-2025 FSC-klagomål mail.docx", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 1488-2025 tillsynsbegäran.docx", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 1488-2025 tillsynsbegäran mail.docx", "A 1488-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45625</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44510</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44518</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44865</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 3741-2022</t>
+          <t>A 45956-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44586</v>
+        <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2819,13 +2819,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2868,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24680-2022</t>
+          <t>A 3741-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2882,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44727</v>
+        <v>44586</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2897,8 +2892,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 45956-2022</t>
+          <t>A 24680-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44846</v>
+        <v>44727</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>44510</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59408-2021</t>
+          <t>A 45095-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44491</v>
+        <v>44842</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3189,8 +3189,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3233,7 +3238,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45095-2022</t>
+          <t>A 59408-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3247,10 +3252,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44842</v>
+        <v>44491</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3262,13 +3267,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>44529</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44693</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44508</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44522</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44743</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>44460</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3876-2024</t>
+          <t>A 33240-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45322</v>
+        <v>45518</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>7.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27713-2022</t>
+          <t>A 56456-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44743</v>
+        <v>45625</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11843-2024</t>
+          <t>A 56459-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45376</v>
+        <v>45625</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3924,13 +3924,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3968,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27080-2022</t>
+          <t>A 27713-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3982,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44741</v>
+        <v>44743</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4003,7 +3998,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4041,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 51189-2023</t>
+          <t>A 68507-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45219</v>
+        <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4076,7 +4071,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59173-2023</t>
+          <t>A 1367-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45253</v>
+        <v>44936</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4144,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24171-2024</t>
+          <t>A 24478-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45456</v>
+        <v>45459</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4260,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 24478-2024</t>
+          <t>A 30966-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4274,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45459</v>
+        <v>45113</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4290,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4333,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 64635-2023</t>
+          <t>A 59320-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4347,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45281</v>
+        <v>45637</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4367,8 +4362,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57519-2022</t>
+          <t>A 15203-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4421,14 +4421,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44896</v>
+        <v>45017</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4440,8 +4440,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>6.6</v>
+        <v>0.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4489,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20541-2024</t>
+          <t>A 15204-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4494,14 +4499,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45436</v>
+        <v>45017</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4513,8 +4518,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4567,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18968-2024</t>
+          <t>A 8655-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4581,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45427</v>
+        <v>45710</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4597,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4640,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 56529-2022</t>
+          <t>A 61641-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4654,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44893</v>
+        <v>46002</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4659,8 +4669,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>9</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4718,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38227-2023</t>
+          <t>A 43453-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4732,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45161</v>
+        <v>45568</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4748,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4791,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3714-2022</t>
+          <t>A 10414-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4805,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44586</v>
+        <v>45720</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4805,13 +4820,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4854,7 +4864,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33240-2024</t>
+          <t>A 53487-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4868,10 +4878,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45518</v>
+        <v>45611</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4884,7 +4894,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>7.4</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4927,7 +4937,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60358-2022</t>
+          <t>A 8173-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4937,14 +4947,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44910</v>
+        <v>45708</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4957,7 +4967,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5000,7 +5010,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39389-2024</t>
+          <t>A 62728-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5014,10 +5024,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45551</v>
+        <v>46008</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5029,8 +5039,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5073,7 +5088,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20478-2025</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5083,14 +5098,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45775</v>
+        <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5102,13 +5117,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5151,7 +5161,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20851-2025</t>
+          <t>A 859-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5161,14 +5171,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45777</v>
+        <v>45665</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5186,7 +5196,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5229,7 +5239,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61575-2022</t>
+          <t>A 10047-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5243,10 +5253,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44916</v>
+        <v>45364</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5260,11 +5270,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5307,7 +5317,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61588-2022</t>
+          <t>A 45838-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5321,10 +5331,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44916</v>
+        <v>44846</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5336,13 +5346,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5385,7 +5390,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29659-2025</t>
+          <t>A 39884-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5395,14 +5400,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45825</v>
+        <v>45891</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5415,7 +5420,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5458,7 +5463,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20854-2025</t>
+          <t>A 39549-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5472,10 +5477,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45777</v>
+        <v>45890</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5487,13 +5492,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5536,7 +5536,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 43453-2024</t>
+          <t>A 39750-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45568</v>
+        <v>45891</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5609,7 +5609,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20853-2025</t>
+          <t>A 1022-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45777</v>
+        <v>46030</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5638,13 +5638,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5687,7 +5682,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8438-2026</t>
+          <t>A 1016-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5701,10 +5696,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46065</v>
+        <v>46030</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5716,13 +5711,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5765,7 +5755,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47396-2024</t>
+          <t>A 15180-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5779,10 +5769,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45587</v>
+        <v>45016</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5795,7 +5785,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5838,7 +5828,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7957-2023</t>
+          <t>A 20478-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5852,10 +5842,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44973</v>
+        <v>45775</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5867,8 +5857,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5911,7 +5906,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30527-2025</t>
+          <t>A 35904-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5925,10 +5920,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45831</v>
+        <v>45862</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5940,8 +5935,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5984,7 +5984,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39549-2025</t>
+          <t>A 29659-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5994,14 +5994,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45890</v>
+        <v>45825</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6057,7 +6057,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32712-2025</t>
+          <t>A 20851-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6071,10 +6071,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45839</v>
+        <v>45777</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47386-2024</t>
+          <t>A 20854-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45587</v>
+        <v>45777</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6164,8 +6164,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6208,7 +6213,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39750-2025</t>
+          <t>A 20853-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6222,10 +6227,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45891</v>
+        <v>45777</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6237,8 +6242,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6281,7 +6291,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 39884-2025</t>
+          <t>A 4236-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6295,10 +6305,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45891</v>
+        <v>46044</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6311,7 +6321,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6354,7 +6364,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37399-2024</t>
+          <t>A 4229-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6368,10 +6378,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45540</v>
+        <v>46044</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6384,7 +6394,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6427,7 +6437,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 35904-2025</t>
+          <t>A 30527-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6441,10 +6451,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45862</v>
+        <v>45831</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6456,13 +6466,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6505,7 +6510,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 51175-2023</t>
+          <t>A 43809-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6519,10 +6524,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45219</v>
+        <v>45912</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6535,7 +6540,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6578,7 +6583,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 10286-2026</t>
+          <t>A 32712-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6592,10 +6597,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46076</v>
+        <v>45839</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6607,8 +6612,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6651,7 +6661,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35909-2025</t>
+          <t>A 44904-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6665,10 +6675,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45862</v>
+        <v>45918</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6680,13 +6690,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6729,7 +6734,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35899-2025</t>
+          <t>A 44899-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6743,10 +6748,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45862</v>
+        <v>45918</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6758,13 +6763,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43809-2025</t>
+          <t>A 7957-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45912</v>
+        <v>44973</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44904-2025</t>
+          <t>A 17836-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45918</v>
+        <v>45037</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6953,7 +6953,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14584-2023</t>
+          <t>A 8438-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45013</v>
+        <v>46065</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6982,8 +6982,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7026,7 +7031,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44899-2025</t>
+          <t>A 30914-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7040,10 +7045,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45918</v>
+        <v>44767</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7056,7 +7061,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7099,7 +7104,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10185-2026</t>
+          <t>A 35909-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7113,10 +7118,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46076</v>
+        <v>45862</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7128,8 +7133,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7172,7 +7182,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29767-2023</t>
+          <t>A 35899-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7186,10 +7196,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45107</v>
+        <v>45862</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7201,8 +7211,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7245,7 +7260,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 19501-2022</t>
+          <t>A 48429-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7259,10 +7274,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44693</v>
+        <v>45934</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7275,7 +7290,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7318,7 +7333,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10189-2026</t>
+          <t>A 48433-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7332,10 +7347,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46076</v>
+        <v>45934</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7348,7 +7363,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7391,7 +7406,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10047-2024</t>
+          <t>A 19501-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7405,10 +7420,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45364</v>
+        <v>44693</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7420,13 +7435,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7469,7 +7479,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51191-2023</t>
+          <t>A 17729-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7483,10 +7493,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45219</v>
+        <v>45758</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7498,8 +7508,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7542,7 +7557,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 52525-2023</t>
+          <t>A 49298-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7556,10 +7571,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45225</v>
+        <v>45938</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7572,7 +7587,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7615,7 +7630,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 10189-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7625,14 +7640,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45708</v>
+        <v>46076</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7645,7 +7660,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7688,7 +7703,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17517-2023</t>
+          <t>A 20443-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7702,10 +7717,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45036</v>
+        <v>45775</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7717,8 +7732,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7761,7 +7781,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 1367-2023</t>
+          <t>A 10286-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7775,10 +7795,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44936</v>
+        <v>46076</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7791,7 +7811,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7834,7 +7854,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48429-2025</t>
+          <t>A 10185-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7848,10 +7868,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45934</v>
+        <v>46076</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7864,7 +7884,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7907,7 +7927,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 48433-2025</t>
+          <t>A 50154-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7921,10 +7941,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45934</v>
+        <v>44865</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7937,7 +7957,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7980,7 +8000,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17729-2025</t>
+          <t>A 29767-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7994,10 +8014,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45758</v>
+        <v>45107</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8009,13 +8029,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8058,7 +8073,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 20443-2025</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8068,14 +8083,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45775</v>
+        <v>45708</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8087,13 +8102,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8136,7 +8146,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 49298-2025</t>
+          <t>A 41905-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8150,10 +8160,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45938</v>
+        <v>44830</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8165,8 +8175,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8209,7 +8224,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 4107-2025</t>
+          <t>A 3955-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8223,10 +8238,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45684</v>
+        <v>44587</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8282,7 +8297,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13347-2026</t>
+          <t>A 60358-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8296,10 +8311,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46094</v>
+        <v>44910</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8311,13 +8326,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8377,7 +8387,7 @@
         <v>45952</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8433,7 +8443,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 52537-2025</t>
+          <t>A 17517-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8447,10 +8457,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45954</v>
+        <v>45036</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8462,13 +8472,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8511,7 +8516,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 52531-2025</t>
+          <t>A 20541-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8525,10 +8530,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45954</v>
+        <v>45436</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8540,13 +8545,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8589,7 +8589,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 52532-2025</t>
+          <t>A 13347-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8603,10 +8603,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45954</v>
+        <v>46094</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8620,11 +8620,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8667,7 +8667,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 52546-2025</t>
+          <t>A 64635-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8681,10 +8681,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45954</v>
+        <v>45281</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8696,13 +8696,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>5.4</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8745,7 +8740,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 52534-2025</t>
+          <t>A 14584-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8759,10 +8754,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45954</v>
+        <v>45013</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8774,13 +8769,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8823,7 +8813,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 53122-2025</t>
+          <t>A 73140-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8837,10 +8827,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45958</v>
+        <v>44550</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8853,7 +8843,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8896,7 +8886,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 63927-2021</t>
+          <t>A 52537-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8910,10 +8900,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44509</v>
+        <v>45954</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8931,7 +8921,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8974,7 +8964,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 49295-2025</t>
+          <t>A 52531-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8988,10 +8978,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45938</v>
+        <v>45954</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9003,8 +8993,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>7.4</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9047,7 +9042,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 8655-2025</t>
+          <t>A 52532-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9061,10 +9056,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45710</v>
+        <v>45954</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9076,8 +9071,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9120,7 +9120,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 41900-2022</t>
+          <t>A 52546-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9134,10 +9134,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44830</v>
+        <v>45954</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9198,7 +9198,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 22432-2023</t>
+          <t>A 52534-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9208,14 +9208,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45070</v>
+        <v>45954</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9229,11 +9229,11 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17552-2023</t>
+          <t>A 53122-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9290,10 +9290,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45036</v>
+        <v>45958</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9349,7 +9349,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 13751-2025</t>
+          <t>A 30405-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45737</v>
+        <v>45111</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9422,7 +9422,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 18464-2026</t>
+          <t>A 3239-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46127</v>
+        <v>45679</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9453,11 +9453,11 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>14.2</v>
+        <v>2.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9500,7 +9500,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 18466-2026</t>
+          <t>A 52525-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46127</v>
+        <v>45225</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9529,13 +9529,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>7.9</v>
+        <v>2.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9595,7 +9590,7 @@
         <v>46127</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9651,7 +9646,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 30405-2023</t>
+          <t>A 51191-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9665,10 +9660,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45111</v>
+        <v>45219</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9681,7 +9676,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9724,7 +9719,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 50892-2022</t>
+          <t>A 49295-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9738,10 +9733,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44867</v>
+        <v>45938</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9754,7 +9749,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9797,7 +9792,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 21917-2025</t>
+          <t>A 18464-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9811,10 +9806,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45784</v>
+        <v>46127</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9826,8 +9821,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>14.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9870,7 +9870,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20855-2025</t>
+          <t>A 18466-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9884,10 +9884,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45777</v>
+        <v>46127</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9948,7 +9948,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 45838-2022</t>
+          <t>A 56467-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9962,10 +9962,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44846</v>
+        <v>45625</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10021,7 +10021,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61638-2025</t>
+          <t>A 20056-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10035,10 +10035,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46002</v>
+        <v>45772</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10094,7 +10094,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 61641-2025</t>
+          <t>A 36895-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10108,10 +10108,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46002</v>
+        <v>45874</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10123,13 +10123,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10172,7 +10167,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 20824-2023</t>
+          <t>A 38303-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10186,10 +10181,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45058</v>
+        <v>45883</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10202,7 +10197,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10245,7 +10240,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 62728-2025</t>
+          <t>A 3876-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10259,10 +10254,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46008</v>
+        <v>45322</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10274,13 +10269,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10323,7 +10313,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 30600-2024</t>
+          <t>A 1490-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10333,14 +10323,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45493</v>
+        <v>45670</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10352,8 +10342,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10396,7 +10391,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 1894-2025</t>
+          <t>A 56471-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10410,10 +10405,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45671</v>
+        <v>45625</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10426,7 +10421,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10469,7 +10464,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15864-2022</t>
+          <t>A 21917-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10483,10 +10478,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44664</v>
+        <v>45784</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10499,7 +10494,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10542,7 +10537,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 47693-2025</t>
+          <t>A 54541-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10552,14 +10547,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45931</v>
+        <v>45233</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10571,8 +10566,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10615,7 +10615,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 20056-2025</t>
+          <t>A 51189-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10629,10 +10629,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45772</v>
+        <v>45219</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10688,7 +10688,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 642-2024</t>
+          <t>A 8690-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10698,14 +10698,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45299</v>
+        <v>44978</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10717,13 +10717,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10766,7 +10761,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 1022-2026</t>
+          <t>A 1894-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10780,10 +10775,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46030</v>
+        <v>45671</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10796,7 +10791,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10839,7 +10834,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 1016-2026</t>
+          <t>A 20855-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10853,10 +10848,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46030</v>
+        <v>45777</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10868,8 +10863,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10912,7 +10912,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 47402-2024</t>
+          <t>A 57519-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10926,10 +10926,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45587</v>
+        <v>44896</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10985,7 +10985,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 36895-2025</t>
+          <t>A 56475-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10999,10 +10999,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45874</v>
+        <v>45625</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11058,7 +11058,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 4229-2026</t>
+          <t>A 61638-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11072,10 +11072,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46044</v>
+        <v>46002</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>9.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11131,7 +11131,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 4236-2026</t>
+          <t>A 65137-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11145,10 +11145,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46044</v>
+        <v>45288</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11204,7 +11204,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 50154-2022</t>
+          <t>A 47693-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11218,10 +11218,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44865</v>
+        <v>45931</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11277,7 +11277,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 64865-2023</t>
+          <t>A 35894-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11291,10 +11291,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45282</v>
+        <v>45862</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11355,7 +11355,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 34386-2023</t>
+          <t>A 20824-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11369,10 +11369,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45139</v>
+        <v>45058</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11428,7 +11428,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 17350-2023</t>
+          <t>A 17204-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11442,10 +11442,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45035</v>
+        <v>45756</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11501,7 +11501,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 14940-2024</t>
+          <t>A 27191-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11515,10 +11515,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45398</v>
+        <v>44741</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11574,7 +11574,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 56471-2024</t>
+          <t>A 49121-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45625</v>
+        <v>45594</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11647,7 +11647,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 38303-2025</t>
+          <t>A 47396-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11661,10 +11661,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45883</v>
+        <v>45587</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11720,7 +11720,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 17836-2023</t>
+          <t>A 1897-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11734,10 +11734,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45037</v>
+        <v>45671</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11793,7 +11793,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 65137-2023</t>
+          <t>A 51175-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11807,10 +11807,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45288</v>
+        <v>45219</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11866,7 +11866,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 35894-2025</t>
+          <t>A 21311-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11880,10 +11880,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45862</v>
+        <v>46147</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11895,13 +11895,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11944,7 +11939,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 43114-2024</t>
+          <t>A 61995-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11958,10 +11953,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45567</v>
+        <v>44918</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11975,11 +11970,11 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12022,7 +12017,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 4413-2022</t>
+          <t>A 4107-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12036,10 +12031,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44589</v>
+        <v>45684</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12052,7 +12047,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12095,7 +12090,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 4465-2024</t>
+          <t>A 3875-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12109,10 +12104,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45327</v>
+        <v>45322</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12125,7 +12120,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12168,7 +12163,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 21311-2026</t>
+          <t>A 50892-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12182,10 +12177,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46147</v>
+        <v>44867</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12241,7 +12236,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33076-2023</t>
+          <t>A 22318-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12251,14 +12246,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45126</v>
+        <v>46154</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12271,7 +12266,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12314,7 +12309,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 70350-2021</t>
+          <t>A 22423-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12324,14 +12319,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44536</v>
+        <v>46154</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12344,7 +12339,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12387,7 +12382,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 1490-2025</t>
+          <t>A 22718-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12397,14 +12392,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45670</v>
+        <v>46157</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12422,7 +12417,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12465,7 +12460,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 22318-2026</t>
+          <t>A 22756-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12479,10 +12474,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12494,8 +12489,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>1.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12538,7 +12538,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 14549-2025</t>
+          <t>A 22758-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12552,10 +12552,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45741</v>
+        <v>46157</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12567,8 +12567,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12611,7 +12616,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 27405-2024</t>
+          <t>A 22766-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12625,10 +12630,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45474</v>
+        <v>46157</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12640,8 +12645,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12684,7 +12694,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 22423-2026</t>
+          <t>A 22719-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12694,14 +12704,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12713,8 +12723,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12757,7 +12772,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 13036-2022</t>
+          <t>A 22720-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12771,10 +12786,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44643</v>
+        <v>46157</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12786,8 +12801,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12830,7 +12850,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 3955-2022</t>
+          <t>A 22764-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12844,10 +12864,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44587</v>
+        <v>46157</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12859,8 +12879,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12903,7 +12928,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 56456-2024</t>
+          <t>A 22768-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12917,10 +12942,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45625</v>
+        <v>46157</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12932,8 +12957,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12976,7 +13006,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 56459-2024</t>
+          <t>A 22770-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12990,10 +13020,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45625</v>
+        <v>46157</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13005,8 +13035,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13049,7 +13084,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 22764-2026</t>
+          <t>A 22723-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13066,7 +13101,7 @@
         <v>46157</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13084,7 +13119,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13127,7 +13162,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 22768-2026</t>
+          <t>A 20485-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13141,10 +13176,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46157</v>
+        <v>45775</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13162,7 +13197,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13205,7 +13240,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 22770-2026</t>
+          <t>A 20431-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13219,10 +13254,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46157</v>
+        <v>45775</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13240,7 +13275,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13283,7 +13318,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 1897-2025</t>
+          <t>A 20435-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13297,10 +13332,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45671</v>
+        <v>45775</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13312,8 +13347,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13356,7 +13396,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 20431-2025</t>
+          <t>A 20681-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13370,10 +13410,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45775</v>
+        <v>45776</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13391,7 +13431,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13434,7 +13474,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 22723-2026</t>
+          <t>A 47402-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13448,10 +13488,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46157</v>
+        <v>45587</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13463,13 +13503,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13512,7 +13547,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 20681-2025</t>
+          <t>A 24275-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13526,10 +13561,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45776</v>
+        <v>46169</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13541,13 +13576,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13590,7 +13620,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 22718-2026</t>
+          <t>A 24271-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13604,10 +13634,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13619,13 +13649,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13668,7 +13693,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 22766-2026</t>
+          <t>A 24272-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13682,10 +13707,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13697,13 +13722,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13746,7 +13766,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 22756-2026</t>
+          <t>A 24269-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13760,10 +13780,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13775,13 +13795,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>8.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13824,7 +13839,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 22758-2026</t>
+          <t>A 25169-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13838,10 +13853,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46157</v>
+        <v>46175</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13853,13 +13868,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13902,7 +13912,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 20825-2023</t>
+          <t>A 20441-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13916,10 +13926,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45058</v>
+        <v>45775</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13931,8 +13941,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13975,7 +13990,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 20435-2025</t>
+          <t>A 59321-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13989,10 +14004,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45775</v>
+        <v>45637</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14010,7 +14025,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14053,7 +14068,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 20485-2025</t>
+          <t>A 14551-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14067,10 +14082,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45775</v>
+        <v>45741</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14082,13 +14097,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14131,7 +14141,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 22719-2026</t>
+          <t>A 27870-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14145,10 +14155,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46157</v>
+        <v>46191</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14160,13 +14170,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14209,7 +14214,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 22720-2026</t>
+          <t>A 27873-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14223,10 +14228,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46157</v>
+        <v>46191</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14238,13 +14243,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14287,7 +14287,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 48639-2023</t>
+          <t>A 20480-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14301,10 +14301,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45202</v>
+        <v>45775</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14316,8 +14316,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14360,7 +14365,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 24275-2026</t>
+          <t>A 32771-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14374,10 +14379,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46169</v>
+        <v>46241</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14390,7 +14395,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14433,7 +14438,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 24271-2026</t>
+          <t>A 32760-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14447,10 +14452,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46169</v>
+        <v>46241</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14463,7 +14468,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14506,7 +14511,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 24272-2026</t>
+          <t>A 32764-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14520,10 +14525,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46169</v>
+        <v>46241</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14536,7 +14541,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14579,7 +14584,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 24269-2026</t>
+          <t>A 32768-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14593,10 +14598,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46169</v>
+        <v>46241</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14609,7 +14614,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14652,7 +14657,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 50162-2023</t>
+          <t>A 4465-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14662,14 +14667,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45215</v>
+        <v>45327</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14681,13 +14686,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14730,7 +14730,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 25169-2026</t>
+          <t>A 4453-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14744,10 +14744,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46175</v>
+        <v>45327</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14759,8 +14759,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14803,7 +14808,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 2755-2025</t>
+          <t>A 50162-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14813,14 +14818,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45677</v>
+        <v>45215</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14832,8 +14837,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14876,7 +14886,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 21745-2022</t>
+          <t>A 30822-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14890,10 +14900,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44708</v>
+        <v>46205</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14906,7 +14916,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>9.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14949,7 +14959,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 39603-2022</t>
+          <t>A 30826-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14963,10 +14973,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44818</v>
+        <v>46205</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14979,7 +14989,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15022,7 +15032,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 27191-2022</t>
+          <t>A 39389-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15036,10 +15046,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44741</v>
+        <v>45551</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15052,7 +15062,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15095,7 +15105,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 17203-2025</t>
+          <t>A 17552-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15109,10 +15119,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45756</v>
+        <v>45036</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15125,7 +15135,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15168,7 +15178,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 40912-2023</t>
+          <t>A 34855-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15182,10 +15192,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45173</v>
+        <v>46255</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15197,8 +15207,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15241,7 +15256,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 3239-2025</t>
+          <t>A 34894-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15255,10 +15270,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45679</v>
+        <v>46259</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15270,13 +15285,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15319,7 +15329,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 54541-2023</t>
+          <t>A 34984-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15329,14 +15339,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45233</v>
+        <v>46258</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15348,13 +15358,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15397,7 +15402,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 3875-2024</t>
+          <t>A 34820-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15411,10 +15416,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45322</v>
+        <v>46255</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15426,8 +15431,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15470,7 +15480,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 18207-2025</t>
+          <t>A 34661-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15484,10 +15494,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45761</v>
+        <v>46257</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15499,13 +15509,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15548,7 +15553,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 18211-2025</t>
+          <t>A 34806-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15562,10 +15567,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45761</v>
+        <v>46255</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15579,11 +15584,11 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15626,7 +15631,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 41905-2022</t>
+          <t>A 40912-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15640,10 +15645,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44830</v>
+        <v>45173</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15655,13 +15660,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15704,7 +15704,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 59321-2024</t>
+          <t>A 31252-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15718,10 +15718,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45637</v>
+        <v>46218</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15735,11 +15735,11 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 20441-2025</t>
+          <t>A 35568-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15796,10 +15796,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45775</v>
+        <v>46262</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2</v>
+        <v>6.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15860,7 +15860,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 14551-2025</t>
+          <t>A 35570-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15874,10 +15874,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45741</v>
+        <v>46262</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15889,8 +15889,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15933,7 +15938,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 39436-2022</t>
+          <t>A 18968-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15947,10 +15952,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44818</v>
+        <v>45427</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15963,7 +15968,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16006,7 +16011,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 27870-2026</t>
+          <t>A 53341-2021</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16020,10 +16025,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46191</v>
+        <v>44468</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16036,7 +16041,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16079,7 +16084,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 27873-2026</t>
+          <t>A 36067-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16093,10 +16098,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46191</v>
+        <v>46267</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16108,8 +16113,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16152,7 +16162,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 17204-2025</t>
+          <t>A 36313-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16166,10 +16176,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45756</v>
+        <v>46268</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16182,7 +16192,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16225,7 +16235,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 20480-2025</t>
+          <t>A 17203-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16239,10 +16249,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45775</v>
+        <v>45756</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16254,13 +16264,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16303,7 +16308,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 35332-2022</t>
+          <t>A 48639-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16317,10 +16322,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44798</v>
+        <v>45202</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16333,7 +16338,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16376,7 +16381,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 56467-2024</t>
+          <t>A 37786-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16390,10 +16395,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45625</v>
+        <v>46279</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16449,7 +16454,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 59320-2024</t>
+          <t>A 27574-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16463,10 +16468,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45637</v>
+        <v>45097</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16478,13 +16483,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16527,7 +16527,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 32760-2026</t>
+          <t>A 4839-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16541,10 +16541,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46241</v>
+        <v>44955</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16600,7 +16600,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 32764-2026</t>
+          <t>A 14549-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16614,10 +16614,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46241</v>
+        <v>45741</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16673,7 +16673,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 32768-2026</t>
+          <t>A 30600-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16687,10 +16687,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46241</v>
+        <v>45493</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16746,7 +16746,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 70349-2021</t>
+          <t>A 24171-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16760,10 +16760,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44536</v>
+        <v>45456</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16819,7 +16819,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 32771-2026</t>
+          <t>A 64865-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16833,10 +16833,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46241</v>
+        <v>45282</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16848,8 +16848,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16892,7 +16897,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 30826-2026</t>
+          <t>A 41900-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16906,10 +16911,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46205</v>
+        <v>44830</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16921,8 +16926,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16965,7 +16975,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 30822-2026</t>
+          <t>A 38227-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16979,10 +16989,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46205</v>
+        <v>45161</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16995,7 +17005,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17038,7 +17048,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 30914-2022</t>
+          <t>A 35332-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17052,10 +17062,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44767</v>
+        <v>44798</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17068,7 +17078,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17111,7 +17121,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 73140-2021</t>
+          <t>A 20825-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17125,10 +17135,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44550</v>
+        <v>45058</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17141,7 +17151,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17184,7 +17194,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 27574-2023</t>
+          <t>A 13751-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17198,10 +17208,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45097</v>
+        <v>45737</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17214,7 +17224,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17257,7 +17267,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 53341-2021</t>
+          <t>A 27405-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17271,10 +17281,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44468</v>
+        <v>45474</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17287,7 +17297,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17330,7 +17340,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 4839-2023</t>
+          <t>A 59173-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17344,10 +17354,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44955</v>
+        <v>45253</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17360,7 +17370,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17403,7 +17413,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 3605-2024</t>
+          <t>A 3714-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17417,10 +17427,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45320</v>
+        <v>44586</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17432,8 +17442,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17476,7 +17491,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 21546-2023</t>
+          <t>A 18207-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17490,10 +17505,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45063</v>
+        <v>45761</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17503,6 +17518,11 @@
       <c r="G221" t="inlineStr">
         <is>
           <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I221" t="n">
@@ -17549,7 +17569,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 34661-2026</t>
+          <t>A 18211-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17563,10 +17583,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46257</v>
+        <v>45761</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17578,8 +17598,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17622,7 +17647,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 34806-2026</t>
+          <t>A 642-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17632,14 +17657,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46255</v>
+        <v>45299</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17653,11 +17678,11 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17700,7 +17725,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 34820-2026</t>
+          <t>A 33076-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17710,14 +17735,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46255</v>
+        <v>45126</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17729,13 +17754,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17778,7 +17798,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 34855-2026</t>
+          <t>A 47386-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17792,10 +17812,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46255</v>
+        <v>45587</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17807,13 +17827,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17856,7 +17871,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 34894-2026</t>
+          <t>A 63927-2021</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17870,10 +17885,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46259</v>
+        <v>44509</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17885,8 +17900,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17929,7 +17949,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 15180-2023</t>
+          <t>A 39603-2022</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17943,10 +17963,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45016</v>
+        <v>44818</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17959,7 +17979,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18002,7 +18022,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 34984-2026</t>
+          <t>A 11843-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18016,10 +18036,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46258</v>
+        <v>45376</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18029,6 +18049,11 @@
       <c r="G228" t="inlineStr">
         <is>
           <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I228" t="n">
@@ -18075,7 +18100,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 35570-2026</t>
+          <t>A 14940-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18089,10 +18114,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46262</v>
+        <v>45398</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18104,13 +18129,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18153,7 +18173,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 859-2025</t>
+          <t>A 4413-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18163,14 +18183,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45665</v>
+        <v>44589</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18182,13 +18202,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18231,7 +18246,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 52031-2023</t>
+          <t>A 3605-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18245,10 +18260,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45223</v>
+        <v>45320</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18261,7 +18276,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18304,7 +18319,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 31252-2026</t>
+          <t>A 34386-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18318,10 +18333,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46218</v>
+        <v>45139</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18333,13 +18348,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18382,7 +18392,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 35568-2026</t>
+          <t>A 21546-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18396,10 +18406,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46262</v>
+        <v>45063</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18411,13 +18421,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>6.9</v>
+        <v>1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18460,7 +18465,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 30966-2023</t>
+          <t>A 15864-2022</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18474,10 +18479,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45113</v>
+        <v>44664</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18490,7 +18495,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18533,7 +18538,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 68507-2021</t>
+          <t>A 38712-2022</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18547,10 +18552,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44529</v>
+        <v>44814</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18563,7 +18568,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18606,7 +18611,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 38712-2022</t>
+          <t>A 22432-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18616,14 +18621,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44814</v>
+        <v>45070</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18635,8 +18640,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I236" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18679,7 +18689,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 36067-2026</t>
+          <t>A 56529-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18693,10 +18703,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46267</v>
+        <v>44893</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18708,13 +18718,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I237" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18757,7 +18762,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 43206-2024</t>
+          <t>A 43114-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18774,7 +18779,7 @@
         <v>45567</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18786,8 +18791,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18830,7 +18840,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 36313-2026</t>
+          <t>A 21745-2022</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18844,10 +18854,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46268</v>
+        <v>44708</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18860,7 +18870,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18903,7 +18913,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 15203-2023</t>
+          <t>A 37399-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18913,14 +18923,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45017</v>
+        <v>45540</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18932,13 +18942,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18981,7 +18986,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 15204-2023</t>
+          <t>A 27080-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18991,14 +18996,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45017</v>
+        <v>44741</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19010,13 +19015,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I241" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19059,7 +19059,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 8690-2023</t>
+          <t>A 43206-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19073,10 +19073,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44978</v>
+        <v>45567</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19132,7 +19132,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 61995-2022</t>
+          <t>A 39436-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19146,10 +19146,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44918</v>
+        <v>44818</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19161,13 +19161,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19210,7 +19205,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 4453-2024</t>
+          <t>A 13036-2022</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19224,10 +19219,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45327</v>
+        <v>44643</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19239,13 +19234,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I244" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19288,7 +19278,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 49121-2024</t>
+          <t>A 52031-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19302,10 +19292,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45594</v>
+        <v>45223</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19318,7 +19308,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19361,7 +19351,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 56475-2024</t>
+          <t>A 70349-2021</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19375,10 +19365,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45625</v>
+        <v>44536</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19434,7 +19424,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 51990-2024</t>
+          <t>A 70350-2021</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19448,10 +19438,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45607</v>
+        <v>44536</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19464,7 +19454,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19507,7 +19497,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 41598-2024</t>
+          <t>A 2755-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19517,14 +19507,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45560</v>
+        <v>45677</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19537,7 +19527,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19580,7 +19570,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 20852-2025</t>
+          <t>A 61575-2022</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19594,10 +19584,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45777</v>
+        <v>44916</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19611,11 +19601,11 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I249" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19658,7 +19648,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 61439-2024</t>
+          <t>A 61588-2022</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19672,10 +19662,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45646</v>
+        <v>44916</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19687,8 +19677,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I250" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19731,7 +19726,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 21951-2025</t>
+          <t>A 17350-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19741,14 +19736,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45784</v>
+        <v>45035</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19760,13 +19755,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I251" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19809,7 +19799,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 37964-2024</t>
+          <t>A 20852-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19819,14 +19809,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45544</v>
+        <v>45777</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19838,8 +19828,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I252" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19882,7 +19877,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 4742-2025</t>
+          <t>A 51990-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19896,10 +19891,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45688</v>
+        <v>45607</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19911,13 +19906,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I253" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19960,7 +19950,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 29566-2024</t>
+          <t>A 41598-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19974,10 +19964,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45484</v>
+        <v>45560</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19990,7 +19980,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>21.3</v>
+        <v>0.8</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20033,7 +20023,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 53487-2024</t>
+          <t>A 61439-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20047,10 +20037,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45611</v>
+        <v>45646</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20063,7 +20053,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20106,7 +20096,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 10414-2025</t>
+          <t>A 21951-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20116,14 +20106,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45720</v>
+        <v>45784</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20135,8 +20125,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I256" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20179,7 +20174,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 37964-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20189,14 +20184,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45708</v>
+        <v>45544</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20252,7 +20247,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 8173-2025</t>
+          <t>A 4742-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20262,14 +20257,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45708</v>
+        <v>45688</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20281,8 +20276,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I258" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20325,24 +20325,24 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>S 2061-2022</t>
+          <t>A 29566-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>44672</v>
+        <v>45484</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>1.6</v>
+        <v>21.3</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20415,7 +20415,7 @@
         <v>45105</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>44795</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>44959</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>S 1592-2023</t>
+          <t>S 2061-2022</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20627,14 +20627,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45056</v>
+        <v>44672</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>19.5</v>
+        <v>1.6</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20690,7 +20690,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>S 366-2023</t>
+          <t>S 1592-2023</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20704,10 +20704,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>44959</v>
+        <v>45056</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>35.8</v>
+        <v>19.5</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20763,7 +20763,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>S 6799-2022</t>
+          <t>S 366-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20777,10 +20777,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>44893</v>
+        <v>44959</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>28.2</v>
+        <v>35.8</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20836,7 +20836,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>S 6798-2022</t>
+          <t>S 6799-2022</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20853,7 +20853,7 @@
         <v>44893</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>149.8</v>
+        <v>28.2</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20909,7 +20909,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>S 1806-2023</t>
+          <t>S 6798-2022</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20923,10 +20923,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45072</v>
+        <v>44893</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>61.9</v>
+        <v>149.8</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20982,7 +20982,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>S 3254-2023</t>
+          <t>S 1806-2023</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20996,10 +20996,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45193</v>
+        <v>45072</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>88.59999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21055,7 +21055,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>S 1019-2024</t>
+          <t>S 3254-2023</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21069,10 +21069,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45386</v>
+        <v>45193</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>14.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21128,7 +21128,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>S 4655-2022</t>
+          <t>S 1019-2024</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21142,10 +21142,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>44795</v>
+        <v>45386</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>19.1</v>
+        <v>14.5</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21201,7 +21201,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>S 312-2025</t>
+          <t>S 4655-2022</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21215,10 +21215,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45688</v>
+        <v>44795</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>25.8</v>
+        <v>19.1</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>S 1799-2025</t>
+          <t>S 312-2025</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21288,10 +21288,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45817</v>
+        <v>45688</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>21.2</v>
+        <v>25.8</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21347,7 +21347,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>S 1798-2025</t>
+          <t>S 1799-2025</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21364,7 +21364,7 @@
         <v>45817</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>73.40000000000001</v>
+        <v>21.2</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>S 3564-2025</t>
+          <t>S 1798-2025</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21434,10 +21434,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>46013</v>
+        <v>45817</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>55.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21493,7 +21493,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>S 3565-2025</t>
+          <t>S 3564-2025</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21510,7 +21510,7 @@
         <v>46013</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>24</v>
+        <v>55.7</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21566,148 +21566,221 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
+          <t>S 3565-2025</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D276" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E276" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I276" t="n">
+        <v>24</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" t="n">
+        <v>0</v>
+      </c>
+      <c r="L276" t="n">
+        <v>0</v>
+      </c>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+      <c r="N276" t="n">
+        <v>0</v>
+      </c>
+      <c r="O276" t="n">
+        <v>0</v>
+      </c>
+      <c r="P276" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>0</v>
+      </c>
+      <c r="R276" t="n">
+        <v>0</v>
+      </c>
+      <c r="S276" t="n">
+        <v>0</v>
+      </c>
+      <c r="T276" t="n">
+        <v>0</v>
+      </c>
+      <c r="U276" t="n">
+        <v>0</v>
+      </c>
+      <c r="V276" s="2" t="inlineStr"/>
+    </row>
+    <row r="277" ht="15" customHeight="1">
+      <c r="A277" t="inlineStr">
+        <is>
           <t>S 375-2026</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
+      <c r="C277" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D276" s="1" t="n">
+      <c r="D277" s="1" t="n">
         <v>46065</v>
       </c>
-      <c r="E276" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="I276" t="n">
+      <c r="E277" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I277" t="n">
         <v>17.6</v>
       </c>
-      <c r="J276" t="n">
-        <v>0</v>
-      </c>
-      <c r="K276" t="n">
-        <v>0</v>
-      </c>
-      <c r="L276" t="n">
-        <v>0</v>
-      </c>
-      <c r="M276" t="n">
-        <v>0</v>
-      </c>
-      <c r="N276" t="n">
-        <v>0</v>
-      </c>
-      <c r="O276" t="n">
-        <v>0</v>
-      </c>
-      <c r="P276" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
-      <c r="R276" t="n">
-        <v>0</v>
-      </c>
-      <c r="S276" t="n">
-        <v>0</v>
-      </c>
-      <c r="T276" t="n">
-        <v>0</v>
-      </c>
-      <c r="U276" t="n">
-        <v>0</v>
-      </c>
-      <c r="V276" s="2" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" t="n">
+        <v>0</v>
+      </c>
+      <c r="L277" t="n">
+        <v>0</v>
+      </c>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+      <c r="N277" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" t="n">
+        <v>0</v>
+      </c>
+      <c r="P277" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>0</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0</v>
+      </c>
+      <c r="S277" t="n">
+        <v>0</v>
+      </c>
+      <c r="T277" t="n">
+        <v>0</v>
+      </c>
+      <c r="U277" t="n">
+        <v>0</v>
+      </c>
+      <c r="V277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
         <is>
           <t>S 1393-2026</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
+      <c r="C278" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D277" s="1" t="n">
+      <c r="D278" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="E277" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="I277" t="n">
+      <c r="E278" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I278" t="n">
         <v>3.4</v>
       </c>
-      <c r="J277" t="n">
-        <v>0</v>
-      </c>
-      <c r="K277" t="n">
-        <v>0</v>
-      </c>
-      <c r="L277" t="n">
-        <v>0</v>
-      </c>
-      <c r="M277" t="n">
-        <v>0</v>
-      </c>
-      <c r="N277" t="n">
-        <v>0</v>
-      </c>
-      <c r="O277" t="n">
-        <v>0</v>
-      </c>
-      <c r="P277" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
-      <c r="R277" t="n">
-        <v>0</v>
-      </c>
-      <c r="S277" t="n">
-        <v>0</v>
-      </c>
-      <c r="T277" t="n">
-        <v>0</v>
-      </c>
-      <c r="U277" t="n">
-        <v>0</v>
-      </c>
-      <c r="V277" s="2" t="inlineStr"/>
+      <c r="J278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" t="n">
+        <v>0</v>
+      </c>
+      <c r="L278" t="n">
+        <v>0</v>
+      </c>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>0</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="n">
+        <v>0</v>
+      </c>
+      <c r="T278" t="n">
+        <v>0</v>
+      </c>
+      <c r="U278" t="n">
+        <v>0</v>
+      </c>
+      <c r="V278" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LESSEBO.xlsx
+++ b/Översikt LESSEBO.xlsx
@@ -601,7 +601,7 @@
         <v>45349</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>46035</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45954</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45954</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45954</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45267</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>46176</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45072</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45954</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1488-2025</t>
+          <t>A 52539-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1713,14 +1713,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45670</v>
+        <v>45954</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1732,14 +1732,19 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1769,152 +1774,147 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52539-2025 artfynd.xlsx", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52539-2025 karta.png", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52539-2025 georefererad karta.tif", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52539-2025 FSC-klagomål.docx", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52539-2025 FSC-klagomål mail.docx", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52539-2025 tillsynsbegäran.docx", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52539-2025 tillsynsbegäran mail.docx", "A 52539-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 1488-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45670</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Korallrot</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 1488-2025 artfynd.xlsx", "A 1488-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 1488-2025 karta.png", "A 1488-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 1488-2025 georefererad karta.tif", "A 1488-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 1488-2025 FSC-klagomål.docx", "A 1488-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 1488-2025 FSC-klagomål mail.docx", "A 1488-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 1488-2025 tillsynsbegäran.docx", "A 1488-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 1488-2025 tillsynsbegäran mail.docx", "A 1488-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 52539-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45954</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52539-2025 artfynd.xlsx", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52539-2025 karta.png", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52539-2025 georefererad karta.tif", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52539-2025 FSC-klagomål.docx", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52539-2025 FSC-klagomål mail.docx", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52539-2025 tillsynsbegäran.docx", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52539-2025 tillsynsbegäran mail.docx", "A 52539-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45625</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44510</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44518</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44865</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 3741-2022</t>
+          <t>A 24680-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44586</v>
+        <v>44727</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2892,13 +2892,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2941,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 24680-2022</t>
+          <t>A 3741-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2955,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44727</v>
+        <v>44586</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2970,8 +2965,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>44510</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 45095-2022</t>
+          <t>A 59408-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44842</v>
+        <v>44491</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3189,13 +3189,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3238,7 +3233,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59408-2021</t>
+          <t>A 45095-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3252,10 +3247,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44491</v>
+        <v>44842</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3267,8 +3262,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 68513-2021</t>
+          <t>A 27080-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44529</v>
+        <v>44741</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19495-2022</t>
+          <t>A 63330-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44693</v>
+        <v>44508</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 63330-2021</t>
+          <t>A 68513-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44508</v>
+        <v>44529</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>44522</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 27794-2022</t>
+          <t>A 11843-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44743</v>
+        <v>45376</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3632,8 +3632,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3676,7 +3681,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 51006-2021</t>
+          <t>A 2755-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3686,14 +3691,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44460</v>
+        <v>45677</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3706,7 +3711,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3749,7 +3754,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33240-2024</t>
+          <t>A 21745-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3763,10 +3768,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45518</v>
+        <v>44708</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3779,7 +3784,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3822,7 +3827,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56456-2024</t>
+          <t>A 39603-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3836,10 +3841,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45625</v>
+        <v>44818</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3852,7 +3857,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3895,7 +3900,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56459-2024</t>
+          <t>A 27794-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45625</v>
+        <v>44743</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3925,7 +3930,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3968,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27713-2022</t>
+          <t>A 19495-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3982,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44743</v>
+        <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3998,7 +4003,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4041,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 68507-2021</t>
+          <t>A 51189-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4055,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44529</v>
+        <v>45219</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4071,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4114,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1367-2023</t>
+          <t>A 27191-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4128,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44936</v>
+        <v>44741</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4144,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4187,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24478-2024</t>
+          <t>A 51006-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4201,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45459</v>
+        <v>44460</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30966-2023</t>
+          <t>A 17203-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45113</v>
+        <v>45756</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4290,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4333,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59320-2024</t>
+          <t>A 40912-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4347,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45637</v>
+        <v>45173</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4362,13 +4367,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15203-2023</t>
+          <t>A 27713-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4421,14 +4421,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45017</v>
+        <v>44743</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4440,13 +4440,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4489,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15204-2023</t>
+          <t>A 59173-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4499,14 +4494,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45017</v>
+        <v>45253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4518,13 +4513,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4567,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8655-2025</t>
+          <t>A 3876-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4581,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45710</v>
+        <v>45322</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4597,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4640,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61641-2025</t>
+          <t>A 3239-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4654,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46002</v>
+        <v>45679</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4671,11 +4661,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4718,7 +4708,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43453-2024</t>
+          <t>A 10047-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4732,10 +4722,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45568</v>
+        <v>45364</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4747,8 +4737,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4791,7 +4786,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10414-2025</t>
+          <t>A 54541-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4801,14 +4796,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45720</v>
+        <v>45233</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4820,8 +4815,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 53487-2024</t>
+          <t>A 3875-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45611</v>
+        <v>45322</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4937,7 +4937,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8173-2025</t>
+          <t>A 24171-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4947,14 +4947,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45708</v>
+        <v>45456</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5010,7 +5010,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62728-2025</t>
+          <t>A 24478-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46008</v>
+        <v>45459</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5039,13 +5039,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5105,7 +5100,7 @@
         <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5161,7 +5156,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 859-2025</t>
+          <t>A 18207-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5171,14 +5166,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45665</v>
+        <v>45761</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5196,7 +5191,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5239,7 +5234,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 10047-2024</t>
+          <t>A 18211-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5253,10 +5248,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45364</v>
+        <v>45761</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5270,11 +5265,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5317,7 +5312,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45838-2022</t>
+          <t>A 41905-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5331,10 +5326,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44846</v>
+        <v>44830</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5346,8 +5341,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 39884-2025</t>
+          <t>A 39436-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45891</v>
+        <v>44818</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5463,7 +5463,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39549-2025</t>
+          <t>A 64635-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45890</v>
+        <v>45281</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7.2</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5536,7 +5536,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39750-2025</t>
+          <t>A 57519-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45891</v>
+        <v>44896</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5609,7 +5609,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1022-2026</t>
+          <t>A 20541-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5623,10 +5623,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46030</v>
+        <v>45436</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1016-2026</t>
+          <t>A 39549-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46030</v>
+        <v>45890</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5755,7 +5755,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15180-2023</t>
+          <t>A 18968-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45016</v>
+        <v>45427</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5828,7 +5828,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20478-2025</t>
+          <t>A 39750-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45775</v>
+        <v>45891</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5857,13 +5857,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5906,7 +5901,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35904-2025</t>
+          <t>A 39884-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5920,10 +5915,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45862</v>
+        <v>45891</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5935,13 +5930,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5984,7 +5974,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29659-2025</t>
+          <t>A 17204-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5994,14 +5984,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45825</v>
+        <v>45756</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6014,7 +6004,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6057,7 +6047,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20851-2025</t>
+          <t>A 35904-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6071,10 +6061,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45777</v>
+        <v>45862</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6092,7 +6082,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6135,7 +6125,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20854-2025</t>
+          <t>A 13347-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6149,10 +6139,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45777</v>
+        <v>46094</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6166,11 +6156,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6213,7 +6203,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20853-2025</t>
+          <t>A 56529-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6227,10 +6217,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45777</v>
+        <v>44893</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6242,13 +6232,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6291,7 +6276,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4236-2026</t>
+          <t>A 38227-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6305,10 +6290,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46044</v>
+        <v>45161</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6321,7 +6306,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6364,7 +6349,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4229-2026</t>
+          <t>A 43809-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6378,10 +6363,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46044</v>
+        <v>45912</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6394,7 +6379,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>9.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6437,7 +6422,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30527-2025</t>
+          <t>A 3714-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6451,10 +6436,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45831</v>
+        <v>44586</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6466,8 +6451,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6510,7 +6500,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 43809-2025</t>
+          <t>A 35332-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6524,10 +6514,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45912</v>
+        <v>44798</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6540,7 +6530,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6583,7 +6573,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32712-2025</t>
+          <t>A 44904-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6597,10 +6587,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45839</v>
+        <v>45918</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6612,13 +6602,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6661,7 +6646,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44904-2025</t>
+          <t>A 33240-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6675,10 +6660,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45918</v>
+        <v>45518</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6691,7 +6676,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>7.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6751,7 +6736,7 @@
         <v>45918</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6807,7 +6792,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7957-2023</t>
+          <t>A 39389-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6821,10 +6806,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44973</v>
+        <v>45551</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6837,7 +6822,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6880,7 +6865,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17836-2023</t>
+          <t>A 60358-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6894,10 +6879,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45037</v>
+        <v>44910</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6910,7 +6895,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6953,7 +6938,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8438-2026</t>
+          <t>A 56467-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6967,10 +6952,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46065</v>
+        <v>45625</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6982,13 +6967,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7031,7 +7011,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 30914-2022</t>
+          <t>A 61575-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7045,10 +7025,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44767</v>
+        <v>44916</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7060,8 +7040,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7104,7 +7089,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35909-2025</t>
+          <t>A 61588-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7118,10 +7103,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45862</v>
+        <v>44916</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7135,11 +7120,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7182,7 +7167,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35899-2025</t>
+          <t>A 43453-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7196,10 +7181,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45862</v>
+        <v>45568</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7211,13 +7196,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7260,7 +7240,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48429-2025</t>
+          <t>A 18464-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7274,10 +7254,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45934</v>
+        <v>46127</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7289,8 +7269,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.9</v>
+        <v>14.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7333,7 +7318,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 48433-2025</t>
+          <t>A 18466-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7347,10 +7332,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45934</v>
+        <v>46127</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7362,8 +7347,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>7.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7406,7 +7396,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 19501-2022</t>
+          <t>A 18625-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7420,10 +7410,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44693</v>
+        <v>46127</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7436,7 +7426,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7479,7 +7469,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 17729-2025</t>
+          <t>A 47396-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7493,10 +7483,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45758</v>
+        <v>45587</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7508,13 +7498,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7557,7 +7542,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 49298-2025</t>
+          <t>A 59320-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7571,10 +7556,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45938</v>
+        <v>45637</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7586,8 +7571,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7630,7 +7620,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10189-2026</t>
+          <t>A 48429-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7644,10 +7634,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46076</v>
+        <v>45934</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7660,7 +7650,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7703,7 +7693,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 20443-2025</t>
+          <t>A 48433-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7717,10 +7707,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45775</v>
+        <v>45934</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7732,13 +7722,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7781,7 +7766,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10286-2026</t>
+          <t>A 17729-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7795,10 +7780,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46076</v>
+        <v>45758</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7810,8 +7795,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7854,7 +7844,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10185-2026</t>
+          <t>A 20443-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7868,10 +7858,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46076</v>
+        <v>45775</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7883,8 +7873,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7927,7 +7922,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 50154-2022</t>
+          <t>A 49298-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7941,10 +7936,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44865</v>
+        <v>45938</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7957,7 +7952,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8000,7 +7995,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 29767-2023</t>
+          <t>A 7957-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8014,10 +8009,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45107</v>
+        <v>44973</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8030,7 +8025,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8073,7 +8068,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 21917-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8083,14 +8078,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45708</v>
+        <v>45784</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8103,7 +8098,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8146,7 +8141,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 41905-2022</t>
+          <t>A 20855-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8160,10 +8155,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44830</v>
+        <v>45777</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8181,7 +8176,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8224,7 +8219,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 3955-2022</t>
+          <t>A 47386-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8238,10 +8233,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44587</v>
+        <v>45587</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8254,7 +8249,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8297,7 +8292,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 60358-2022</t>
+          <t>A 1894-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8311,10 +8306,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44910</v>
+        <v>45671</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8327,7 +8322,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8370,7 +8365,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 52031-2025</t>
+          <t>A 47693-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8384,10 +8379,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45952</v>
+        <v>45931</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8400,7 +8395,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8443,7 +8438,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17517-2023</t>
+          <t>A 20056-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8457,10 +8452,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45036</v>
+        <v>45772</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8473,7 +8468,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8516,7 +8511,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20541-2024</t>
+          <t>A 37399-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8530,10 +8525,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45436</v>
+        <v>45540</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8546,7 +8541,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8589,7 +8584,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13347-2026</t>
+          <t>A 52031-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8603,10 +8598,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46094</v>
+        <v>45952</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8618,13 +8613,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8667,7 +8657,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 64635-2023</t>
+          <t>A 52537-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8681,10 +8671,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45281</v>
+        <v>45954</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8696,8 +8686,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8740,7 +8735,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 14584-2023</t>
+          <t>A 52531-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8754,10 +8749,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45013</v>
+        <v>45954</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8769,8 +8764,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8813,7 +8813,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 73140-2021</t>
+          <t>A 52532-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8827,10 +8827,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44550</v>
+        <v>45954</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8842,8 +8842,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8886,7 +8891,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52537-2025</t>
+          <t>A 52546-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8903,7 +8908,7 @@
         <v>45954</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8921,7 +8926,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8964,7 +8969,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 52531-2025</t>
+          <t>A 51175-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8978,10 +8983,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45954</v>
+        <v>45219</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8993,13 +8998,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9042,7 +9042,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 52532-2025</t>
+          <t>A 52534-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9059,7 +9059,7 @@
         <v>45954</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9120,7 +9120,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 52546-2025</t>
+          <t>A 53122-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9134,10 +9134,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9149,13 +9149,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9198,7 +9193,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 52534-2025</t>
+          <t>A 14584-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9212,10 +9207,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45954</v>
+        <v>45013</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9227,13 +9222,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9276,7 +9266,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 53122-2025</t>
+          <t>A 36895-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9290,10 +9280,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45958</v>
+        <v>45874</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9306,7 +9296,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9349,7 +9339,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 30405-2023</t>
+          <t>A 49295-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9363,10 +9353,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45111</v>
+        <v>45938</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9379,7 +9369,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9422,7 +9412,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 3239-2025</t>
+          <t>A 29767-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9436,10 +9426,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45679</v>
+        <v>45107</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9451,13 +9441,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9500,7 +9485,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 52525-2023</t>
+          <t>A 19501-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9514,10 +9499,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45225</v>
+        <v>44693</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9530,7 +9515,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9573,7 +9558,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 18625-2026</t>
+          <t>A 70349-2021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9587,10 +9572,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46127</v>
+        <v>44536</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9603,7 +9588,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9663,7 +9648,7 @@
         <v>45219</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9719,7 +9704,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 49295-2025</t>
+          <t>A 56471-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9733,10 +9718,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45938</v>
+        <v>45625</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9749,7 +9734,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9792,7 +9777,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 18464-2026</t>
+          <t>A 38303-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9806,10 +9791,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46127</v>
+        <v>45883</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9821,13 +9806,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>14.2</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9870,7 +9850,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 18466-2026</t>
+          <t>A 52525-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9884,10 +9864,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46127</v>
+        <v>45225</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9899,13 +9879,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>7.9</v>
+        <v>2.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9948,7 +9923,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 56467-2024</t>
+          <t>A 17517-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9962,10 +9937,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45625</v>
+        <v>45036</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9978,7 +9953,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10021,7 +9996,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 20056-2025</t>
+          <t>A 1367-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10035,10 +10010,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45772</v>
+        <v>44936</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10051,7 +10026,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10094,7 +10069,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 36895-2025</t>
+          <t>A 4107-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10108,10 +10083,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45874</v>
+        <v>45684</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10124,7 +10099,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10167,7 +10142,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 38303-2025</t>
+          <t>A 35894-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10181,10 +10156,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45883</v>
+        <v>45862</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10196,8 +10171,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10240,7 +10220,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 3876-2024</t>
+          <t>A 21311-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10254,10 +10234,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45322</v>
+        <v>46147</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10270,7 +10250,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10313,7 +10293,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 1490-2025</t>
+          <t>A 61638-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10323,14 +10303,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45670</v>
+        <v>46002</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10342,13 +10322,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>6.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10391,7 +10366,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56471-2024</t>
+          <t>A 61641-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10405,10 +10380,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45625</v>
+        <v>46002</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10420,8 +10395,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10464,7 +10444,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 21917-2025</t>
+          <t>A 22318-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10478,10 +10458,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45784</v>
+        <v>46154</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10494,7 +10474,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10537,7 +10517,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 54541-2023</t>
+          <t>A 30914-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10547,14 +10527,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45233</v>
+        <v>44767</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10566,13 +10546,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10615,7 +10590,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 51189-2023</t>
+          <t>A 63927-2021</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10629,10 +10604,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45219</v>
+        <v>44509</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10644,8 +10619,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10688,7 +10668,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 8690-2023</t>
+          <t>A 22423-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10698,14 +10678,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44978</v>
+        <v>46154</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10718,7 +10698,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10761,7 +10741,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 1894-2025</t>
+          <t>A 62728-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10775,10 +10755,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45671</v>
+        <v>46008</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10790,8 +10770,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10834,7 +10819,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 20855-2025</t>
+          <t>A 8655-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10848,10 +10833,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45777</v>
+        <v>45710</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10863,13 +10848,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10912,7 +10892,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 57519-2022</t>
+          <t>A 22764-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10926,10 +10906,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44896</v>
+        <v>46157</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10941,8 +10921,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10985,7 +10970,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56475-2024</t>
+          <t>A 22768-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10999,10 +10984,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45625</v>
+        <v>46157</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11014,8 +10999,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11058,7 +11048,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 61638-2025</t>
+          <t>A 22770-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11072,10 +11062,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46002</v>
+        <v>46157</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11087,8 +11077,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11131,7 +11126,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 65137-2023</t>
+          <t>A 20431-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11145,10 +11140,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45288</v>
+        <v>45775</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11160,8 +11155,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11204,7 +11204,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 47693-2025</t>
+          <t>A 22723-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11218,10 +11218,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45931</v>
+        <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11233,8 +11233,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11277,7 +11282,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 35894-2025</t>
+          <t>A 20681-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11291,10 +11296,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45862</v>
+        <v>45776</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11312,7 +11317,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11355,7 +11360,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 20824-2023</t>
+          <t>A 22718-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11369,10 +11374,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45058</v>
+        <v>46157</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11384,8 +11389,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11428,7 +11438,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 17204-2025</t>
+          <t>A 22766-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11442,10 +11452,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45756</v>
+        <v>46157</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11455,6 +11465,11 @@
       <c r="G140" t="inlineStr">
         <is>
           <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I140" t="n">
@@ -11501,7 +11516,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 27191-2022</t>
+          <t>A 22756-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11515,10 +11530,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44741</v>
+        <v>46157</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11530,8 +11545,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>4.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11574,7 +11594,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 49121-2024</t>
+          <t>A 22758-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11588,10 +11608,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45594</v>
+        <v>46157</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11603,8 +11623,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11647,7 +11672,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 47396-2024</t>
+          <t>A 20435-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11661,10 +11686,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45587</v>
+        <v>45775</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11676,8 +11701,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11720,7 +11750,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 1897-2025</t>
+          <t>A 20485-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11734,10 +11764,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45671</v>
+        <v>45775</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11749,8 +11779,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11793,7 +11828,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 51175-2023</t>
+          <t>A 22719-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11807,10 +11842,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45219</v>
+        <v>46157</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11822,8 +11857,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11866,7 +11906,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 21311-2026</t>
+          <t>A 22720-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11880,10 +11920,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46147</v>
+        <v>46157</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11895,8 +11935,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11939,7 +11984,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 61995-2022</t>
+          <t>A 41900-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11953,10 +11998,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44918</v>
+        <v>44830</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11970,11 +12015,11 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12017,7 +12062,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 4107-2025</t>
+          <t>A 22432-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12027,14 +12072,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45684</v>
+        <v>45070</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12046,8 +12091,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12090,7 +12140,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 3875-2024</t>
+          <t>A 73140-2021</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12104,10 +12154,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45322</v>
+        <v>44550</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12120,7 +12170,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12163,7 +12213,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 50892-2022</t>
+          <t>A 1022-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12177,10 +12227,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44867</v>
+        <v>46030</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12193,7 +12243,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12236,7 +12286,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 22318-2026</t>
+          <t>A 17552-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12250,10 +12300,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46154</v>
+        <v>45036</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12266,7 +12316,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12309,7 +12359,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 22423-2026</t>
+          <t>A 1016-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12319,14 +12369,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46154</v>
+        <v>46030</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12339,7 +12389,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12382,7 +12432,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 22718-2026</t>
+          <t>A 13751-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12396,10 +12446,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46157</v>
+        <v>45737</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12411,13 +12461,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12460,7 +12505,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 22756-2026</t>
+          <t>A 30405-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12474,10 +12519,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46157</v>
+        <v>45111</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12489,13 +12534,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>8.699999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12538,7 +12578,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 22758-2026</t>
+          <t>A 24275-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12552,10 +12592,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12567,13 +12607,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12616,7 +12651,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 22766-2026</t>
+          <t>A 27574-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12630,10 +12665,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46157</v>
+        <v>45097</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12645,13 +12680,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12694,7 +12724,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 22719-2026</t>
+          <t>A 24271-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12708,10 +12738,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12723,13 +12753,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12772,7 +12797,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 22720-2026</t>
+          <t>A 24272-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12786,10 +12811,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12801,13 +12826,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12850,7 +12870,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 22764-2026</t>
+          <t>A 24269-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12864,10 +12884,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12879,13 +12899,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12928,7 +12943,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 22768-2026</t>
+          <t>A 53341-2021</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12942,10 +12957,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46157</v>
+        <v>44468</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12957,13 +12972,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13006,7 +13016,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 22770-2026</t>
+          <t>A 4839-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13020,10 +13030,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46157</v>
+        <v>44955</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13035,13 +13045,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13084,7 +13089,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 22723-2026</t>
+          <t>A 25169-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13098,10 +13103,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46157</v>
+        <v>46175</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13113,13 +13118,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13162,7 +13162,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 20485-2025</t>
+          <t>A 4229-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13176,10 +13176,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45775</v>
+        <v>46044</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13191,13 +13191,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13240,7 +13235,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 20431-2025</t>
+          <t>A 50892-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13254,10 +13249,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45775</v>
+        <v>44867</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13269,13 +13264,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13318,7 +13308,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 20435-2025</t>
+          <t>A 4236-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13332,10 +13322,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45775</v>
+        <v>46044</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13347,13 +13337,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13396,7 +13381,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 20681-2025</t>
+          <t>A 3605-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13410,10 +13395,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45776</v>
+        <v>45320</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13425,13 +13410,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13474,7 +13454,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 47402-2024</t>
+          <t>A 45838-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13488,10 +13468,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45587</v>
+        <v>44846</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13504,7 +13484,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13547,7 +13527,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 24275-2026</t>
+          <t>A 20824-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13561,10 +13541,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46169</v>
+        <v>45058</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13577,7 +13557,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13620,7 +13600,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 24271-2026</t>
+          <t>A 30600-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13634,10 +13614,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46169</v>
+        <v>45493</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13650,7 +13630,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13693,7 +13673,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 24272-2026</t>
+          <t>A 15864-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13707,10 +13687,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46169</v>
+        <v>44664</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13723,7 +13703,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13766,7 +13746,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 24269-2026</t>
+          <t>A 642-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13776,14 +13756,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46169</v>
+        <v>45299</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13795,8 +13775,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13839,7 +13824,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 25169-2026</t>
+          <t>A 21546-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13853,10 +13838,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46175</v>
+        <v>45063</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13869,7 +13854,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13912,7 +13897,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 20441-2025</t>
+          <t>A 8438-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13926,10 +13911,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45775</v>
+        <v>46065</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13947,7 +13932,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14007,7 +13992,7 @@
         <v>45637</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14068,7 +14053,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 14551-2025</t>
+          <t>A 47402-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14082,10 +14067,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45741</v>
+        <v>45587</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14098,7 +14083,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.3</v>
+        <v>5.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14141,7 +14126,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 27870-2026</t>
+          <t>A 20441-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14155,10 +14140,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46191</v>
+        <v>45775</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14170,8 +14155,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14214,7 +14204,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 27873-2026</t>
+          <t>A 10286-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14228,10 +14218,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46191</v>
+        <v>46076</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14244,7 +14234,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14287,7 +14277,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 20480-2025</t>
+          <t>A 14551-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14301,10 +14291,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45775</v>
+        <v>45741</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14316,13 +14306,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14365,7 +14350,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 32771-2026</t>
+          <t>A 10185-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14379,10 +14364,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46241</v>
+        <v>46076</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14395,7 +14380,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14438,7 +14423,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 32760-2026</t>
+          <t>A 10189-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14452,10 +14437,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46241</v>
+        <v>46076</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14468,7 +14453,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14511,7 +14496,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 32764-2026</t>
+          <t>A 27870-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14525,10 +14510,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46241</v>
+        <v>46191</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14541,7 +14526,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14584,7 +14569,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 32768-2026</t>
+          <t>A 27873-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14598,10 +14583,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46241</v>
+        <v>46191</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14614,7 +14599,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14657,7 +14642,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 4465-2024</t>
+          <t>A 20480-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14671,10 +14656,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45327</v>
+        <v>45775</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14686,8 +14671,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14730,7 +14720,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 4453-2024</t>
+          <t>A 50154-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14744,10 +14734,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45327</v>
+        <v>44865</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14759,13 +14749,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14808,7 +14793,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 50162-2023</t>
+          <t>A 64865-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14818,14 +14803,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45215</v>
+        <v>45282</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14843,7 +14828,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14886,7 +14871,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 30822-2026</t>
+          <t>A 34386-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14900,10 +14885,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46205</v>
+        <v>45139</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14916,7 +14901,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14959,7 +14944,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 30826-2026</t>
+          <t>A 17350-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14973,10 +14958,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46205</v>
+        <v>45035</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14989,7 +14974,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15032,7 +15017,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 39389-2024</t>
+          <t>A 14940-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15046,10 +15031,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45551</v>
+        <v>45398</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15062,7 +15047,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15105,7 +15090,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 17552-2023</t>
+          <t>A 15180-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15119,10 +15104,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45036</v>
+        <v>45016</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15135,7 +15120,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15178,7 +15163,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 34855-2026</t>
+          <t>A 17836-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15192,10 +15177,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46255</v>
+        <v>45037</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15207,13 +15192,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15256,7 +15236,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 34894-2026</t>
+          <t>A 32760-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15270,10 +15250,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46259</v>
+        <v>46241</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15286,7 +15266,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15329,7 +15309,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 34984-2026</t>
+          <t>A 32764-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15343,10 +15323,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46258</v>
+        <v>46241</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15359,7 +15339,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15402,7 +15382,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 34820-2026</t>
+          <t>A 32768-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15416,10 +15396,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46255</v>
+        <v>46241</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15431,13 +15411,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15480,7 +15455,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 34661-2026</t>
+          <t>A 32771-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15494,10 +15469,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46257</v>
+        <v>46241</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15510,7 +15485,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15553,7 +15528,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 34806-2026</t>
+          <t>A 65137-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15567,10 +15542,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46255</v>
+        <v>45288</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15582,13 +15557,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15631,7 +15601,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 40912-2023</t>
+          <t>A 859-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15641,14 +15611,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45173</v>
+        <v>45665</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15660,8 +15630,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15704,7 +15679,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 31252-2026</t>
+          <t>A 52031-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15718,10 +15693,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46218</v>
+        <v>45223</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15733,13 +15708,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15782,7 +15752,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 35568-2026</t>
+          <t>A 43114-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15796,10 +15766,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46262</v>
+        <v>45567</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15817,7 +15787,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>6.9</v>
+        <v>4.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15860,7 +15830,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 35570-2026</t>
+          <t>A 4413-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15874,10 +15844,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46262</v>
+        <v>44589</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15889,13 +15859,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15938,7 +15903,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 18968-2024</t>
+          <t>A 30826-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15952,10 +15917,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45427</v>
+        <v>46205</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15968,7 +15933,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16011,7 +15976,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 53341-2021</t>
+          <t>A 30822-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16025,10 +15990,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44468</v>
+        <v>46205</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16041,7 +16006,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16084,7 +16049,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 36067-2026</t>
+          <t>A 4465-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16098,10 +16063,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46267</v>
+        <v>45327</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16113,13 +16078,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16162,7 +16122,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 36313-2026</t>
+          <t>A 33076-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16172,14 +16132,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46268</v>
+        <v>45126</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16192,7 +16152,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16235,7 +16195,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 17203-2025</t>
+          <t>A 70350-2021</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16249,10 +16209,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45756</v>
+        <v>44536</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16265,7 +16225,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16308,7 +16268,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 48639-2023</t>
+          <t>A 1490-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16318,14 +16278,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45202</v>
+        <v>45670</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16337,8 +16297,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16381,7 +16346,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 37786-2026</t>
+          <t>A 14549-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16395,10 +16360,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46279</v>
+        <v>45741</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16411,7 +16376,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16454,7 +16419,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 27574-2023</t>
+          <t>A 27405-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16468,10 +16433,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45097</v>
+        <v>45474</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16484,7 +16449,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16527,7 +16492,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 4839-2023</t>
+          <t>A 13036-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16541,10 +16506,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44955</v>
+        <v>44643</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16557,7 +16522,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16600,7 +16565,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 14549-2025</t>
+          <t>A 3955-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16614,10 +16579,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45741</v>
+        <v>44587</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16630,7 +16595,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16673,7 +16638,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 30600-2024</t>
+          <t>A 56456-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16687,10 +16652,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45493</v>
+        <v>45625</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16703,7 +16668,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16746,7 +16711,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 24171-2024</t>
+          <t>A 56459-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16760,10 +16725,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45456</v>
+        <v>45625</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16776,7 +16741,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16819,7 +16784,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 64865-2023</t>
+          <t>A 1897-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16833,10 +16798,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45282</v>
+        <v>45671</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16848,13 +16813,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16897,7 +16857,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 41900-2022</t>
+          <t>A 20825-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16911,10 +16871,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44830</v>
+        <v>45058</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16926,13 +16886,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16975,7 +16930,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 38227-2023</t>
+          <t>A 30966-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16989,10 +16944,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45161</v>
+        <v>45113</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17005,7 +16960,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.4</v>
+        <v>7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17048,7 +17003,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 35332-2022</t>
+          <t>A 34661-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17062,10 +17017,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44798</v>
+        <v>46257</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17078,7 +17033,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17121,7 +17076,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 20825-2023</t>
+          <t>A 68507-2021</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17135,10 +17090,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45058</v>
+        <v>44529</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17151,7 +17106,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17194,7 +17149,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 13751-2025</t>
+          <t>A 34806-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17208,10 +17163,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45737</v>
+        <v>46255</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17223,8 +17178,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17267,7 +17227,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 27405-2024</t>
+          <t>A 34820-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17281,10 +17241,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45474</v>
+        <v>46255</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17296,8 +17256,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17340,7 +17305,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 59173-2023</t>
+          <t>A 34855-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17354,10 +17319,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45253</v>
+        <v>46255</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17367,6 +17332,11 @@
       <c r="G219" t="inlineStr">
         <is>
           <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I219" t="n">
@@ -17413,7 +17383,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 3714-2022</t>
+          <t>A 34894-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17427,10 +17397,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44586</v>
+        <v>46259</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17442,13 +17412,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17491,7 +17456,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 18207-2025</t>
+          <t>A 34984-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17505,10 +17470,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45761</v>
+        <v>46258</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17520,13 +17485,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17569,7 +17529,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 18211-2025</t>
+          <t>A 38712-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17583,10 +17543,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45761</v>
+        <v>44814</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17598,13 +17558,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17647,7 +17602,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 642-2024</t>
+          <t>A 35570-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17657,14 +17612,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45299</v>
+        <v>46262</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17682,7 +17637,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17725,7 +17680,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 33076-2023</t>
+          <t>A 48639-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17735,14 +17690,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45126</v>
+        <v>45202</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17755,7 +17710,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17798,7 +17753,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 47386-2024</t>
+          <t>A 31252-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17812,10 +17767,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45587</v>
+        <v>46218</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17827,8 +17782,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17871,7 +17831,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 63927-2021</t>
+          <t>A 35568-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17885,10 +17845,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44509</v>
+        <v>46262</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17906,7 +17866,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2.6</v>
+        <v>6.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17949,7 +17909,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 39603-2022</t>
+          <t>A 50162-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17959,14 +17919,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44818</v>
+        <v>45215</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17978,8 +17938,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18022,7 +17987,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 11843-2024</t>
+          <t>A 43206-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18036,10 +18001,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45376</v>
+        <v>45567</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18051,13 +18016,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18100,7 +18060,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 14940-2024</t>
+          <t>A 15203-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18110,14 +18070,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45398</v>
+        <v>45017</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18129,8 +18089,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18173,7 +18138,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 4413-2022</t>
+          <t>A 15204-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18183,14 +18148,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44589</v>
+        <v>45017</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18202,8 +18167,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18246,7 +18216,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 3605-2024</t>
+          <t>A 36067-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18260,10 +18230,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45320</v>
+        <v>46267</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18275,8 +18245,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18319,7 +18294,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 34386-2023</t>
+          <t>A 8690-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18333,10 +18308,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45139</v>
+        <v>44978</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18349,7 +18324,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18392,7 +18367,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 21546-2023</t>
+          <t>A 36313-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18406,10 +18381,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45063</v>
+        <v>46268</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18422,7 +18397,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18465,7 +18440,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 15864-2022</t>
+          <t>A 61995-2022</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18479,10 +18454,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44664</v>
+        <v>44918</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18494,8 +18469,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18538,7 +18518,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 38712-2022</t>
+          <t>A 4453-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18552,10 +18532,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44814</v>
+        <v>45327</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18567,8 +18547,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18611,7 +18596,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 22432-2023</t>
+          <t>A 49121-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18621,14 +18606,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45070</v>
+        <v>45594</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18640,13 +18625,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I236" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18689,7 +18669,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 56529-2022</t>
+          <t>A 56475-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18703,10 +18683,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44893</v>
+        <v>45625</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18719,7 +18699,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>9</v>
+        <v>1.3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18762,7 +18742,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 43114-2024</t>
+          <t>A 51990-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18776,10 +18756,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45567</v>
+        <v>45607</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18791,13 +18771,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I238" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18840,7 +18815,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 21745-2022</t>
+          <t>A 41598-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18854,10 +18829,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44708</v>
+        <v>45560</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18870,7 +18845,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>9.699999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18913,7 +18888,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 37399-2024</t>
+          <t>A 20852-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18927,10 +18902,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45540</v>
+        <v>45777</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18942,8 +18917,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I240" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18986,7 +18966,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 27080-2022</t>
+          <t>A 61439-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19000,10 +18980,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44741</v>
+        <v>45646</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19016,7 +18996,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19059,7 +19039,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 43206-2024</t>
+          <t>A 37786-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19073,10 +19053,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45567</v>
+        <v>46279</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19089,7 +19069,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19132,7 +19112,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 39436-2022</t>
+          <t>A 21951-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19142,14 +19122,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44818</v>
+        <v>45784</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19161,8 +19141,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I243" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19205,7 +19190,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 13036-2022</t>
+          <t>A 37964-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19215,14 +19200,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44643</v>
+        <v>45544</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19235,7 +19220,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19278,7 +19263,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 52031-2023</t>
+          <t>A 4742-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19292,10 +19277,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45223</v>
+        <v>45688</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19307,8 +19292,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I245" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19351,7 +19341,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 70349-2021</t>
+          <t>A 29566-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19365,10 +19355,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>44536</v>
+        <v>45484</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19381,7 +19371,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.3</v>
+        <v>21.3</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19424,7 +19414,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 70350-2021</t>
+          <t>A 53487-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19438,10 +19428,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>44536</v>
+        <v>45611</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19454,7 +19444,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19497,7 +19487,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 2755-2025</t>
+          <t>A 10414-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19507,14 +19497,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45677</v>
+        <v>45720</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19527,7 +19517,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19570,7 +19560,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 61575-2022</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19580,14 +19570,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44916</v>
+        <v>45708</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19599,13 +19589,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I249" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19648,7 +19633,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 61588-2022</t>
+          <t>A 8173-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19658,14 +19643,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44916</v>
+        <v>45708</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19677,13 +19662,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I250" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19726,7 +19706,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 17350-2023</t>
+          <t>A 20478-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19740,10 +19720,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45035</v>
+        <v>45775</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19755,8 +19735,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I251" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19799,7 +19784,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 20852-2025</t>
+          <t>A 20851-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19816,7 +19801,7 @@
         <v>45777</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19834,7 +19819,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19877,7 +19862,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 51990-2024</t>
+          <t>A 29659-2025</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19887,14 +19872,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45607</v>
+        <v>45825</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19907,7 +19892,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19950,7 +19935,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 41598-2024</t>
+          <t>A 20854-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19964,10 +19949,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45560</v>
+        <v>45777</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19979,8 +19964,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I254" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20023,7 +20013,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 61439-2024</t>
+          <t>A 20853-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20037,10 +20027,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45646</v>
+        <v>45777</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20052,8 +20042,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I255" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20096,7 +20091,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 21951-2025</t>
+          <t>A 30527-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20106,14 +20101,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45784</v>
+        <v>45831</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20125,13 +20120,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I256" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20174,7 +20164,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 37964-2024</t>
+          <t>A 32712-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20184,14 +20174,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45544</v>
+        <v>45839</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20203,8 +20193,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I257" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20247,7 +20242,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 4742-2025</t>
+          <t>A 35909-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20261,10 +20256,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45688</v>
+        <v>45862</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20278,11 +20273,11 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I258" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20325,7 +20320,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 29566-2024</t>
+          <t>A 35899-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20339,10 +20334,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45484</v>
+        <v>45862</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20354,8 +20349,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I259" t="n">
-        <v>21.3</v>
+        <v>1.4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20398,7 +20398,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>S 2321-2023</t>
+          <t>S 2061-2022</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20412,10 +20412,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45105</v>
+        <v>44672</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20471,7 +20471,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>S 4661-2022</t>
+          <t>S 2321-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20481,14 +20481,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>44795</v>
+        <v>45105</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>43.6</v>
+        <v>0.7</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20544,7 +20544,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>S 396-2023</t>
+          <t>S 4661-2022</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20558,10 +20558,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>44959</v>
+        <v>44795</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>78.8</v>
+        <v>43.6</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20617,7 +20617,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>S 2061-2022</t>
+          <t>S 396-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20627,14 +20627,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>44672</v>
+        <v>44959</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.6</v>
+        <v>78.8</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20707,7 +20707,7 @@
         <v>45056</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44959</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44893</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44893</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>45072</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45193</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45386</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44795</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>45688</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45817</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45817</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>46013</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>46013</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46065</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>46154</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>

--- a/Översikt LESSEBO.xlsx
+++ b/Översikt LESSEBO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE278"/>
+  <dimension ref="A1:AE279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45349</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>46035</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45954</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45954</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45954</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45267</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>46176</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45072</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45954</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52539-2025</t>
+          <t>A 1488-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1713,14 +1713,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45954</v>
+        <v>45670</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1732,19 +1732,14 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1774,147 +1769,152 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 1488-2025 artfynd.xlsx", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 1488-2025 karta.png", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 1488-2025 georefererad karta.tif", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 1488-2025 FSC-klagomål.docx", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 1488-2025 FSC-klagomål mail.docx", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 1488-2025 tillsynsbegäran.docx", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 1488-2025 tillsynsbegäran mail.docx", "A 1488-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 52539-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52539-2025 artfynd.xlsx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52539-2025 karta.png", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52539-2025 georefererad karta.tif", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52539-2025 FSC-klagomål.docx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52539-2025 FSC-klagomål mail.docx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52539-2025 tillsynsbegäran.docx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52539-2025 tillsynsbegäran mail.docx", "A 52539-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 1488-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45670</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Korallrot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 1488-2025 artfynd.xlsx", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 1488-2025 karta.png", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 1488-2025 georefererad karta.tif", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 1488-2025 FSC-klagomål.docx", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 1488-2025 FSC-klagomål mail.docx", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 1488-2025 tillsynsbegäran.docx", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 1488-2025 tillsynsbegäran mail.docx", "A 1488-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45625</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44510</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44518</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44865</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>44727</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44586</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44510</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59408-2021</t>
+          <t>A 45095-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44491</v>
+        <v>44842</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3189,8 +3189,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3233,7 +3238,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45095-2022</t>
+          <t>A 59408-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3247,10 +3252,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44842</v>
+        <v>44491</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3262,13 +3267,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27080-2022</t>
+          <t>A 68513-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44741</v>
+        <v>44529</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 63330-2021</t>
+          <t>A 19495-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44508</v>
+        <v>44693</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 68513-2021</t>
+          <t>A 63330-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44529</v>
+        <v>44508</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>44522</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 11843-2024</t>
+          <t>A 27794-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45376</v>
+        <v>44743</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3632,13 +3632,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3681,7 +3676,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 2755-2025</t>
+          <t>A 51006-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3691,14 +3686,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45677</v>
+        <v>44460</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3711,7 +3706,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3754,7 +3749,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21745-2022</t>
+          <t>A 33240-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3768,10 +3763,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44708</v>
+        <v>45518</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3784,7 +3779,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>9.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3827,7 +3822,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 39603-2022</t>
+          <t>A 56456-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3841,10 +3836,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44818</v>
+        <v>45625</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3857,7 +3852,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3900,7 +3895,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27794-2022</t>
+          <t>A 56459-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3914,10 +3909,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44743</v>
+        <v>45625</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3930,7 +3925,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3968,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 19495-2022</t>
+          <t>A 68507-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3982,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44693</v>
+        <v>44529</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4046,7 +4041,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 51189-2023</t>
+          <t>A 24478-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45219</v>
+        <v>45459</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4076,7 +4071,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 27191-2022</t>
+          <t>A 1367-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44741</v>
+        <v>44936</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4144,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 51006-2021</t>
+          <t>A 30966-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44460</v>
+        <v>45113</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4260,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 17203-2025</t>
+          <t>A 59320-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4274,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45756</v>
+        <v>45637</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4294,8 +4289,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40912-2023</t>
+          <t>A 15203-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4348,14 +4348,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45173</v>
+        <v>45017</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4367,8 +4367,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4416,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27713-2022</t>
+          <t>A 15204-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4421,14 +4426,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44743</v>
+        <v>45017</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4440,8 +4445,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4494,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59173-2023</t>
+          <t>A 8655-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4508,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45253</v>
+        <v>45710</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4514,7 +4524,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4567,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3876-2024</t>
+          <t>A 27713-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4571,10 +4581,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45322</v>
+        <v>44743</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4587,7 +4597,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4640,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3239-2025</t>
+          <t>A 43453-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4654,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45679</v>
+        <v>45568</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4659,13 +4669,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4708,7 +4713,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10047-2024</t>
+          <t>A 859-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4718,14 +4723,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45364</v>
+        <v>45665</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4739,11 +4744,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4786,7 +4791,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54541-2023</t>
+          <t>A 45838-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4796,14 +4801,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45233</v>
+        <v>44846</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4815,13 +4820,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3875-2024</t>
+          <t>A 10414-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45322</v>
+        <v>45720</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4937,7 +4937,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24171-2024</t>
+          <t>A 53487-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45456</v>
+        <v>45611</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5010,7 +5010,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24478-2024</t>
+          <t>A 8173-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5020,14 +5020,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45459</v>
+        <v>45708</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 15180-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5093,14 +5093,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45708</v>
+        <v>45016</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5156,7 +5156,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18207-2025</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5166,14 +5166,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45761</v>
+        <v>45708</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5185,13 +5185,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5234,7 +5229,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18211-2025</t>
+          <t>A 1022-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5248,10 +5243,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45761</v>
+        <v>46030</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5263,13 +5258,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5312,7 +5302,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 41905-2022</t>
+          <t>A 1016-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5326,10 +5316,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44830</v>
+        <v>46030</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5341,13 +5331,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5390,7 +5375,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 39436-2022</t>
+          <t>A 10047-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5404,10 +5389,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44818</v>
+        <v>45364</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5419,8 +5404,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5463,7 +5453,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 64635-2023</t>
+          <t>A 39884-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5477,10 +5467,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45281</v>
+        <v>45891</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5493,7 +5483,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5536,7 +5526,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 57519-2022</t>
+          <t>A 39549-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5550,10 +5540,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44896</v>
+        <v>45890</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5566,7 +5556,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5609,7 +5599,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20541-2024</t>
+          <t>A 39750-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5623,10 +5613,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45436</v>
+        <v>45891</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5639,7 +5629,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5682,7 +5672,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 39549-2025</t>
+          <t>A 20478-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5696,10 +5686,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45890</v>
+        <v>45775</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5711,8 +5701,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5755,7 +5750,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18968-2024</t>
+          <t>A 29659-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5765,14 +5760,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45427</v>
+        <v>45825</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5785,7 +5780,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5828,7 +5823,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39750-2025</t>
+          <t>A 20851-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5842,10 +5837,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45891</v>
+        <v>45777</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5857,8 +5852,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5901,7 +5901,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39884-2025</t>
+          <t>A 7957-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5915,10 +5915,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45891</v>
+        <v>44973</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5974,7 +5974,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17204-2025</t>
+          <t>A 35904-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45756</v>
+        <v>45862</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6003,8 +6003,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6047,7 +6052,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35904-2025</t>
+          <t>A 20854-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6061,10 +6066,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45862</v>
+        <v>45777</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6082,7 +6087,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6125,7 +6130,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13347-2026</t>
+          <t>A 20853-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6139,10 +6144,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46094</v>
+        <v>45777</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6156,11 +6161,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6203,7 +6208,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56529-2022</t>
+          <t>A 30527-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6217,10 +6222,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44893</v>
+        <v>45831</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6233,7 +6238,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>9</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6276,7 +6281,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38227-2023</t>
+          <t>A 17836-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6290,10 +6295,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45161</v>
+        <v>45037</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6349,7 +6354,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 43809-2025</t>
+          <t>A 30914-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6363,10 +6368,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45912</v>
+        <v>44767</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6379,7 +6384,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6422,7 +6427,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3714-2022</t>
+          <t>A 43809-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6436,10 +6441,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44586</v>
+        <v>45912</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6451,13 +6456,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 35332-2022</t>
+          <t>A 32712-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44798</v>
+        <v>45839</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6529,8 +6529,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6573,7 +6578,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44904-2025</t>
+          <t>A 19501-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6587,10 +6592,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45918</v>
+        <v>44693</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6603,7 +6608,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6646,7 +6651,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33240-2024</t>
+          <t>A 44904-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6660,10 +6665,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45518</v>
+        <v>45918</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6676,7 +6681,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>7.4</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6736,7 +6741,7 @@
         <v>45918</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6792,7 +6797,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39389-2024</t>
+          <t>A 50154-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6806,10 +6811,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45551</v>
+        <v>44865</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6822,7 +6827,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6865,7 +6870,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60358-2022</t>
+          <t>A 29767-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6879,10 +6884,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44910</v>
+        <v>45107</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6895,7 +6900,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6938,7 +6943,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56467-2024</t>
+          <t>A 35909-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6952,10 +6957,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45625</v>
+        <v>45862</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6967,8 +6972,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7011,7 +7021,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61575-2022</t>
+          <t>A 35899-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7025,10 +7035,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44916</v>
+        <v>45862</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7042,11 +7052,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7089,7 +7099,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61588-2022</t>
+          <t>A 41905-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7103,10 +7113,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44916</v>
+        <v>44830</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7120,11 +7130,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7167,7 +7177,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 43453-2024</t>
+          <t>A 48429-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7181,10 +7191,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45568</v>
+        <v>45934</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7197,7 +7207,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7240,7 +7250,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 18464-2026</t>
+          <t>A 48433-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7254,10 +7264,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46127</v>
+        <v>45934</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7269,13 +7279,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>14.2</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7318,7 +7323,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 18466-2026</t>
+          <t>A 17729-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7332,10 +7337,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46127</v>
+        <v>45758</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7353,7 +7358,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7.9</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7396,7 +7401,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 18625-2026</t>
+          <t>A 3955-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7410,10 +7415,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46127</v>
+        <v>44587</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7426,7 +7431,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7469,7 +7474,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47396-2024</t>
+          <t>A 4236-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7483,10 +7488,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45587</v>
+        <v>46044</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7499,7 +7504,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7542,7 +7547,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59320-2024</t>
+          <t>A 4229-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7556,10 +7561,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45637</v>
+        <v>46044</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7571,13 +7576,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7620,7 +7620,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 48429-2025</t>
+          <t>A 49298-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45934</v>
+        <v>45938</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7693,7 +7693,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 48433-2025</t>
+          <t>A 20443-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45934</v>
+        <v>45775</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7722,8 +7722,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7766,7 +7771,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 17729-2025</t>
+          <t>A 60358-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7780,10 +7785,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45758</v>
+        <v>44910</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7795,13 +7800,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7844,7 +7844,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20443-2025</t>
+          <t>A 17517-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7858,10 +7858,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45775</v>
+        <v>45036</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7873,13 +7873,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7922,7 +7917,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 49298-2025</t>
+          <t>A 20541-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7936,10 +7931,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45938</v>
+        <v>45436</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7952,7 +7947,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7995,7 +7990,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 7957-2023</t>
+          <t>A 64635-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8009,10 +8004,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44973</v>
+        <v>45281</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8025,7 +8020,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8068,7 +8063,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21917-2025</t>
+          <t>A 14584-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8082,10 +8077,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45784</v>
+        <v>45013</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8098,7 +8093,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8141,7 +8136,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20855-2025</t>
+          <t>A 52031-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8155,10 +8150,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45777</v>
+        <v>45952</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8170,13 +8165,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8219,7 +8209,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 47386-2024</t>
+          <t>A 73140-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8233,10 +8223,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45587</v>
+        <v>44550</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8249,7 +8239,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8292,7 +8282,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1894-2025</t>
+          <t>A 30405-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8306,10 +8296,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45671</v>
+        <v>45111</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8322,7 +8312,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8365,7 +8355,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 47693-2025</t>
+          <t>A 52537-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8379,10 +8369,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45931</v>
+        <v>45954</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8394,8 +8384,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8438,7 +8433,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20056-2025</t>
+          <t>A 52531-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8452,10 +8447,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45772</v>
+        <v>45954</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8467,8 +8462,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8511,7 +8511,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 37399-2024</t>
+          <t>A 52532-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45540</v>
+        <v>45954</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8540,8 +8540,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8584,7 +8589,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 52031-2025</t>
+          <t>A 52546-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8598,10 +8603,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8613,8 +8618,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8657,7 +8667,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 52537-2025</t>
+          <t>A 52534-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8674,7 +8684,7 @@
         <v>45954</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8692,7 +8702,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8735,7 +8745,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 52531-2025</t>
+          <t>A 53122-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8749,10 +8759,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8764,13 +8774,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8813,7 +8818,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 52532-2025</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8823,14 +8828,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45954</v>
+        <v>45708</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8842,13 +8847,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8891,7 +8891,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52546-2025</t>
+          <t>A 3239-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45954</v>
+        <v>45679</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8922,11 +8922,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8969,7 +8969,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 51175-2023</t>
+          <t>A 52525-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8983,10 +8983,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45219</v>
+        <v>45225</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9042,7 +9042,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 52534-2025</t>
+          <t>A 51191-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9056,10 +9056,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45954</v>
+        <v>45219</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9071,13 +9071,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9120,7 +9115,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 53122-2025</t>
+          <t>A 8438-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9134,10 +9129,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45958</v>
+        <v>46065</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9149,8 +9144,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9193,7 +9193,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 14584-2023</t>
+          <t>A 56467-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9207,10 +9207,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45013</v>
+        <v>45625</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9266,7 +9266,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 36895-2025</t>
+          <t>A 49295-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45874</v>
+        <v>45938</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9339,7 +9339,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 49295-2025</t>
+          <t>A 3876-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9353,10 +9353,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45938</v>
+        <v>45322</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>7.4</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9412,7 +9412,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 29767-2023</t>
+          <t>A 1490-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9422,14 +9422,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45107</v>
+        <v>45670</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9441,8 +9441,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9485,7 +9490,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 19501-2022</t>
+          <t>A 54541-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9495,14 +9500,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44693</v>
+        <v>45233</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9514,8 +9519,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9558,7 +9568,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 70349-2021</t>
+          <t>A 10189-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9572,10 +9582,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44536</v>
+        <v>46076</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9588,7 +9598,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9631,7 +9641,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 51191-2023</t>
+          <t>A 51189-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9648,7 +9658,7 @@
         <v>45219</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9661,7 +9671,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9704,7 +9714,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 56471-2024</t>
+          <t>A 10286-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9718,10 +9728,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45625</v>
+        <v>46076</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9734,7 +9744,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9777,7 +9787,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 38303-2025</t>
+          <t>A 10185-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9791,10 +9801,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45883</v>
+        <v>46076</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9807,7 +9817,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9850,7 +9860,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 52525-2023</t>
+          <t>A 8690-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9864,10 +9874,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45225</v>
+        <v>44978</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9880,7 +9890,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9923,7 +9933,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 17517-2023</t>
+          <t>A 57519-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9937,10 +9947,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45036</v>
+        <v>44896</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9953,7 +9963,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9996,7 +10006,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 1367-2023</t>
+          <t>A 56475-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10010,10 +10020,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44936</v>
+        <v>45625</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10026,7 +10036,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10069,7 +10079,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4107-2025</t>
+          <t>A 65137-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10083,10 +10093,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45684</v>
+        <v>45288</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10099,7 +10109,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10142,7 +10152,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 35894-2025</t>
+          <t>A 61638-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10156,10 +10166,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45862</v>
+        <v>46002</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10171,13 +10181,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10220,7 +10225,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 21311-2026</t>
+          <t>A 61641-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10234,10 +10239,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46147</v>
+        <v>46002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10247,6 +10252,11 @@
       <c r="G124" t="inlineStr">
         <is>
           <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -10293,7 +10303,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61638-2025</t>
+          <t>A 20824-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10307,10 +10317,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46002</v>
+        <v>45058</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10323,7 +10333,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10366,7 +10376,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 61641-2025</t>
+          <t>A 17204-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10380,10 +10390,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46002</v>
+        <v>45756</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10395,13 +10405,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10444,7 +10449,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 22318-2026</t>
+          <t>A 62728-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10458,10 +10463,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46154</v>
+        <v>46008</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10473,8 +10478,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10517,7 +10527,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 30914-2022</t>
+          <t>A 27191-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10531,10 +10541,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44767</v>
+        <v>44741</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10547,7 +10557,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10590,7 +10600,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 63927-2021</t>
+          <t>A 49121-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10604,10 +10614,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44509</v>
+        <v>45594</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10619,13 +10629,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10668,7 +10673,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 22423-2026</t>
+          <t>A 13347-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10678,14 +10683,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46154</v>
+        <v>46094</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10697,8 +10702,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10741,7 +10751,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 62728-2025</t>
+          <t>A 47396-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10755,10 +10765,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46008</v>
+        <v>45587</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10770,13 +10780,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10819,7 +10824,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 8655-2025</t>
+          <t>A 1897-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10833,10 +10838,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45710</v>
+        <v>45671</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10849,7 +10854,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10892,7 +10897,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 22764-2026</t>
+          <t>A 51175-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10906,10 +10911,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46157</v>
+        <v>45219</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10921,13 +10926,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10970,7 +10970,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 22768-2026</t>
+          <t>A 61995-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10984,10 +10984,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46157</v>
+        <v>44918</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11001,11 +11001,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11048,7 +11048,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 22770-2026</t>
+          <t>A 4107-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11062,10 +11062,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46157</v>
+        <v>45684</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11077,13 +11077,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11126,7 +11121,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 20431-2025</t>
+          <t>A 3875-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11140,10 +11135,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45775</v>
+        <v>45322</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11155,13 +11150,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11204,7 +11194,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 22723-2026</t>
+          <t>A 50892-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11218,10 +11208,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46157</v>
+        <v>44867</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11233,13 +11223,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11282,7 +11267,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 20681-2025</t>
+          <t>A 47402-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11296,10 +11281,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45776</v>
+        <v>45587</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11311,13 +11296,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11360,7 +11340,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 22718-2026</t>
+          <t>A 18625-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11374,10 +11354,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46157</v>
+        <v>46127</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11389,13 +11369,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11438,7 +11413,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 22766-2026</t>
+          <t>A 18464-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11452,10 +11427,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46157</v>
+        <v>46127</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11473,7 +11448,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>14.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11516,7 +11491,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 22756-2026</t>
+          <t>A 18466-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11530,10 +11505,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46157</v>
+        <v>46127</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11551,7 +11526,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11594,7 +11569,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 22758-2026</t>
+          <t>A 4465-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11608,10 +11583,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46157</v>
+        <v>45327</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11623,13 +11598,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11672,7 +11642,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 20435-2025</t>
+          <t>A 4453-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11686,10 +11656,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45775</v>
+        <v>45327</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11703,11 +11673,11 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11750,7 +11720,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 20485-2025</t>
+          <t>A 50162-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11760,14 +11730,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45775</v>
+        <v>45215</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11785,7 +11755,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11828,7 +11798,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 22719-2026</t>
+          <t>A 20056-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11842,10 +11812,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46157</v>
+        <v>45772</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11857,13 +11827,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11906,7 +11871,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 22720-2026</t>
+          <t>A 39389-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11920,10 +11885,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46157</v>
+        <v>45551</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11935,13 +11900,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11984,7 +11944,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 41900-2022</t>
+          <t>A 36895-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11998,10 +11958,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44830</v>
+        <v>45874</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12013,13 +11973,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12062,7 +12017,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 22432-2023</t>
+          <t>A 38303-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12072,14 +12027,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45070</v>
+        <v>45883</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12091,13 +12046,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12140,7 +12090,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 73140-2021</t>
+          <t>A 17552-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12154,10 +12104,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44550</v>
+        <v>45036</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12170,7 +12120,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12213,7 +12163,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 1022-2026</t>
+          <t>A 56471-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12227,10 +12177,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46030</v>
+        <v>45625</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12243,7 +12193,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12286,7 +12236,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 17552-2023</t>
+          <t>A 40912-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12300,10 +12250,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45036</v>
+        <v>45173</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12316,7 +12266,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12359,7 +12309,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 1016-2026</t>
+          <t>A 21917-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12373,10 +12323,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46030</v>
+        <v>45784</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12389,7 +12339,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12432,7 +12382,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 13751-2025</t>
+          <t>A 18968-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12446,10 +12396,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45737</v>
+        <v>45427</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12462,7 +12412,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12505,7 +12455,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 30405-2023</t>
+          <t>A 53341-2021</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12519,10 +12469,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45111</v>
+        <v>44468</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12535,7 +12485,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12578,7 +12528,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24275-2026</t>
+          <t>A 1894-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12592,10 +12542,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46169</v>
+        <v>45671</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12608,7 +12558,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12651,7 +12601,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 27574-2023</t>
+          <t>A 20855-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12665,10 +12615,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45097</v>
+        <v>45777</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12680,8 +12630,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12724,7 +12679,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 24271-2026</t>
+          <t>A 17203-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12738,10 +12693,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46169</v>
+        <v>45756</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12754,7 +12709,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12797,7 +12752,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 24272-2026</t>
+          <t>A 48639-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12811,10 +12766,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46169</v>
+        <v>45202</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12827,7 +12782,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12870,7 +12825,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 24269-2026</t>
+          <t>A 47693-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12884,10 +12839,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46169</v>
+        <v>45931</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12900,7 +12855,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12943,7 +12898,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 53341-2021</t>
+          <t>A 35894-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12957,10 +12912,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44468</v>
+        <v>45862</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12972,8 +12927,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13016,7 +12976,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 4839-2023</t>
+          <t>A 21311-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13030,10 +12990,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44955</v>
+        <v>46147</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13046,7 +13006,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13089,7 +13049,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 25169-2026</t>
+          <t>A 27574-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13103,10 +13063,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46175</v>
+        <v>45097</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13119,7 +13079,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13162,7 +13122,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 4229-2026</t>
+          <t>A 4839-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13176,10 +13136,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46044</v>
+        <v>44955</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13192,7 +13152,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>9.699999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13235,7 +13195,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 50892-2022</t>
+          <t>A 14549-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13249,10 +13209,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44867</v>
+        <v>45741</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13265,7 +13225,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13308,7 +13268,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 4236-2026</t>
+          <t>A 30600-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13322,10 +13282,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46044</v>
+        <v>45493</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13338,7 +13298,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13381,7 +13341,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 3605-2024</t>
+          <t>A 22318-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13395,10 +13355,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45320</v>
+        <v>46154</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13411,7 +13371,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13454,7 +13414,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 45838-2022</t>
+          <t>A 24171-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13468,10 +13428,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44846</v>
+        <v>45456</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13484,7 +13444,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13527,7 +13487,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 20824-2023</t>
+          <t>A 22423-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13537,14 +13497,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45058</v>
+        <v>46154</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13600,7 +13560,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 30600-2024</t>
+          <t>A 22718-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13614,10 +13574,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45493</v>
+        <v>46157</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13629,8 +13589,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13673,7 +13638,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 15864-2022</t>
+          <t>A 64865-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13687,10 +13652,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44664</v>
+        <v>45282</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13702,8 +13667,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13746,7 +13716,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 642-2024</t>
+          <t>A 22756-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13756,14 +13726,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45299</v>
+        <v>46157</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13781,7 +13751,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13824,7 +13794,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 21546-2023</t>
+          <t>A 22758-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13838,10 +13808,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45063</v>
+        <v>46157</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13853,8 +13823,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13897,7 +13872,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 8438-2026</t>
+          <t>A 22766-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13911,10 +13886,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46065</v>
+        <v>46157</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13932,7 +13907,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13975,7 +13950,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 59321-2024</t>
+          <t>A 22719-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13989,10 +13964,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45637</v>
+        <v>46157</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14010,7 +13985,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14053,7 +14028,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 47402-2024</t>
+          <t>A 22720-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14067,10 +14042,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45587</v>
+        <v>46157</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14082,8 +14057,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14126,7 +14106,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 20441-2025</t>
+          <t>A 22764-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14140,10 +14120,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45775</v>
+        <v>46157</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14161,7 +14141,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14204,7 +14184,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 10286-2026</t>
+          <t>A 22768-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14218,10 +14198,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46076</v>
+        <v>46157</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14233,8 +14213,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14277,7 +14262,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 14551-2025</t>
+          <t>A 22770-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14291,10 +14276,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45741</v>
+        <v>46157</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14306,8 +14291,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14350,7 +14340,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 10185-2026</t>
+          <t>A 22723-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14364,10 +14354,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46076</v>
+        <v>46157</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14379,8 +14369,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14423,7 +14418,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 10189-2026</t>
+          <t>A 41900-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14437,10 +14432,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46076</v>
+        <v>44830</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14452,8 +14447,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14496,7 +14496,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 27870-2026</t>
+          <t>A 38227-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46191</v>
+        <v>45161</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14569,7 +14569,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 27873-2026</t>
+          <t>A 20485-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46191</v>
+        <v>45775</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14598,8 +14598,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14642,7 +14647,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 20480-2025</t>
+          <t>A 20431-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14659,7 +14664,7 @@
         <v>45775</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14677,7 +14682,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14720,7 +14725,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 50154-2022</t>
+          <t>A 20435-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14734,10 +14739,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44865</v>
+        <v>45775</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14749,8 +14754,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14793,7 +14803,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 64865-2023</t>
+          <t>A 20681-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14807,10 +14817,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45282</v>
+        <v>45776</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14828,7 +14838,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14871,7 +14881,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 34386-2023</t>
+          <t>A 35332-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14885,10 +14895,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45139</v>
+        <v>44798</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14901,7 +14911,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14944,7 +14954,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 17350-2023</t>
+          <t>A 20825-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14958,10 +14968,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45035</v>
+        <v>45058</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14974,7 +14984,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15017,7 +15027,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 14940-2024</t>
+          <t>A 24275-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15031,10 +15041,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45398</v>
+        <v>46169</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15047,7 +15057,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15090,7 +15100,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 15180-2023</t>
+          <t>A 24271-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15104,10 +15114,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45016</v>
+        <v>46169</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15120,7 +15130,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15163,7 +15173,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 17836-2023</t>
+          <t>A 24272-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15177,10 +15187,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45037</v>
+        <v>46169</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15193,7 +15203,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15236,7 +15246,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 32760-2026</t>
+          <t>A 13751-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15250,10 +15260,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46241</v>
+        <v>45737</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15266,7 +15276,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15309,7 +15319,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 32764-2026</t>
+          <t>A 24269-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15323,10 +15333,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46241</v>
+        <v>46169</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15339,7 +15349,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15382,7 +15392,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 32768-2026</t>
+          <t>A 27405-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15396,10 +15406,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46241</v>
+        <v>45474</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15412,7 +15422,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15455,7 +15465,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 32771-2026</t>
+          <t>A 59173-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15469,10 +15479,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46241</v>
+        <v>45253</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15485,7 +15495,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15528,7 +15538,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 65137-2023</t>
+          <t>A 3714-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15542,10 +15552,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45288</v>
+        <v>44586</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15557,8 +15567,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15601,7 +15616,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 859-2025</t>
+          <t>A 25169-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15611,14 +15626,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45665</v>
+        <v>46175</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15630,13 +15645,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15679,7 +15689,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 52031-2023</t>
+          <t>A 18207-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15693,10 +15703,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45223</v>
+        <v>45761</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15708,8 +15718,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15752,7 +15767,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 43114-2024</t>
+          <t>A 18211-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15766,10 +15781,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45567</v>
+        <v>45761</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15787,7 +15802,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15830,7 +15845,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 4413-2022</t>
+          <t>A 642-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15840,14 +15855,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44589</v>
+        <v>45299</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15859,8 +15874,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15903,7 +15923,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 30826-2026</t>
+          <t>A 33076-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15913,14 +15933,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46205</v>
+        <v>45126</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15933,7 +15953,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15976,7 +15996,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 30822-2026</t>
+          <t>A 20441-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15990,10 +16010,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46205</v>
+        <v>45775</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16005,8 +16025,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16049,7 +16074,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 4465-2024</t>
+          <t>A 47386-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16063,10 +16088,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45327</v>
+        <v>45587</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16079,7 +16104,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16122,7 +16147,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 33076-2023</t>
+          <t>A 63927-2021</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16132,14 +16157,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45126</v>
+        <v>44509</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16151,8 +16176,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16195,7 +16225,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 70350-2021</t>
+          <t>A 59321-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16209,10 +16239,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44536</v>
+        <v>45637</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16224,8 +16254,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16268,7 +16303,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 1490-2025</t>
+          <t>A 14551-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16278,14 +16313,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45670</v>
+        <v>45741</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16297,13 +16332,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16346,7 +16376,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 14549-2025</t>
+          <t>A 39603-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16360,10 +16390,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45741</v>
+        <v>44818</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16376,7 +16406,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16419,7 +16449,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 27405-2024</t>
+          <t>A 27870-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16433,10 +16463,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45474</v>
+        <v>46191</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16449,7 +16479,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16492,7 +16522,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 13036-2022</t>
+          <t>A 27873-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16506,10 +16536,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44643</v>
+        <v>46191</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16522,7 +16552,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16565,7 +16595,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 3955-2022</t>
+          <t>A 20480-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16579,10 +16609,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44587</v>
+        <v>45775</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16594,8 +16624,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16638,7 +16673,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 56456-2024</t>
+          <t>A 11843-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16652,10 +16687,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45625</v>
+        <v>45376</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16667,8 +16702,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16711,7 +16751,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 56459-2024</t>
+          <t>A 14940-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16725,10 +16765,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45625</v>
+        <v>45398</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16741,7 +16781,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16784,7 +16824,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 1897-2025</t>
+          <t>A 32771-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16798,10 +16838,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45671</v>
+        <v>46241</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16814,7 +16854,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16857,7 +16897,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 20825-2023</t>
+          <t>A 32760-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16871,10 +16911,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45058</v>
+        <v>46241</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16887,7 +16927,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16930,7 +16970,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 30966-2023</t>
+          <t>A 32764-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16944,10 +16984,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45113</v>
+        <v>46241</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16960,7 +17000,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17003,7 +17043,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 34661-2026</t>
+          <t>A 32768-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17017,10 +17057,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46257</v>
+        <v>46241</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17033,7 +17073,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17076,7 +17116,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 68507-2021</t>
+          <t>A 4413-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17090,10 +17130,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44529</v>
+        <v>44589</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17106,7 +17146,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17149,7 +17189,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 34806-2026</t>
+          <t>A 30822-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17163,10 +17203,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46255</v>
+        <v>46205</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17178,13 +17218,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17227,7 +17262,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 34820-2026</t>
+          <t>A 30826-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17241,10 +17276,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46255</v>
+        <v>46205</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17256,13 +17291,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17305,7 +17335,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 34855-2026</t>
+          <t>A 3605-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17319,10 +17349,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46255</v>
+        <v>45320</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17334,13 +17364,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17383,7 +17408,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 34894-2026</t>
+          <t>A 34386-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17397,10 +17422,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46259</v>
+        <v>45139</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17413,7 +17438,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17456,7 +17481,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 34984-2026</t>
+          <t>A 21546-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17470,10 +17495,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46258</v>
+        <v>45063</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17486,7 +17511,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17529,7 +17554,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 38712-2022</t>
+          <t>A 15864-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17543,10 +17568,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44814</v>
+        <v>44664</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17559,7 +17584,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17602,7 +17627,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 35570-2026</t>
+          <t>A 38712-2022</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17616,10 +17641,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46262</v>
+        <v>44814</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17631,13 +17656,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17680,7 +17700,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 48639-2023</t>
+          <t>A 34855-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17694,10 +17714,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45202</v>
+        <v>46255</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17709,8 +17729,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17753,7 +17778,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 31252-2026</t>
+          <t>A 22432-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17763,14 +17788,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46218</v>
+        <v>45070</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17788,7 +17813,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17831,7 +17856,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 35568-2026</t>
+          <t>A 56529-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17845,10 +17870,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46262</v>
+        <v>44893</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17860,13 +17885,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>6.9</v>
+        <v>9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17909,7 +17929,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 50162-2023</t>
+          <t>A 34894-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17919,14 +17939,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45215</v>
+        <v>46259</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17938,13 +17958,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17987,7 +18002,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 43206-2024</t>
+          <t>A 34984-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18001,10 +18016,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45567</v>
+        <v>46258</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18017,7 +18032,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18060,7 +18075,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 15203-2023</t>
+          <t>A 34820-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18070,14 +18085,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45017</v>
+        <v>46255</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18091,11 +18106,11 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18138,7 +18153,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 15204-2023</t>
+          <t>A 43114-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18148,14 +18163,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45017</v>
+        <v>45567</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18173,7 +18188,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.3</v>
+        <v>4.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18216,7 +18231,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 36067-2026</t>
+          <t>A 34661-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18230,10 +18245,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46267</v>
+        <v>46257</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18245,13 +18260,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18294,7 +18304,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 8690-2023</t>
+          <t>A 34806-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18308,10 +18318,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44978</v>
+        <v>46255</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18323,8 +18333,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18367,7 +18382,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 36313-2026</t>
+          <t>A 31252-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18381,10 +18396,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46268</v>
+        <v>46218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18396,8 +18411,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18440,7 +18460,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 61995-2022</t>
+          <t>A 21745-2022</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18454,10 +18474,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44918</v>
+        <v>44708</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18469,13 +18489,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18518,7 +18533,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 4453-2024</t>
+          <t>A 37399-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18532,10 +18547,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45327</v>
+        <v>45540</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18547,13 +18562,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I235" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18596,7 +18606,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 49121-2024</t>
+          <t>A 35568-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18610,10 +18620,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45594</v>
+        <v>46262</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18625,8 +18635,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I236" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18669,7 +18684,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 56475-2024</t>
+          <t>A 27080-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18683,10 +18698,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45625</v>
+        <v>44741</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18699,7 +18714,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18742,7 +18757,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 51990-2024</t>
+          <t>A 35570-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18756,10 +18771,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45607</v>
+        <v>46262</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18771,8 +18786,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18815,7 +18835,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 41598-2024</t>
+          <t>A 36067-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18829,10 +18849,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45560</v>
+        <v>46267</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18844,8 +18864,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I239" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18888,7 +18913,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 20852-2025</t>
+          <t>A 43206-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18902,10 +18927,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45777</v>
+        <v>45567</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18917,13 +18942,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18966,7 +18986,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 61439-2024</t>
+          <t>A 36313-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18980,10 +19000,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45646</v>
+        <v>46268</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18996,7 +19016,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19039,7 +19059,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 37786-2026</t>
+          <t>A 39436-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19053,10 +19073,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46279</v>
+        <v>44818</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19069,7 +19089,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19112,7 +19132,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 21951-2025</t>
+          <t>A 13036-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19122,14 +19142,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45784</v>
+        <v>44643</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19141,13 +19161,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19190,7 +19205,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 37964-2024</t>
+          <t>A 52031-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19200,14 +19215,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45544</v>
+        <v>45223</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19220,7 +19235,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19263,7 +19278,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 4742-2025</t>
+          <t>A 70349-2021</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19277,10 +19292,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45688</v>
+        <v>44536</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19292,13 +19307,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I245" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19341,7 +19351,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 29566-2024</t>
+          <t>A 70350-2021</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19355,10 +19365,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45484</v>
+        <v>44536</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19371,7 +19381,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>21.3</v>
+        <v>0.8</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19414,7 +19424,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 53487-2024</t>
+          <t>A 2755-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19424,14 +19434,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45611</v>
+        <v>45677</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19444,7 +19454,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19487,7 +19497,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 10414-2025</t>
+          <t>A 61575-2022</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19501,10 +19511,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45720</v>
+        <v>44916</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19516,8 +19526,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I248" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19560,7 +19575,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 61588-2022</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19570,14 +19585,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45708</v>
+        <v>44916</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19589,8 +19604,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I249" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19633,7 +19653,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 8173-2025</t>
+          <t>A 37786-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19643,14 +19663,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45708</v>
+        <v>46279</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19663,7 +19683,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19706,7 +19726,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 20478-2025</t>
+          <t>A 17350-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19720,10 +19740,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45775</v>
+        <v>45035</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19735,13 +19755,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I251" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19784,7 +19799,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 20851-2025</t>
+          <t>A 20852-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19801,7 +19816,7 @@
         <v>45777</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19819,7 +19834,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19862,7 +19877,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 29659-2025</t>
+          <t>A 51990-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19872,14 +19887,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45825</v>
+        <v>45607</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19892,7 +19907,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19935,7 +19950,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 20854-2025</t>
+          <t>A 41598-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19949,10 +19964,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45777</v>
+        <v>45560</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19964,13 +19979,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I254" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20013,7 +20023,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 20853-2025</t>
+          <t>A 61439-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20027,10 +20037,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45777</v>
+        <v>45646</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20042,13 +20052,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I255" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20091,7 +20096,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 30527-2025</t>
+          <t>A 38098-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20105,10 +20110,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45831</v>
+        <v>46281</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20121,7 +20126,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20164,7 +20169,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 32712-2025</t>
+          <t>A 21951-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20174,14 +20179,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45839</v>
+        <v>45784</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20195,11 +20200,11 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I257" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20242,7 +20247,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 35909-2025</t>
+          <t>A 37964-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20252,14 +20257,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45862</v>
+        <v>45544</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20271,13 +20276,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I258" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20320,7 +20320,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 35899-2025</t>
+          <t>A 4742-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20334,10 +20334,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45862</v>
+        <v>45688</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20351,11 +20351,11 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I259" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20398,24 +20398,24 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>S 2061-2022</t>
+          <t>A 29566-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>44672</v>
+        <v>45484</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.6</v>
+        <v>21.3</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20488,7 +20488,7 @@
         <v>45105</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>44795</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>44959</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>S 1592-2023</t>
+          <t>S 2061-2022</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20700,14 +20700,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45056</v>
+        <v>44672</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>19.5</v>
+        <v>1.6</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20763,7 +20763,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>S 366-2023</t>
+          <t>S 1592-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20777,10 +20777,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>44959</v>
+        <v>45056</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>35.8</v>
+        <v>19.5</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20836,7 +20836,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>S 6799-2022</t>
+          <t>S 366-2023</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20850,10 +20850,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>44893</v>
+        <v>44959</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>28.2</v>
+        <v>35.8</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20909,7 +20909,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>S 6798-2022</t>
+          <t>S 6799-2022</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20926,7 +20926,7 @@
         <v>44893</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>149.8</v>
+        <v>28.2</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20982,7 +20982,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>S 1806-2023</t>
+          <t>S 6798-2022</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20996,10 +20996,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45072</v>
+        <v>44893</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>61.9</v>
+        <v>149.8</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21055,7 +21055,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>S 3254-2023</t>
+          <t>S 1806-2023</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21069,10 +21069,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45193</v>
+        <v>45072</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>88.59999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21128,7 +21128,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>S 1019-2024</t>
+          <t>S 3254-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21142,10 +21142,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45386</v>
+        <v>45193</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>14.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21201,7 +21201,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>S 4655-2022</t>
+          <t>S 1019-2024</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21215,10 +21215,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>44795</v>
+        <v>45386</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>19.1</v>
+        <v>14.5</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>S 312-2025</t>
+          <t>S 4655-2022</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21288,10 +21288,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45688</v>
+        <v>44795</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>25.8</v>
+        <v>19.1</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21347,7 +21347,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>S 1799-2025</t>
+          <t>S 312-2025</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21361,10 +21361,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45817</v>
+        <v>45688</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>21.2</v>
+        <v>25.8</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>S 1798-2025</t>
+          <t>S 1799-2025</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21437,7 +21437,7 @@
         <v>45817</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>73.40000000000001</v>
+        <v>21.2</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21493,7 +21493,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>S 3564-2025</t>
+          <t>S 1798-2025</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21507,10 +21507,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>46013</v>
+        <v>45817</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>55.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21566,7 +21566,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>S 3565-2025</t>
+          <t>S 3564-2025</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21583,7 +21583,7 @@
         <v>46013</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>24</v>
+        <v>55.7</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21639,148 +21639,221 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
+          <t>S 3565-2025</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D277" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E277" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I277" t="n">
+        <v>24</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" t="n">
+        <v>0</v>
+      </c>
+      <c r="L277" t="n">
+        <v>0</v>
+      </c>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+      <c r="N277" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" t="n">
+        <v>0</v>
+      </c>
+      <c r="P277" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>0</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0</v>
+      </c>
+      <c r="S277" t="n">
+        <v>0</v>
+      </c>
+      <c r="T277" t="n">
+        <v>0</v>
+      </c>
+      <c r="U277" t="n">
+        <v>0</v>
+      </c>
+      <c r="V277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278" ht="15" customHeight="1">
+      <c r="A278" t="inlineStr">
+        <is>
           <t>S 375-2026</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
+      <c r="C278" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D277" s="1" t="n">
+      <c r="D278" s="1" t="n">
         <v>46065</v>
       </c>
-      <c r="E277" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="I277" t="n">
+      <c r="E278" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I278" t="n">
         <v>17.6</v>
       </c>
-      <c r="J277" t="n">
-        <v>0</v>
-      </c>
-      <c r="K277" t="n">
-        <v>0</v>
-      </c>
-      <c r="L277" t="n">
-        <v>0</v>
-      </c>
-      <c r="M277" t="n">
-        <v>0</v>
-      </c>
-      <c r="N277" t="n">
-        <v>0</v>
-      </c>
-      <c r="O277" t="n">
-        <v>0</v>
-      </c>
-      <c r="P277" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
-      <c r="R277" t="n">
-        <v>0</v>
-      </c>
-      <c r="S277" t="n">
-        <v>0</v>
-      </c>
-      <c r="T277" t="n">
-        <v>0</v>
-      </c>
-      <c r="U277" t="n">
-        <v>0</v>
-      </c>
-      <c r="V277" s="2" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
+      <c r="J278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" t="n">
+        <v>0</v>
+      </c>
+      <c r="L278" t="n">
+        <v>0</v>
+      </c>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>0</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="n">
+        <v>0</v>
+      </c>
+      <c r="T278" t="n">
+        <v>0</v>
+      </c>
+      <c r="U278" t="n">
+        <v>0</v>
+      </c>
+      <c r="V278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>S 1393-2026</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
+      <c r="C279" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D278" s="1" t="n">
+      <c r="D279" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="E278" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="I278" t="n">
+      <c r="E279" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I279" t="n">
         <v>3.4</v>
       </c>
-      <c r="J278" t="n">
-        <v>0</v>
-      </c>
-      <c r="K278" t="n">
-        <v>0</v>
-      </c>
-      <c r="L278" t="n">
-        <v>0</v>
-      </c>
-      <c r="M278" t="n">
-        <v>0</v>
-      </c>
-      <c r="N278" t="n">
-        <v>0</v>
-      </c>
-      <c r="O278" t="n">
-        <v>0</v>
-      </c>
-      <c r="P278" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
-      <c r="R278" t="n">
-        <v>0</v>
-      </c>
-      <c r="S278" t="n">
-        <v>0</v>
-      </c>
-      <c r="T278" t="n">
-        <v>0</v>
-      </c>
-      <c r="U278" t="n">
-        <v>0</v>
-      </c>
-      <c r="V278" s="2" t="inlineStr"/>
+      <c r="J279" t="n">
+        <v>0</v>
+      </c>
+      <c r="K279" t="n">
+        <v>0</v>
+      </c>
+      <c r="L279" t="n">
+        <v>0</v>
+      </c>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0</v>
+      </c>
+      <c r="P279" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>0</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0</v>
+      </c>
+      <c r="S279" t="n">
+        <v>0</v>
+      </c>
+      <c r="T279" t="n">
+        <v>0</v>
+      </c>
+      <c r="U279" t="n">
+        <v>0</v>
+      </c>
+      <c r="V279" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LESSEBO.xlsx
+++ b/Översikt LESSEBO.xlsx
@@ -601,7 +601,7 @@
         <v>45349</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>46035</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45954</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45954</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45954</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45267</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>46176</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45072</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45954</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>45670</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>45954</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45625</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44510</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44518</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44865</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>44727</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44586</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44510</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44842</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>44491</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44529</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44693</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44508</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44522</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44743</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>44460</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33240-2024</t>
+          <t>A 3876-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45518</v>
+        <v>45322</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.4</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56456-2024</t>
+          <t>A 27713-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45625</v>
+        <v>44743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56459-2024</t>
+          <t>A 27080-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45625</v>
+        <v>44741</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 68507-2021</t>
+          <t>A 51189-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44529</v>
+        <v>45219</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 24478-2024</t>
+          <t>A 59173-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45459</v>
+        <v>45253</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1367-2023</t>
+          <t>A 11843-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44936</v>
+        <v>45376</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4143,8 +4143,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4187,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30966-2023</t>
+          <t>A 24171-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4201,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45113</v>
+        <v>45456</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59320-2024</t>
+          <t>A 24478-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45637</v>
+        <v>45459</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4289,13 +4294,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15203-2023</t>
+          <t>A 64635-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4348,14 +4348,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45017</v>
+        <v>45281</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4367,13 +4367,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4416,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15204-2023</t>
+          <t>A 57519-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4426,14 +4421,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45017</v>
+        <v>44896</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4445,13 +4440,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.3</v>
+        <v>6.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4494,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8655-2025</t>
+          <t>A 20541-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4508,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45710</v>
+        <v>45436</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4524,7 +4514,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4567,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27713-2022</t>
+          <t>A 18968-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4581,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44743</v>
+        <v>45427</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4597,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4640,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 43453-2024</t>
+          <t>A 56529-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4654,10 +4644,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45568</v>
+        <v>44893</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4670,7 +4660,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4713,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 859-2025</t>
+          <t>A 38227-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4723,14 +4713,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45665</v>
+        <v>45161</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4742,13 +4732,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4791,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45838-2022</t>
+          <t>A 3714-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4805,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44846</v>
+        <v>44586</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4820,8 +4805,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4864,7 +4854,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10414-2025</t>
+          <t>A 33240-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4878,10 +4868,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45720</v>
+        <v>45518</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4894,7 +4884,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>7.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4937,7 +4927,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 53487-2024</t>
+          <t>A 60358-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4951,10 +4941,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45611</v>
+        <v>44910</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4967,7 +4957,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5010,7 +5000,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8173-2025</t>
+          <t>A 39389-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5020,14 +5010,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45708</v>
+        <v>45551</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5040,7 +5030,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5083,7 +5073,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 15180-2023</t>
+          <t>A 20478-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5097,10 +5087,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45016</v>
+        <v>45775</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5112,8 +5102,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5156,7 +5151,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 20851-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5166,14 +5161,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45708</v>
+        <v>45777</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5185,8 +5180,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1022-2026</t>
+          <t>A 8438-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46030</v>
+        <v>46065</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5258,8 +5258,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5302,7 +5307,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1016-2026</t>
+          <t>A 61575-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5316,10 +5321,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46030</v>
+        <v>44916</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5331,8 +5336,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5375,7 +5385,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10047-2024</t>
+          <t>A 61588-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5389,10 +5399,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45364</v>
+        <v>44916</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5406,11 +5416,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5453,7 +5463,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39884-2025</t>
+          <t>A 29659-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5463,14 +5473,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45891</v>
+        <v>45825</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5483,7 +5493,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5526,7 +5536,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39549-2025</t>
+          <t>A 43453-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5540,10 +5550,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45890</v>
+        <v>45568</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5556,7 +5566,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5599,7 +5609,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39750-2025</t>
+          <t>A 20854-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5613,10 +5623,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45891</v>
+        <v>45777</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5628,8 +5638,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5672,7 +5687,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20478-2025</t>
+          <t>A 20853-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5686,10 +5701,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45775</v>
+        <v>45777</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5707,7 +5722,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5750,7 +5765,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29659-2025</t>
+          <t>A 47396-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5760,14 +5775,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45825</v>
+        <v>45587</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5780,7 +5795,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5823,7 +5838,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20851-2025</t>
+          <t>A 10286-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5837,10 +5852,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45777</v>
+        <v>46076</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5852,13 +5867,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5918,7 +5928,7 @@
         <v>44973</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5974,7 +5984,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35904-2025</t>
+          <t>A 10185-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5988,10 +5998,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45862</v>
+        <v>46076</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6003,13 +6013,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6052,7 +6057,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20854-2025</t>
+          <t>A 10189-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6066,10 +6071,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45777</v>
+        <v>46076</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6081,13 +6086,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6130,7 +6130,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20853-2025</t>
+          <t>A 30527-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45777</v>
+        <v>45831</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6159,13 +6159,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6208,7 +6203,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30527-2025</t>
+          <t>A 47386-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6222,10 +6217,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45831</v>
+        <v>45587</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6238,7 +6233,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6281,7 +6276,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 17836-2023</t>
+          <t>A 32712-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6295,10 +6290,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45037</v>
+        <v>45839</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6310,8 +6305,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30914-2022</t>
+          <t>A 37399-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44767</v>
+        <v>45540</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6427,7 +6427,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 43809-2025</t>
+          <t>A 51175-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6441,10 +6441,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45912</v>
+        <v>45219</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32712-2025</t>
+          <t>A 13347-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45839</v>
+        <v>46094</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6531,11 +6531,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19501-2022</t>
+          <t>A 39549-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6592,10 +6592,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44693</v>
+        <v>45890</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6651,7 +6651,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44904-2025</t>
+          <t>A 14584-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45918</v>
+        <v>45013</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6724,7 +6724,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 44899-2025</t>
+          <t>A 35909-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6738,10 +6738,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45918</v>
+        <v>45862</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6753,8 +6753,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6797,7 +6802,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 50154-2022</t>
+          <t>A 35899-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6811,10 +6816,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44865</v>
+        <v>45862</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6826,8 +6831,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6887,7 +6897,7 @@
         <v>45107</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6943,7 +6953,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35909-2025</t>
+          <t>A 19501-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6957,10 +6967,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45862</v>
+        <v>44693</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6972,13 +6982,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7021,7 +7026,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35899-2025</t>
+          <t>A 51191-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7035,10 +7040,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45862</v>
+        <v>45219</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7050,13 +7055,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41905-2022</t>
+          <t>A 39750-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44830</v>
+        <v>45891</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7128,13 +7128,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7177,7 +7172,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 48429-2025</t>
+          <t>A 39884-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7191,10 +7186,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45934</v>
+        <v>45891</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7207,7 +7202,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7250,7 +7245,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48433-2025</t>
+          <t>A 52525-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7264,10 +7259,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45934</v>
+        <v>45225</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7280,7 +7275,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7323,7 +7318,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17729-2025</t>
+          <t>A 17517-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7337,10 +7332,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45758</v>
+        <v>45036</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7352,13 +7347,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7401,7 +7391,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3955-2022</t>
+          <t>A 1367-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7415,10 +7405,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44587</v>
+        <v>44936</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7431,7 +7421,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7474,7 +7464,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 4236-2026</t>
+          <t>A 18464-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7488,10 +7478,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46044</v>
+        <v>46127</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7503,8 +7493,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>3.3</v>
+        <v>14.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7547,7 +7542,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 4229-2026</t>
+          <t>A 18466-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7561,10 +7556,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46044</v>
+        <v>46127</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7576,8 +7571,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>9.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7620,7 +7620,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 49298-2025</t>
+          <t>A 18625-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45938</v>
+        <v>46127</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7693,7 +7693,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 20443-2025</t>
+          <t>A 10047-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45775</v>
+        <v>45364</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7724,11 +7724,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 60358-2022</t>
+          <t>A 4107-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44910</v>
+        <v>45684</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7844,7 +7844,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17517-2023</t>
+          <t>A 35904-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7858,10 +7858,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45036</v>
+        <v>45862</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7873,8 +7873,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7917,7 +7922,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 20541-2024</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7927,14 +7932,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45436</v>
+        <v>45708</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7947,7 +7952,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7990,7 +7995,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 64635-2023</t>
+          <t>A 21917-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8004,10 +8009,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45281</v>
+        <v>45784</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8020,7 +8025,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8063,7 +8068,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 14584-2023</t>
+          <t>A 20855-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8077,10 +8082,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45013</v>
+        <v>45777</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8092,8 +8097,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8136,7 +8146,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 52031-2025</t>
+          <t>A 43809-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8150,10 +8160,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45952</v>
+        <v>45912</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8166,7 +8176,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8209,7 +8219,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 73140-2021</t>
+          <t>A 1894-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8223,10 +8233,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44550</v>
+        <v>45671</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8239,7 +8249,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8282,7 +8292,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 30405-2023</t>
+          <t>A 47693-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8296,10 +8306,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45111</v>
+        <v>45931</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8312,7 +8322,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8355,7 +8365,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 52537-2025</t>
+          <t>A 20056-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8369,10 +8379,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45954</v>
+        <v>45772</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8384,13 +8394,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8433,7 +8438,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 52531-2025</t>
+          <t>A 44904-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8447,10 +8452,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45954</v>
+        <v>45918</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8462,13 +8467,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8511,7 +8511,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 52532-2025</t>
+          <t>A 44899-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45954</v>
+        <v>45918</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8540,13 +8540,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8589,7 +8584,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 52546-2025</t>
+          <t>A 63927-2021</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8603,10 +8598,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45954</v>
+        <v>44509</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8624,7 +8619,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.4</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8667,7 +8662,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 52534-2025</t>
+          <t>A 8655-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8681,10 +8676,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45954</v>
+        <v>45710</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8696,13 +8691,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8745,7 +8735,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 53122-2025</t>
+          <t>A 36895-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8759,10 +8749,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45958</v>
+        <v>45874</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8775,7 +8765,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8818,7 +8808,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 41900-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8828,14 +8818,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45708</v>
+        <v>44830</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8847,8 +8837,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8891,7 +8886,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3239-2025</t>
+          <t>A 22432-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8901,14 +8896,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45679</v>
+        <v>45070</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8926,7 +8921,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8969,7 +8964,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 52525-2023</t>
+          <t>A 17552-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8983,10 +8978,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45225</v>
+        <v>45036</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8999,7 +8994,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9042,7 +9037,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 51191-2023</t>
+          <t>A 13751-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9056,10 +9051,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45219</v>
+        <v>45737</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9115,7 +9110,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 8438-2026</t>
+          <t>A 56471-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9129,10 +9124,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46065</v>
+        <v>45625</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9144,13 +9139,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9193,7 +9183,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56467-2024</t>
+          <t>A 38303-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9207,10 +9197,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45625</v>
+        <v>45883</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9223,7 +9213,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9266,7 +9256,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 49295-2025</t>
+          <t>A 30405-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9280,10 +9270,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45938</v>
+        <v>45111</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9296,7 +9286,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9339,7 +9329,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 3876-2024</t>
+          <t>A 35894-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9353,10 +9343,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45322</v>
+        <v>45862</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9368,8 +9358,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9412,7 +9407,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 1490-2025</t>
+          <t>A 50892-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9422,14 +9417,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45670</v>
+        <v>44867</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9441,13 +9436,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9490,7 +9480,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 54541-2023</t>
+          <t>A 45838-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9500,14 +9490,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45233</v>
+        <v>44846</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9519,13 +9509,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9568,7 +9553,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 10189-2026</t>
+          <t>A 21311-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9582,10 +9567,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46076</v>
+        <v>46147</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9598,7 +9583,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9641,7 +9626,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 51189-2023</t>
+          <t>A 20824-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9655,10 +9640,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45219</v>
+        <v>45058</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9671,7 +9656,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9714,7 +9699,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 10286-2026</t>
+          <t>A 30600-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9728,10 +9713,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46076</v>
+        <v>45493</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9744,7 +9729,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9787,7 +9772,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 10185-2026</t>
+          <t>A 48429-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9801,10 +9786,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46076</v>
+        <v>45934</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9817,7 +9802,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9860,7 +9845,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 8690-2023</t>
+          <t>A 48433-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9874,10 +9859,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44978</v>
+        <v>45934</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9890,7 +9875,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9933,7 +9918,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 57519-2022</t>
+          <t>A 22318-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9947,10 +9932,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44896</v>
+        <v>46154</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9963,7 +9948,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10006,7 +9991,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 56475-2024</t>
+          <t>A 15864-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10020,10 +10005,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45625</v>
+        <v>44664</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10036,7 +10021,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10079,7 +10064,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 65137-2023</t>
+          <t>A 642-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10089,14 +10074,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45288</v>
+        <v>45299</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10108,8 +10093,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>5.4</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10152,7 +10142,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 61638-2025</t>
+          <t>A 22423-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10162,14 +10152,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46002</v>
+        <v>46154</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10182,7 +10172,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10225,7 +10215,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 61641-2025</t>
+          <t>A 17729-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10239,10 +10229,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46002</v>
+        <v>45758</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10260,7 +10250,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10303,7 +10293,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 20824-2023</t>
+          <t>A 22764-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10317,10 +10307,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45058</v>
+        <v>46157</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10332,8 +10322,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10376,7 +10371,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 17204-2025</t>
+          <t>A 22768-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10390,10 +10385,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45756</v>
+        <v>46157</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10405,8 +10400,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10449,7 +10449,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 62728-2025</t>
+          <t>A 22770-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10463,10 +10463,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46008</v>
+        <v>46157</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10527,7 +10527,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 27191-2022</t>
+          <t>A 20431-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10541,10 +10541,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44741</v>
+        <v>45775</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10556,8 +10556,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10600,7 +10605,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 49121-2024</t>
+          <t>A 22723-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10614,10 +10619,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45594</v>
+        <v>46157</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10629,8 +10634,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10673,7 +10683,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 13347-2026</t>
+          <t>A 20681-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10687,10 +10697,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46094</v>
+        <v>45776</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10704,11 +10714,11 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10751,7 +10761,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 47396-2024</t>
+          <t>A 20443-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10765,10 +10775,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45587</v>
+        <v>45775</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10780,8 +10790,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10824,7 +10839,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 1897-2025</t>
+          <t>A 22718-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10838,10 +10853,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45671</v>
+        <v>46157</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10853,8 +10868,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10897,7 +10917,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 51175-2023</t>
+          <t>A 22766-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10911,10 +10931,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45219</v>
+        <v>46157</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10926,8 +10946,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10970,7 +10995,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 61995-2022</t>
+          <t>A 22756-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10984,10 +11009,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44918</v>
+        <v>46157</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11001,11 +11026,11 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11048,7 +11073,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 4107-2025</t>
+          <t>A 22758-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11062,10 +11087,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45684</v>
+        <v>46157</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11077,8 +11102,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11121,7 +11151,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 3875-2024</t>
+          <t>A 20435-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11135,10 +11165,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45322</v>
+        <v>45775</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11150,8 +11180,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11194,7 +11229,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 50892-2022</t>
+          <t>A 20485-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11208,10 +11243,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44867</v>
+        <v>45775</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11223,8 +11258,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11267,7 +11307,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 47402-2024</t>
+          <t>A 22719-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11281,10 +11321,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45587</v>
+        <v>46157</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11296,8 +11336,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11340,7 +11385,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 18625-2026</t>
+          <t>A 22720-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11354,10 +11399,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46127</v>
+        <v>46157</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11369,8 +11414,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11413,7 +11463,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 18464-2026</t>
+          <t>A 49298-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11427,10 +11477,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46127</v>
+        <v>45938</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11442,13 +11492,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>14.2</v>
+        <v>4.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11491,7 +11536,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 18466-2026</t>
+          <t>A 47402-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11505,10 +11550,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46127</v>
+        <v>45587</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11520,13 +11565,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11569,7 +11609,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 4465-2024</t>
+          <t>A 50154-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11583,10 +11623,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45327</v>
+        <v>44865</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11599,7 +11639,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11642,7 +11682,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 4453-2024</t>
+          <t>A 24275-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11656,10 +11696,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45327</v>
+        <v>46169</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11671,13 +11711,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11720,7 +11755,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 50162-2023</t>
+          <t>A 64865-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11730,14 +11765,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45215</v>
+        <v>45282</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11755,7 +11790,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11798,7 +11833,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 20056-2025</t>
+          <t>A 24271-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11812,10 +11847,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45772</v>
+        <v>46169</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11828,7 +11863,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11871,7 +11906,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 39389-2024</t>
+          <t>A 24272-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11885,10 +11920,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45551</v>
+        <v>46169</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11901,7 +11936,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11944,7 +11979,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 36895-2025</t>
+          <t>A 24269-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11958,10 +11993,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45874</v>
+        <v>46169</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11974,7 +12009,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12017,7 +12052,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 38303-2025</t>
+          <t>A 34386-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12031,10 +12066,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45883</v>
+        <v>45139</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12047,7 +12082,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12090,7 +12125,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 17552-2023</t>
+          <t>A 17350-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12104,10 +12139,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45036</v>
+        <v>45035</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12120,7 +12155,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12163,7 +12198,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 56471-2024</t>
+          <t>A 14940-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12177,10 +12212,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45625</v>
+        <v>45398</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12193,7 +12228,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12236,7 +12271,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 40912-2023</t>
+          <t>A 17836-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12250,10 +12285,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45173</v>
+        <v>45037</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12309,7 +12344,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 21917-2025</t>
+          <t>A 25169-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12323,10 +12358,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45784</v>
+        <v>46175</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12339,7 +12374,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12382,7 +12417,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 18968-2024</t>
+          <t>A 65137-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12396,10 +12431,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45427</v>
+        <v>45288</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12412,7 +12447,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12455,7 +12490,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 53341-2021</t>
+          <t>A 52031-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12469,10 +12504,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44468</v>
+        <v>45952</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12485,7 +12520,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12528,7 +12563,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 1894-2025</t>
+          <t>A 43114-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12542,10 +12577,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45671</v>
+        <v>45567</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12557,8 +12592,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12601,7 +12641,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 20855-2025</t>
+          <t>A 4413-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12615,10 +12655,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45777</v>
+        <v>44589</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12630,13 +12670,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12679,7 +12714,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 17203-2025</t>
+          <t>A 52537-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12693,10 +12728,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45756</v>
+        <v>45954</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12708,8 +12743,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12752,7 +12792,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 48639-2023</t>
+          <t>A 52531-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12766,10 +12806,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45202</v>
+        <v>45954</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12781,8 +12821,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12825,7 +12870,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 47693-2025</t>
+          <t>A 52532-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12839,10 +12884,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45931</v>
+        <v>45954</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12854,8 +12899,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12898,7 +12948,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35894-2025</t>
+          <t>A 52546-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12912,10 +12962,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45862</v>
+        <v>45954</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12933,7 +12983,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12976,7 +13026,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 21311-2026</t>
+          <t>A 59321-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12990,10 +13040,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46147</v>
+        <v>45637</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13005,8 +13055,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13049,7 +13104,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 27574-2023</t>
+          <t>A 4465-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13063,10 +13118,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45097</v>
+        <v>45327</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13079,7 +13134,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13122,7 +13177,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 4839-2023</t>
+          <t>A 20441-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13136,10 +13191,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44955</v>
+        <v>45775</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13151,8 +13206,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13195,7 +13255,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 14549-2025</t>
+          <t>A 52534-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13209,10 +13269,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45741</v>
+        <v>45954</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13224,8 +13284,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13268,7 +13333,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 30600-2024</t>
+          <t>A 53122-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13282,10 +13347,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45493</v>
+        <v>45958</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13298,7 +13363,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13341,7 +13406,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 22318-2026</t>
+          <t>A 14551-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13355,10 +13420,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46154</v>
+        <v>45741</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13371,7 +13436,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13414,7 +13479,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 24171-2024</t>
+          <t>A 33076-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13424,14 +13489,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45456</v>
+        <v>45126</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13444,7 +13509,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13487,7 +13552,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 22423-2026</t>
+          <t>A 70350-2021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13497,14 +13562,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46154</v>
+        <v>44536</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13517,7 +13582,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13560,7 +13625,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 22718-2026</t>
+          <t>A 1490-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13570,14 +13635,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46157</v>
+        <v>45670</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13595,7 +13660,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13638,7 +13703,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 64865-2023</t>
+          <t>A 27870-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13652,10 +13717,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45282</v>
+        <v>46191</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13667,13 +13732,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>5.6</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13716,7 +13776,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 22756-2026</t>
+          <t>A 27873-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13730,10 +13790,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46157</v>
+        <v>46191</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13745,13 +13805,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>8.699999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13794,7 +13849,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 22758-2026</t>
+          <t>A 14549-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13808,10 +13863,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46157</v>
+        <v>45741</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13823,13 +13878,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13872,7 +13922,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 22766-2026</t>
+          <t>A 20480-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13886,10 +13936,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46157</v>
+        <v>45775</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13907,7 +13957,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13950,7 +14000,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 22719-2026</t>
+          <t>A 27405-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13964,10 +14014,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46157</v>
+        <v>45474</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13979,13 +14029,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14028,7 +14073,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 22720-2026</t>
+          <t>A 13036-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14042,10 +14087,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46157</v>
+        <v>44643</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14057,13 +14102,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14106,7 +14146,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 22764-2026</t>
+          <t>A 3955-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14120,10 +14160,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46157</v>
+        <v>44587</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14135,13 +14175,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14184,7 +14219,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 22768-2026</t>
+          <t>A 49295-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14198,10 +14233,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46157</v>
+        <v>45938</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14213,13 +14248,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>3</v>
+        <v>7.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14262,7 +14292,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 22770-2026</t>
+          <t>A 56456-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14276,10 +14306,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46157</v>
+        <v>45625</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14291,13 +14321,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14340,7 +14365,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 22723-2026</t>
+          <t>A 56459-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14354,10 +14379,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46157</v>
+        <v>45625</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14369,13 +14394,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14418,7 +14438,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 41900-2022</t>
+          <t>A 1897-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14432,10 +14452,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44830</v>
+        <v>45671</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14447,13 +14467,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14496,7 +14511,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 38227-2023</t>
+          <t>A 20825-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14510,10 +14525,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45161</v>
+        <v>45058</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14526,7 +14541,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14569,7 +14584,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 20485-2025</t>
+          <t>A 32760-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14583,10 +14598,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45775</v>
+        <v>46241</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14598,13 +14613,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14647,7 +14657,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 20431-2025</t>
+          <t>A 32764-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14661,10 +14671,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45775</v>
+        <v>46241</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14676,13 +14686,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14725,7 +14730,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 20435-2025</t>
+          <t>A 32768-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14739,10 +14744,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45775</v>
+        <v>46241</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14754,13 +14759,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14803,7 +14803,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 20681-2025</t>
+          <t>A 32771-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14817,10 +14817,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45776</v>
+        <v>46241</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14832,13 +14832,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14881,7 +14876,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 35332-2022</t>
+          <t>A 30826-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14895,10 +14890,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44798</v>
+        <v>46205</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14911,7 +14906,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14954,7 +14949,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 20825-2023</t>
+          <t>A 30822-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14968,10 +14963,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45058</v>
+        <v>46205</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14984,7 +14979,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15027,7 +15022,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 24275-2026</t>
+          <t>A 48639-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15041,10 +15036,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46169</v>
+        <v>45202</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15057,7 +15052,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15100,7 +15095,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 24271-2026</t>
+          <t>A 50162-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15110,14 +15105,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46169</v>
+        <v>45215</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15129,8 +15124,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15173,7 +15173,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 24272-2026</t>
+          <t>A 2755-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15183,14 +15183,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46169</v>
+        <v>45677</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15246,7 +15246,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 13751-2025</t>
+          <t>A 21745-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15260,10 +15260,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45737</v>
+        <v>44708</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15319,7 +15319,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 24269-2026</t>
+          <t>A 39603-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15333,10 +15333,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46169</v>
+        <v>44818</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15392,7 +15392,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 27405-2024</t>
+          <t>A 27191-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15406,10 +15406,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45474</v>
+        <v>44741</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15465,7 +15465,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 59173-2023</t>
+          <t>A 17203-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15479,10 +15479,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45253</v>
+        <v>45756</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15538,7 +15538,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 3714-2022</t>
+          <t>A 40912-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15552,10 +15552,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44586</v>
+        <v>45173</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15567,13 +15567,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15616,7 +15611,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 25169-2026</t>
+          <t>A 34661-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15630,10 +15625,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46175</v>
+        <v>46257</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15646,7 +15641,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15689,7 +15684,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 18207-2025</t>
+          <t>A 3239-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15703,10 +15698,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45761</v>
+        <v>45679</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15720,11 +15715,11 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15767,7 +15762,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 18211-2025</t>
+          <t>A 34806-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15781,10 +15776,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45761</v>
+        <v>46255</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15798,11 +15793,11 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15845,7 +15840,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 642-2024</t>
+          <t>A 54541-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15855,14 +15850,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45299</v>
+        <v>45233</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15880,7 +15875,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15923,7 +15918,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 33076-2023</t>
+          <t>A 34820-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15933,14 +15928,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45126</v>
+        <v>46255</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15952,8 +15947,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15996,7 +15996,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 20441-2025</t>
+          <t>A 34855-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16010,10 +16010,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45775</v>
+        <v>46255</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I201" t="n">
@@ -16074,7 +16074,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 47386-2024</t>
+          <t>A 3875-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16088,10 +16088,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45587</v>
+        <v>45322</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16147,7 +16147,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 63927-2021</t>
+          <t>A 34894-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16161,10 +16161,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44509</v>
+        <v>46259</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16176,13 +16176,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16225,7 +16220,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 59321-2024</t>
+          <t>A 34984-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16239,10 +16234,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45637</v>
+        <v>46258</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16254,13 +16249,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16303,7 +16293,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 14551-2025</t>
+          <t>A 18207-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16317,10 +16307,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45741</v>
+        <v>45761</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16332,8 +16322,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16376,7 +16371,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 39603-2022</t>
+          <t>A 18211-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16390,10 +16385,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44818</v>
+        <v>45761</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16405,8 +16400,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16449,7 +16449,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 27870-2026</t>
+          <t>A 41905-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16463,10 +16463,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46191</v>
+        <v>44830</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16478,8 +16478,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16522,7 +16527,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 27873-2026</t>
+          <t>A 35570-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16536,10 +16541,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46191</v>
+        <v>46262</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16551,8 +16556,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16595,7 +16605,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 20480-2025</t>
+          <t>A 31252-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16609,10 +16619,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45775</v>
+        <v>46218</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16626,11 +16636,11 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16673,7 +16683,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 11843-2024</t>
+          <t>A 35568-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16687,10 +16697,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45376</v>
+        <v>46262</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16704,11 +16714,11 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16751,7 +16761,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 14940-2024</t>
+          <t>A 39436-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16765,10 +16775,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45398</v>
+        <v>44818</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16781,7 +16791,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16824,7 +16834,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 32771-2026</t>
+          <t>A 61638-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16838,10 +16848,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46241</v>
+        <v>46002</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16854,7 +16864,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16897,7 +16907,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 32760-2026</t>
+          <t>A 61641-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16911,10 +16921,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46241</v>
+        <v>46002</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16926,8 +16936,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16970,7 +16985,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 32764-2026</t>
+          <t>A 36067-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16984,10 +16999,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46241</v>
+        <v>46267</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16999,8 +17014,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17043,7 +17063,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 32768-2026</t>
+          <t>A 36313-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17057,10 +17077,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46241</v>
+        <v>46268</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17073,7 +17093,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17116,7 +17136,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 4413-2022</t>
+          <t>A 17204-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17130,10 +17150,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44589</v>
+        <v>45756</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17146,7 +17166,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17189,7 +17209,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 30822-2026</t>
+          <t>A 35332-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17203,10 +17223,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46205</v>
+        <v>44798</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17219,7 +17239,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17262,7 +17282,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 30826-2026</t>
+          <t>A 62728-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17276,10 +17296,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46205</v>
+        <v>46008</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17291,8 +17311,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17335,7 +17360,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 3605-2024</t>
+          <t>A 56467-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17349,10 +17374,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45320</v>
+        <v>45625</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17365,7 +17390,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17408,7 +17433,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 34386-2023</t>
+          <t>A 59320-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17422,10 +17447,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45139</v>
+        <v>45637</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17437,8 +17462,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17481,7 +17511,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 21546-2023</t>
+          <t>A 70349-2021</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17495,10 +17525,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45063</v>
+        <v>44536</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17511,7 +17541,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17554,7 +17584,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 15864-2022</t>
+          <t>A 37786-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17568,10 +17598,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44664</v>
+        <v>46279</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17584,7 +17614,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17627,7 +17657,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 38712-2022</t>
+          <t>A 1022-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17641,10 +17671,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44814</v>
+        <v>46030</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17657,7 +17687,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17700,7 +17730,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 34855-2026</t>
+          <t>A 1016-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17714,10 +17744,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46255</v>
+        <v>46030</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17729,13 +17759,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17778,7 +17803,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 22432-2023</t>
+          <t>A 38098-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17788,14 +17813,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45070</v>
+        <v>46281</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17807,13 +17832,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17856,7 +17876,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 56529-2022</t>
+          <t>A 30914-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17870,10 +17890,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44893</v>
+        <v>44767</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17886,7 +17906,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>9</v>
+        <v>1.4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17929,7 +17949,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 34894-2026</t>
+          <t>A 73140-2021</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17943,10 +17963,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46259</v>
+        <v>44550</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17959,7 +17979,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18002,7 +18022,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 34984-2026</t>
+          <t>A 27574-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18016,10 +18036,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46258</v>
+        <v>45097</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18032,7 +18052,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18075,7 +18095,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 34820-2026</t>
+          <t>A 53341-2021</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18089,10 +18109,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46255</v>
+        <v>44468</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18104,13 +18124,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18153,7 +18168,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 43114-2024</t>
+          <t>A 4839-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18167,10 +18182,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45567</v>
+        <v>44955</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18182,13 +18197,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18231,7 +18241,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 34661-2026</t>
+          <t>A 3605-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18245,10 +18255,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46257</v>
+        <v>45320</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18261,7 +18271,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18304,7 +18314,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 34806-2026</t>
+          <t>A 4229-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18318,10 +18328,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46255</v>
+        <v>46044</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18333,13 +18343,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>2.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18382,7 +18387,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 31252-2026</t>
+          <t>A 21546-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18396,10 +18401,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46218</v>
+        <v>45063</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18411,13 +18416,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18460,7 +18460,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 21745-2022</t>
+          <t>A 4236-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18474,10 +18474,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44708</v>
+        <v>46044</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>9.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18533,7 +18533,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 37399-2024</t>
+          <t>A 15180-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18547,10 +18547,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45540</v>
+        <v>45016</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18606,7 +18606,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 35568-2026</t>
+          <t>A 859-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18616,14 +18616,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46262</v>
+        <v>45665</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18684,7 +18684,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 27080-2022</t>
+          <t>A 52031-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18698,10 +18698,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44741</v>
+        <v>45223</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18757,7 +18757,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 35570-2026</t>
+          <t>A 30966-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18771,10 +18771,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46262</v>
+        <v>45113</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18786,13 +18786,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I238" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18835,7 +18830,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 36067-2026</t>
+          <t>A 68507-2021</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18849,10 +18844,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46267</v>
+        <v>44529</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18864,13 +18859,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I239" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18913,7 +18903,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 43206-2024</t>
+          <t>A 38712-2022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18927,10 +18917,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45567</v>
+        <v>44814</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18943,7 +18933,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18986,7 +18976,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 36313-2026</t>
+          <t>A 43206-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19000,10 +18990,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46268</v>
+        <v>45567</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19016,7 +19006,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19059,7 +19049,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 39436-2022</t>
+          <t>A 15203-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19069,14 +19059,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44818</v>
+        <v>45017</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19088,8 +19078,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I242" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19132,7 +19127,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 13036-2022</t>
+          <t>A 15204-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19142,14 +19137,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44643</v>
+        <v>45017</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19161,8 +19156,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I243" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19205,7 +19205,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 52031-2023</t>
+          <t>A 8690-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19219,10 +19219,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45223</v>
+        <v>44978</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19278,7 +19278,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 70349-2021</t>
+          <t>A 61995-2022</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19292,10 +19292,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>44536</v>
+        <v>44918</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19307,8 +19307,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I245" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19351,7 +19356,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 70350-2021</t>
+          <t>A 4453-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19365,10 +19370,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>44536</v>
+        <v>45327</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19380,8 +19385,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I246" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19424,7 +19434,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 2755-2025</t>
+          <t>A 49121-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19434,14 +19444,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45677</v>
+        <v>45594</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19497,7 +19507,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 61575-2022</t>
+          <t>A 56475-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19511,10 +19521,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44916</v>
+        <v>45625</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19526,13 +19536,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I248" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19575,7 +19580,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 61588-2022</t>
+          <t>A 51990-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19589,10 +19594,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44916</v>
+        <v>45607</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19604,13 +19609,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I249" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19653,7 +19653,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 37786-2026</t>
+          <t>A 41598-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19667,10 +19667,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46279</v>
+        <v>45560</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19726,7 +19726,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 17350-2023</t>
+          <t>A 20852-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19740,10 +19740,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45035</v>
+        <v>45777</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19755,8 +19755,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I251" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19799,7 +19804,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 20852-2025</t>
+          <t>A 61439-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19813,10 +19818,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45777</v>
+        <v>45646</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19828,13 +19833,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I252" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19877,7 +19877,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 51990-2024</t>
+          <t>A 21951-2025</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19887,14 +19887,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45607</v>
+        <v>45784</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19906,8 +19906,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I253" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19950,7 +19955,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 41598-2024</t>
+          <t>A 37964-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19960,14 +19965,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45560</v>
+        <v>45544</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19980,7 +19985,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20023,7 +20028,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 61439-2024</t>
+          <t>A 4742-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20037,10 +20042,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45646</v>
+        <v>45688</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20052,8 +20057,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I255" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20096,7 +20106,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 38098-2026</t>
+          <t>A 29566-2024</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20110,10 +20120,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46281</v>
+        <v>45484</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20126,7 +20136,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.5</v>
+        <v>21.3</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20169,7 +20179,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 21951-2025</t>
+          <t>A 53487-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20179,14 +20189,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45784</v>
+        <v>45611</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20198,13 +20208,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I257" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20247,7 +20252,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 37964-2024</t>
+          <t>A 10414-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20257,14 +20262,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45544</v>
+        <v>45720</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20277,7 +20282,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20320,7 +20325,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 4742-2025</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20330,14 +20335,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45688</v>
+        <v>45708</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20349,13 +20354,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I259" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20398,7 +20398,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 29566-2024</t>
+          <t>A 8173-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20408,14 +20408,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45484</v>
+        <v>45708</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>21.3</v>
+        <v>0.9</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20471,7 +20471,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>S 2321-2023</t>
+          <t>S 2061-2022</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20485,10 +20485,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45105</v>
+        <v>44672</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20544,7 +20544,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>S 4661-2022</t>
+          <t>S 2321-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20554,14 +20554,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>44795</v>
+        <v>45105</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>43.6</v>
+        <v>0.7</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20617,7 +20617,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>S 396-2023</t>
+          <t>S 4661-2022</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20631,10 +20631,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>44959</v>
+        <v>44795</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>78.8</v>
+        <v>43.6</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20690,7 +20690,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>S 2061-2022</t>
+          <t>S 396-2023</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20700,14 +20700,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>44672</v>
+        <v>44959</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.6</v>
+        <v>78.8</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20780,7 +20780,7 @@
         <v>45056</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44959</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44893</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>44893</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45072</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45193</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45386</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>44795</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45688</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45817</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45817</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>46013</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46013</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>46065</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>46154</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>

--- a/Översikt LESSEBO.xlsx
+++ b/Översikt LESSEBO.xlsx
@@ -601,7 +601,7 @@
         <v>45349</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>46035</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45954</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45954</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45954</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45267</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>46176</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45072</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52540-2025</t>
+          <t>A 1488-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1603,14 +1603,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45954</v>
+        <v>45670</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1622,19 +1622,14 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1661,365 +1656,370 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 1488-2025 artfynd.xlsx", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 1488-2025 karta.png", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 1488-2025 georefererad karta.tif", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 1488-2025 FSC-klagomål.docx", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 1488-2025 FSC-klagomål mail.docx", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 1488-2025 tillsynsbegäran.docx", "A 1488-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 1488-2025 tillsynsbegäran mail.docx", "A 1488-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 56472-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45625</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 56472-2024 artfynd.xlsx", "A 56472-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 56472-2024 karta.png", "A 56472-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 56472-2024 georefererad karta.tif", "A 56472-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 56472-2024 FSC-klagomål.docx", "A 56472-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 56472-2024 FSC-klagomål mail.docx", "A 56472-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 56472-2024 tillsynsbegäran.docx", "A 56472-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 56472-2024 tillsynsbegäran mail.docx", "A 56472-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 52540-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U13" t="n">
         <v>4</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52540-2025 artfynd.xlsx", "A 52540-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52540-2025 karta.png", "A 52540-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52540-2025 georefererad karta.tif", "A 52540-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52540-2025 FSC-klagomål.docx", "A 52540-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52540-2025 FSC-klagomål mail.docx", "A 52540-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52540-2025 tillsynsbegäran.docx", "A 52540-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52540-2025 tillsynsbegäran mail.docx", "A 52540-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 1488-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45670</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J12" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 52539-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U14" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Korallrot</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 1488-2025 artfynd.xlsx", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 1488-2025 karta.png", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 1488-2025 georefererad karta.tif", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 1488-2025 FSC-klagomål.docx", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 1488-2025 FSC-klagomål mail.docx", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 1488-2025 tillsynsbegäran.docx", "A 1488-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 1488-2025 tillsynsbegäran mail.docx", "A 1488-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 52539-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45954</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52539-2025 artfynd.xlsx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52539-2025 karta.png", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52539-2025 georefererad karta.tif", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52539-2025 FSC-klagomål.docx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52539-2025 FSC-klagomål mail.docx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52539-2025 tillsynsbegäran.docx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52539-2025 tillsynsbegäran mail.docx", "A 52539-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 56472-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45625</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 56472-2024 artfynd.xlsx", "A 56472-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 56472-2024 karta.png", "A 56472-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 56472-2024 georefererad karta.tif", "A 56472-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 56472-2024 FSC-klagomål.docx", "A 56472-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 56472-2024 FSC-klagomål mail.docx", "A 56472-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 56472-2024 tillsynsbegäran.docx", "A 56472-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 56472-2024 tillsynsbegäran mail.docx", "A 56472-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44510</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44518</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44865</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24680-2022</t>
+          <t>A 3741-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44727</v>
+        <v>44586</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2892,8 +2892,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2941,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3741-2022</t>
+          <t>A 24680-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2955,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44586</v>
+        <v>44727</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2965,13 +2970,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>44510</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44842</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>44491</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44529</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44693</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44508</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44522</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44743</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>44460</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3876-2024</t>
+          <t>A 33240-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45322</v>
+        <v>45518</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>7.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3839,7 +3839,7 @@
         <v>44743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27080-2022</t>
+          <t>A 56456-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44741</v>
+        <v>45625</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51189-2023</t>
+          <t>A 56459-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45219</v>
+        <v>45625</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59173-2023</t>
+          <t>A 68507-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45253</v>
+        <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 11843-2024</t>
+          <t>A 1367-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45376</v>
+        <v>44936</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4143,13 +4143,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24171-2024</t>
+          <t>A 24478-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45456</v>
+        <v>45459</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4222,7 +4217,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4260,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 24478-2024</t>
+          <t>A 30966-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4274,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45459</v>
+        <v>45113</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4290,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4333,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 64635-2023</t>
+          <t>A 59320-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4347,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45281</v>
+        <v>45637</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4367,8 +4362,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57519-2022</t>
+          <t>A 8655-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44896</v>
+        <v>45710</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.6</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20541-2024</t>
+          <t>A 15203-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45436</v>
+        <v>45017</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4513,8 +4513,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4562,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18968-2024</t>
+          <t>A 15204-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4567,14 +4572,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45427</v>
+        <v>45017</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4586,8 +4591,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4640,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 56529-2022</t>
+          <t>A 43453-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4644,10 +4654,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44893</v>
+        <v>45568</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4660,7 +4670,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4713,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38227-2023</t>
+          <t>A 859-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4713,14 +4723,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45161</v>
+        <v>45665</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4732,8 +4742,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4791,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3714-2022</t>
+          <t>A 45838-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4805,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44586</v>
+        <v>44846</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4805,13 +4820,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4854,7 +4864,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33240-2024</t>
+          <t>A 15180-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4868,10 +4878,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45518</v>
+        <v>45016</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4884,7 +4894,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4927,7 +4937,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60358-2022</t>
+          <t>A 7957-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4941,10 +4951,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44910</v>
+        <v>44973</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4957,7 +4967,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5000,7 +5010,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39389-2024</t>
+          <t>A 17836-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5014,10 +5024,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45551</v>
+        <v>45037</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5030,7 +5040,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5073,7 +5083,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20478-2025</t>
+          <t>A 30914-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5087,10 +5097,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45775</v>
+        <v>44767</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5102,13 +5112,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5151,7 +5156,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20851-2025</t>
+          <t>A 19501-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5165,10 +5170,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45777</v>
+        <v>44693</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5180,13 +5185,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8438-2026</t>
+          <t>A 50154-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46065</v>
+        <v>44865</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5258,13 +5258,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5307,7 +5302,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61575-2022</t>
+          <t>A 29767-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5321,10 +5316,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44916</v>
+        <v>45107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5336,13 +5331,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5385,7 +5375,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 61588-2022</t>
+          <t>A 41905-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5399,10 +5389,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44916</v>
+        <v>44830</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5416,11 +5406,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5463,7 +5453,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29659-2025</t>
+          <t>A 3955-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5473,14 +5463,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45825</v>
+        <v>44587</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5493,7 +5483,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5536,7 +5526,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 43453-2024</t>
+          <t>A 17517-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5550,10 +5540,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45568</v>
+        <v>45036</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5566,7 +5556,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5609,7 +5599,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20854-2025</t>
+          <t>A 60358-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5623,10 +5613,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45777</v>
+        <v>44910</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5638,13 +5628,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5687,7 +5672,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20853-2025</t>
+          <t>A 64635-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5701,10 +5686,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45777</v>
+        <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5716,13 +5701,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5765,7 +5745,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47396-2024</t>
+          <t>A 14584-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5779,10 +5759,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45587</v>
+        <v>45013</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5838,7 +5818,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10286-2026</t>
+          <t>A 73140-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5852,10 +5832,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46076</v>
+        <v>44550</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5868,7 +5848,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5911,7 +5891,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7957-2023</t>
+          <t>A 30405-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5925,10 +5905,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44973</v>
+        <v>45111</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5941,7 +5921,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5984,7 +5964,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10185-2026</t>
+          <t>A 3239-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5998,10 +5978,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46076</v>
+        <v>45679</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6013,8 +5993,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6057,7 +6042,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10189-2026</t>
+          <t>A 51191-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6071,10 +6056,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46076</v>
+        <v>45219</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6087,7 +6072,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6130,7 +6115,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30527-2025</t>
+          <t>A 52525-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6144,10 +6129,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45831</v>
+        <v>45225</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6160,7 +6145,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6203,7 +6188,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 47386-2024</t>
+          <t>A 20541-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6217,10 +6202,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45587</v>
+        <v>45436</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6233,7 +6218,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6276,7 +6261,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32712-2025</t>
+          <t>A 56467-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6290,10 +6275,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45839</v>
+        <v>45625</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6305,13 +6290,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6354,7 +6334,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37399-2024</t>
+          <t>A 56471-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6368,10 +6348,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45540</v>
+        <v>45625</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6384,7 +6364,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6427,7 +6407,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 51175-2023</t>
+          <t>A 21917-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6441,10 +6421,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45219</v>
+        <v>45784</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6457,7 +6437,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6500,7 +6480,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13347-2026</t>
+          <t>A 3876-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6514,10 +6494,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46094</v>
+        <v>45322</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6529,13 +6509,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6578,7 +6553,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39549-2025</t>
+          <t>A 1490-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6588,14 +6563,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45890</v>
+        <v>45670</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6607,8 +6582,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6651,7 +6631,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14584-2023</t>
+          <t>A 10047-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6665,10 +6645,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45013</v>
+        <v>45364</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6680,8 +6660,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6724,7 +6709,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35909-2025</t>
+          <t>A 54541-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6734,14 +6719,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45862</v>
+        <v>45233</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6759,7 +6744,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6802,7 +6787,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35899-2025</t>
+          <t>A 51189-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6816,10 +6801,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45862</v>
+        <v>45219</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6831,13 +6816,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6880,7 +6860,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 29767-2023</t>
+          <t>A 1894-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6894,10 +6874,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45107</v>
+        <v>45671</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6910,7 +6890,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6953,7 +6933,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19501-2022</t>
+          <t>A 8690-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6967,10 +6947,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44693</v>
+        <v>44978</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6983,7 +6963,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7026,7 +7006,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 51191-2023</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7036,14 +7016,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45219</v>
+        <v>45708</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7056,7 +7036,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7099,7 +7079,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 39750-2025</t>
+          <t>A 39884-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7116,7 +7096,7 @@
         <v>45891</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7129,7 +7109,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7172,7 +7152,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 39884-2025</t>
+          <t>A 39549-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7186,10 +7166,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45891</v>
+        <v>45890</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7202,7 +7182,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>7.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7245,7 +7225,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52525-2023</t>
+          <t>A 39750-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7259,10 +7239,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45225</v>
+        <v>45891</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7275,7 +7255,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7318,7 +7298,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17517-2023</t>
+          <t>A 20855-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7332,10 +7312,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45036</v>
+        <v>45777</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7347,8 +7327,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7391,7 +7376,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 1367-2023</t>
+          <t>A 57519-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7405,10 +7390,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44936</v>
+        <v>44896</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7421,7 +7406,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7464,7 +7449,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18464-2026</t>
+          <t>A 56475-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7478,10 +7463,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46127</v>
+        <v>45625</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7493,13 +7478,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>14.2</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7542,7 +7522,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18466-2026</t>
+          <t>A 65137-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7556,10 +7536,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46127</v>
+        <v>45288</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7571,13 +7551,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>7.9</v>
+        <v>5.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7620,7 +7595,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 18625-2026</t>
+          <t>A 35904-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7634,10 +7609,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46127</v>
+        <v>45862</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7649,8 +7624,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7693,7 +7673,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 10047-2024</t>
+          <t>A 47693-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7707,10 +7687,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45364</v>
+        <v>45931</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7722,13 +7702,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7771,7 +7746,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 4107-2025</t>
+          <t>A 20824-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7785,10 +7760,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45684</v>
+        <v>45058</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7801,7 +7776,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7844,7 +7819,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35904-2025</t>
+          <t>A 35894-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7861,7 +7836,7 @@
         <v>45862</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7879,7 +7854,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7922,7 +7897,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 17204-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7932,14 +7907,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45708</v>
+        <v>45756</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7952,7 +7927,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7995,7 +7970,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21917-2025</t>
+          <t>A 43809-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8009,10 +7984,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45784</v>
+        <v>45912</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8025,7 +8000,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8068,7 +8043,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 20855-2025</t>
+          <t>A 27191-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8082,10 +8057,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45777</v>
+        <v>44741</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8097,13 +8072,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8146,7 +8116,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 43809-2025</t>
+          <t>A 49121-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8160,10 +8130,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45912</v>
+        <v>45594</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8176,7 +8146,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8219,7 +8189,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 1894-2025</t>
+          <t>A 44904-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8233,10 +8203,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45671</v>
+        <v>45918</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8249,7 +8219,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8292,7 +8262,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 47693-2025</t>
+          <t>A 44899-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8306,10 +8276,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45931</v>
+        <v>45918</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8322,7 +8292,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8365,7 +8335,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20056-2025</t>
+          <t>A 47396-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8379,10 +8349,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45772</v>
+        <v>45587</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8395,7 +8365,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8438,7 +8408,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 44904-2025</t>
+          <t>A 1897-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8452,10 +8422,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45918</v>
+        <v>45671</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8468,7 +8438,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8511,7 +8481,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 44899-2025</t>
+          <t>A 51175-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8525,10 +8495,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45918</v>
+        <v>45219</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8541,7 +8511,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8584,7 +8554,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 63927-2021</t>
+          <t>A 61995-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8598,10 +8568,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44509</v>
+        <v>44918</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8615,11 +8585,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8662,7 +8632,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 8655-2025</t>
+          <t>A 4107-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8676,10 +8646,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45710</v>
+        <v>45684</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8692,7 +8662,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8735,7 +8705,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 36895-2025</t>
+          <t>A 48429-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8749,10 +8719,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45874</v>
+        <v>45934</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8765,7 +8735,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8808,7 +8778,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 41900-2022</t>
+          <t>A 3875-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8822,10 +8792,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44830</v>
+        <v>45322</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8837,13 +8807,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8886,7 +8851,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22432-2023</t>
+          <t>A 48433-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8896,14 +8861,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45070</v>
+        <v>45934</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8915,13 +8880,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8964,7 +8924,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 17552-2023</t>
+          <t>A 21311-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8978,10 +8938,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45036</v>
+        <v>46147</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8994,7 +8954,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9037,7 +8997,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 13751-2025</t>
+          <t>A 17729-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9051,10 +9011,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45737</v>
+        <v>45758</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9066,8 +9026,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9110,7 +9075,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56471-2024</t>
+          <t>A 50892-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9124,10 +9089,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45625</v>
+        <v>44867</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9140,7 +9105,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9183,7 +9148,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 38303-2025</t>
+          <t>A 49298-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9197,10 +9162,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45883</v>
+        <v>45938</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9213,7 +9178,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9256,7 +9221,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 30405-2023</t>
+          <t>A 20443-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9270,10 +9235,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45111</v>
+        <v>45775</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9285,8 +9250,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9329,7 +9299,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 35894-2025</t>
+          <t>A 47402-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9343,10 +9313,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45862</v>
+        <v>45587</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9358,13 +9328,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9407,7 +9372,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 50892-2022</t>
+          <t>A 52031-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9421,10 +9386,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44867</v>
+        <v>45952</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9437,7 +9402,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9480,7 +9445,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 45838-2022</t>
+          <t>A 4465-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9494,10 +9459,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44846</v>
+        <v>45327</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9510,7 +9475,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9553,7 +9518,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 21311-2026</t>
+          <t>A 52537-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9567,10 +9532,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46147</v>
+        <v>45954</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9582,8 +9547,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9626,7 +9596,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20824-2023</t>
+          <t>A 52531-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9640,10 +9610,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45058</v>
+        <v>45954</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9655,8 +9625,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9699,7 +9674,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 30600-2024</t>
+          <t>A 52532-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9713,10 +9688,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45493</v>
+        <v>45954</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9728,8 +9703,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9772,7 +9752,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 48429-2025</t>
+          <t>A 52546-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9786,10 +9766,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45934</v>
+        <v>45954</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9801,8 +9781,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9845,7 +9830,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 48433-2025</t>
+          <t>A 4453-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9859,10 +9844,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45934</v>
+        <v>45327</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9874,8 +9859,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9918,7 +9908,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 22318-2026</t>
+          <t>A 50162-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9928,14 +9918,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46154</v>
+        <v>45215</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9947,8 +9937,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9991,7 +9986,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 15864-2022</t>
+          <t>A 52534-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10005,10 +10000,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44664</v>
+        <v>45954</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10020,8 +10015,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 642-2024</t>
+          <t>A 53122-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10074,14 +10074,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45299</v>
+        <v>45958</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10093,13 +10093,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10142,7 +10137,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 22423-2026</t>
+          <t>A 39389-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10152,14 +10147,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46154</v>
+        <v>45551</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10172,7 +10167,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10215,7 +10210,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 17729-2025</t>
+          <t>A 17552-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10229,10 +10224,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45758</v>
+        <v>45036</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10244,13 +10239,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10293,7 +10283,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 22764-2026</t>
+          <t>A 49295-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10307,10 +10297,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46157</v>
+        <v>45938</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10322,13 +10312,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10371,7 +10356,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 22768-2026</t>
+          <t>A 40912-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10385,10 +10370,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46157</v>
+        <v>45173</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10400,13 +10385,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10449,7 +10429,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 22770-2026</t>
+          <t>A 22318-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10463,10 +10443,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10478,13 +10458,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10527,7 +10502,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 20431-2025</t>
+          <t>A 18968-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10541,10 +10516,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45775</v>
+        <v>45427</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10556,13 +10531,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10605,7 +10575,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 22723-2026</t>
+          <t>A 53341-2021</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10619,10 +10589,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46157</v>
+        <v>44468</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10634,13 +10604,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10683,7 +10648,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20681-2025</t>
+          <t>A 22423-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10693,14 +10658,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45776</v>
+        <v>46154</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10712,13 +10677,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10761,7 +10721,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 20443-2025</t>
+          <t>A 22718-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10775,10 +10735,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45775</v>
+        <v>46157</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10796,7 +10756,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10839,7 +10799,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 22718-2026</t>
+          <t>A 17203-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10853,10 +10813,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46157</v>
+        <v>45756</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10868,13 +10828,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10917,7 +10872,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 22766-2026</t>
+          <t>A 22756-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10934,7 +10889,7 @@
         <v>46157</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10952,7 +10907,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10995,7 +10950,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 22756-2026</t>
+          <t>A 22758-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11012,7 +10967,7 @@
         <v>46157</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11030,7 +10985,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>8.699999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11073,7 +11028,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 22758-2026</t>
+          <t>A 22766-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11090,7 +11045,7 @@
         <v>46157</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11108,7 +11063,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11151,7 +11106,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 20435-2025</t>
+          <t>A 22719-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11165,10 +11120,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45775</v>
+        <v>46157</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11186,7 +11141,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11229,7 +11184,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 20485-2025</t>
+          <t>A 22720-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11243,10 +11198,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45775</v>
+        <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11264,7 +11219,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11307,7 +11262,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 22719-2026</t>
+          <t>A 22764-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11324,7 +11279,7 @@
         <v>46157</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11342,7 +11297,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11385,7 +11340,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 22720-2026</t>
+          <t>A 22768-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11402,7 +11357,7 @@
         <v>46157</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11420,7 +11375,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11463,7 +11418,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 49298-2025</t>
+          <t>A 22770-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11477,10 +11432,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45938</v>
+        <v>46157</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11492,8 +11447,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11536,7 +11496,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 47402-2024</t>
+          <t>A 22723-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11550,10 +11510,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45587</v>
+        <v>46157</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11565,8 +11525,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11609,7 +11574,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 50154-2022</t>
+          <t>A 48639-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11623,10 +11588,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44865</v>
+        <v>45202</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11639,7 +11604,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11682,7 +11647,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 24275-2026</t>
+          <t>A 20485-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11696,10 +11661,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46169</v>
+        <v>45775</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11711,8 +11676,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11755,7 +11725,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 64865-2023</t>
+          <t>A 20431-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11769,10 +11739,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45282</v>
+        <v>45775</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11790,7 +11760,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11833,7 +11803,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 24271-2026</t>
+          <t>A 20435-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11847,10 +11817,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46169</v>
+        <v>45775</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11862,8 +11832,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11906,7 +11881,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 24272-2026</t>
+          <t>A 20681-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11920,10 +11895,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46169</v>
+        <v>45776</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11935,8 +11910,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11979,7 +11959,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 24269-2026</t>
+          <t>A 61638-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11993,10 +11973,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46169</v>
+        <v>46002</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12009,7 +11989,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12052,7 +12032,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 34386-2023</t>
+          <t>A 61641-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12066,10 +12046,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45139</v>
+        <v>46002</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12081,8 +12061,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12125,7 +12110,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 17350-2023</t>
+          <t>A 62728-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12139,10 +12124,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45035</v>
+        <v>46008</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12154,8 +12139,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12198,7 +12188,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 14940-2024</t>
+          <t>A 27574-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12212,10 +12202,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45398</v>
+        <v>45097</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12228,7 +12218,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12271,7 +12261,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 17836-2023</t>
+          <t>A 4839-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12285,10 +12275,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45037</v>
+        <v>44955</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12301,7 +12291,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12344,7 +12334,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 25169-2026</t>
+          <t>A 24275-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12358,10 +12348,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46175</v>
+        <v>46169</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12374,7 +12364,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12417,7 +12407,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 65137-2023</t>
+          <t>A 14549-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12431,10 +12421,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45288</v>
+        <v>45741</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12447,7 +12437,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12490,7 +12480,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 52031-2025</t>
+          <t>A 24271-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12504,10 +12494,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45952</v>
+        <v>46169</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12520,7 +12510,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12563,7 +12553,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 43114-2024</t>
+          <t>A 24272-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12577,10 +12567,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45567</v>
+        <v>46169</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12592,13 +12582,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12641,7 +12626,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 4413-2022</t>
+          <t>A 24269-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12655,10 +12640,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44589</v>
+        <v>46169</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12671,7 +12656,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12714,7 +12699,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 52537-2025</t>
+          <t>A 30600-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12728,10 +12713,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45954</v>
+        <v>45493</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12743,13 +12728,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12792,7 +12772,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 52531-2025</t>
+          <t>A 24171-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12806,10 +12786,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45954</v>
+        <v>45456</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12819,11 +12799,6 @@
       <c r="G158" t="inlineStr">
         <is>
           <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I158" t="n">
@@ -12870,7 +12845,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 52532-2025</t>
+          <t>A 64865-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12884,10 +12859,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45954</v>
+        <v>45282</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12905,7 +12880,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12948,7 +12923,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 52546-2025</t>
+          <t>A 41900-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12962,10 +12937,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45954</v>
+        <v>44830</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12983,7 +12958,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13026,7 +13001,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 59321-2024</t>
+          <t>A 38227-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13040,10 +13015,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45637</v>
+        <v>45161</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13055,13 +13030,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13104,7 +13074,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 4465-2024</t>
+          <t>A 1022-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13118,10 +13088,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45327</v>
+        <v>46030</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13134,7 +13104,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13177,7 +13147,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 20441-2025</t>
+          <t>A 1016-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13191,10 +13161,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45775</v>
+        <v>46030</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13206,13 +13176,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13255,7 +13220,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 52534-2025</t>
+          <t>A 35332-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13269,10 +13234,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45954</v>
+        <v>44798</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13284,13 +13249,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13333,7 +13293,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 53122-2025</t>
+          <t>A 4236-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13347,10 +13307,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45958</v>
+        <v>46044</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13363,7 +13323,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13406,7 +13366,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 14551-2025</t>
+          <t>A 4229-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13420,10 +13380,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45741</v>
+        <v>46044</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13436,7 +13396,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13479,7 +13439,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 33076-2023</t>
+          <t>A 20825-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13489,14 +13449,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45126</v>
+        <v>45058</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13509,7 +13469,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13552,7 +13512,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 70350-2021</t>
+          <t>A 13751-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13566,10 +13526,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44536</v>
+        <v>45737</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13582,7 +13542,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13625,7 +13585,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 1490-2025</t>
+          <t>A 25169-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13635,14 +13595,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45670</v>
+        <v>46175</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13654,13 +13614,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13703,7 +13658,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 27870-2026</t>
+          <t>A 27405-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13717,10 +13672,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46191</v>
+        <v>45474</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13733,7 +13688,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13776,7 +13731,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 27873-2026</t>
+          <t>A 59173-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13790,10 +13745,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46191</v>
+        <v>45253</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13806,7 +13761,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13849,7 +13804,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 14549-2025</t>
+          <t>A 3714-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13863,10 +13818,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45741</v>
+        <v>44586</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13878,8 +13833,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13922,7 +13882,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 20480-2025</t>
+          <t>A 8438-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13936,10 +13896,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45775</v>
+        <v>46065</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13957,7 +13917,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14000,7 +13960,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 27405-2024</t>
+          <t>A 18207-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14014,10 +13974,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45474</v>
+        <v>45761</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14029,8 +13989,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14073,7 +14038,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 13036-2022</t>
+          <t>A 18211-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14087,10 +14052,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44643</v>
+        <v>45761</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14102,8 +14067,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14146,7 +14116,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 3955-2022</t>
+          <t>A 642-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14156,14 +14126,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44587</v>
+        <v>45299</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14175,8 +14145,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14219,7 +14194,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 49295-2025</t>
+          <t>A 10189-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14233,10 +14208,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45938</v>
+        <v>46076</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14249,7 +14224,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14292,7 +14267,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 56456-2024</t>
+          <t>A 10286-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14306,10 +14281,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45625</v>
+        <v>46076</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14322,7 +14297,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14365,7 +14340,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 56459-2024</t>
+          <t>A 10185-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14379,10 +14354,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45625</v>
+        <v>46076</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14395,7 +14370,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14438,7 +14413,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 1897-2025</t>
+          <t>A 33076-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14448,14 +14423,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45671</v>
+        <v>45126</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14468,7 +14443,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14511,7 +14486,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 20825-2023</t>
+          <t>A 20441-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14525,10 +14500,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45058</v>
+        <v>45775</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14540,8 +14515,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14584,7 +14564,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 32760-2026</t>
+          <t>A 59321-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14598,10 +14578,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46241</v>
+        <v>45637</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14613,8 +14593,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14657,7 +14642,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 32764-2026</t>
+          <t>A 14551-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14671,10 +14656,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46241</v>
+        <v>45741</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14687,7 +14672,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14730,7 +14715,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 32768-2026</t>
+          <t>A 47386-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14744,10 +14729,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46241</v>
+        <v>45587</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14760,7 +14745,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14803,7 +14788,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 32771-2026</t>
+          <t>A 63927-2021</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14817,10 +14802,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46241</v>
+        <v>44509</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14832,8 +14817,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14876,7 +14866,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 30826-2026</t>
+          <t>A 13347-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14890,10 +14880,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46205</v>
+        <v>46094</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14905,8 +14895,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14949,7 +14944,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 30822-2026</t>
+          <t>A 39603-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14963,10 +14958,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46205</v>
+        <v>44818</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14979,7 +14974,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15022,7 +15017,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 48639-2023</t>
+          <t>A 27870-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15036,10 +15031,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45202</v>
+        <v>46191</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15052,7 +15047,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15095,7 +15090,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 50162-2023</t>
+          <t>A 27873-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15105,14 +15100,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45215</v>
+        <v>46191</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15124,13 +15119,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15173,7 +15163,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 2755-2025</t>
+          <t>A 20480-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15183,14 +15173,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45677</v>
+        <v>45775</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15202,8 +15192,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15246,7 +15241,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 21745-2022</t>
+          <t>A 11843-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15260,10 +15255,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44708</v>
+        <v>45376</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15275,8 +15270,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>9.699999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15319,7 +15319,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 39603-2022</t>
+          <t>A 14940-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15333,10 +15333,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44818</v>
+        <v>45398</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15392,7 +15392,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 27191-2022</t>
+          <t>A 4413-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15406,10 +15406,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44741</v>
+        <v>44589</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15465,7 +15465,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 17203-2025</t>
+          <t>A 18625-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15479,10 +15479,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45756</v>
+        <v>46127</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15538,7 +15538,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 40912-2023</t>
+          <t>A 3605-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15552,10 +15552,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45173</v>
+        <v>45320</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15611,7 +15611,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 34661-2026</t>
+          <t>A 34386-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15625,10 +15625,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46257</v>
+        <v>45139</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15684,7 +15684,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 3239-2025</t>
+          <t>A 18464-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15698,10 +15698,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45679</v>
+        <v>46127</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15715,11 +15715,11 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.5</v>
+        <v>14.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15762,7 +15762,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 34806-2026</t>
+          <t>A 18466-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15776,10 +15776,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46255</v>
+        <v>46127</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15793,11 +15793,11 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15840,7 +15840,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 54541-2023</t>
+          <t>A 21546-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15850,14 +15850,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45233</v>
+        <v>45063</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15869,13 +15869,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15918,7 +15913,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 34820-2026</t>
+          <t>A 15864-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15932,10 +15927,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46255</v>
+        <v>44664</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15947,13 +15942,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15996,7 +15986,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 34855-2026</t>
+          <t>A 20056-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16010,10 +16000,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46255</v>
+        <v>45772</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16025,13 +16015,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16074,7 +16059,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 3875-2024</t>
+          <t>A 30822-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16088,10 +16073,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45322</v>
+        <v>46205</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16104,7 +16089,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16147,7 +16132,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 34894-2026</t>
+          <t>A 30826-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16161,10 +16146,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46259</v>
+        <v>46205</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16177,7 +16162,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16220,7 +16205,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 34984-2026</t>
+          <t>A 38712-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16234,10 +16219,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46258</v>
+        <v>44814</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16250,7 +16235,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16293,7 +16278,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 18207-2025</t>
+          <t>A 36895-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16307,10 +16292,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45761</v>
+        <v>45874</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16320,11 +16305,6 @@
       <c r="G205" t="inlineStr">
         <is>
           <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I205" t="n">
@@ -16371,7 +16351,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 18211-2025</t>
+          <t>A 38303-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16385,10 +16365,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45761</v>
+        <v>45883</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16400,13 +16380,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16449,7 +16424,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 41905-2022</t>
+          <t>A 22432-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16459,14 +16434,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44830</v>
+        <v>45070</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16480,11 +16455,11 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16527,7 +16502,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 35570-2026</t>
+          <t>A 56529-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16541,10 +16516,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46262</v>
+        <v>44893</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16556,13 +16531,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16605,7 +16575,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 31252-2026</t>
+          <t>A 43114-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16619,10 +16589,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46218</v>
+        <v>45567</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16636,11 +16606,11 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16683,7 +16653,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 35568-2026</t>
+          <t>A 21745-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16697,10 +16667,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46262</v>
+        <v>44708</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16712,13 +16682,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>6.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16761,7 +16726,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 39436-2022</t>
+          <t>A 37399-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16775,10 +16740,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44818</v>
+        <v>45540</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16791,7 +16756,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16834,7 +16799,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 61638-2025</t>
+          <t>A 27080-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16848,10 +16813,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46002</v>
+        <v>44741</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16864,7 +16829,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16907,7 +16872,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 61641-2025</t>
+          <t>A 34855-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16921,10 +16886,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46002</v>
+        <v>46255</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16938,11 +16903,11 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16985,7 +16950,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 36067-2026</t>
+          <t>A 43206-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16999,10 +16964,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46267</v>
+        <v>45567</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17014,13 +16979,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17063,7 +17023,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 36313-2026</t>
+          <t>A 39436-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17077,10 +17037,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46268</v>
+        <v>44818</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17093,7 +17053,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17136,7 +17096,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 17204-2025</t>
+          <t>A 34894-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17150,10 +17110,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45756</v>
+        <v>46259</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17166,7 +17126,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17209,7 +17169,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 35332-2022</t>
+          <t>A 34984-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17223,10 +17183,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44798</v>
+        <v>46258</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17239,7 +17199,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17282,7 +17242,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 62728-2025</t>
+          <t>A 34820-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17296,10 +17256,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46008</v>
+        <v>46255</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17313,11 +17273,11 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17360,7 +17320,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 56467-2024</t>
+          <t>A 34661-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17374,10 +17334,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45625</v>
+        <v>46257</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17390,7 +17350,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17433,7 +17393,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 59320-2024</t>
+          <t>A 34806-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17447,10 +17407,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45637</v>
+        <v>46255</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17464,11 +17424,11 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17511,7 +17471,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 70349-2021</t>
+          <t>A 31252-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17525,10 +17485,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44536</v>
+        <v>46218</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17540,8 +17500,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17584,7 +17549,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 37786-2026</t>
+          <t>A 13036-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17598,10 +17563,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46279</v>
+        <v>44643</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17614,7 +17579,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17657,7 +17622,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 1022-2026</t>
+          <t>A 52031-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17671,10 +17636,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46030</v>
+        <v>45223</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17687,7 +17652,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17730,7 +17695,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 1016-2026</t>
+          <t>A 70349-2021</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17744,10 +17709,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46030</v>
+        <v>44536</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17760,7 +17725,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17803,7 +17768,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 38098-2026</t>
+          <t>A 70350-2021</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17817,10 +17782,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46281</v>
+        <v>44536</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17833,7 +17798,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17876,7 +17841,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 30914-2022</t>
+          <t>A 35568-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17890,10 +17855,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44767</v>
+        <v>46262</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17905,8 +17870,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17949,7 +17919,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 73140-2021</t>
+          <t>A 35570-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17963,10 +17933,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44550</v>
+        <v>46262</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17978,8 +17948,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18022,7 +17997,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 27574-2023</t>
+          <t>A 2755-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18032,14 +18007,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45097</v>
+        <v>45677</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18095,7 +18070,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 53341-2021</t>
+          <t>A 61575-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18109,10 +18084,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44468</v>
+        <v>44916</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18124,8 +18099,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18168,7 +18148,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 4839-2023</t>
+          <t>A 61588-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18182,10 +18162,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44955</v>
+        <v>44916</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18197,8 +18177,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18241,7 +18226,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 3605-2024</t>
+          <t>A 36067-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18255,10 +18240,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45320</v>
+        <v>46267</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18270,8 +18255,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18314,7 +18304,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 4229-2026</t>
+          <t>A 36313-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18328,10 +18318,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46044</v>
+        <v>46268</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18344,7 +18334,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>9.699999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18387,7 +18377,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 21546-2023</t>
+          <t>A 17350-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18401,10 +18391,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45063</v>
+        <v>45035</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18417,7 +18407,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18460,7 +18450,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 4236-2026</t>
+          <t>A 20852-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18474,10 +18464,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46044</v>
+        <v>45777</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18489,8 +18479,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18533,7 +18528,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 15180-2023</t>
+          <t>A 51990-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18547,10 +18542,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45016</v>
+        <v>45607</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18563,7 +18558,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18606,7 +18601,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 859-2025</t>
+          <t>A 41598-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18616,14 +18611,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45665</v>
+        <v>45560</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18635,13 +18630,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I236" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18684,7 +18674,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 52031-2023</t>
+          <t>A 61439-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18698,10 +18688,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45223</v>
+        <v>45646</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18714,7 +18704,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18757,7 +18747,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 30966-2023</t>
+          <t>A 21951-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18767,14 +18757,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45113</v>
+        <v>45784</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18786,8 +18776,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18830,7 +18825,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 68507-2021</t>
+          <t>A 37786-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18844,10 +18839,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44529</v>
+        <v>46279</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18860,7 +18855,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18903,7 +18898,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 38712-2022</t>
+          <t>A 37964-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18913,14 +18908,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44814</v>
+        <v>45544</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18933,7 +18928,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18976,7 +18971,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 43206-2024</t>
+          <t>A 4742-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18990,10 +18985,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45567</v>
+        <v>45688</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19005,8 +19000,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I241" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19049,7 +19049,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 15203-2023</t>
+          <t>A 29566-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19059,14 +19059,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45017</v>
+        <v>45484</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19078,13 +19078,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I242" t="n">
-        <v>0.2</v>
+        <v>21.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19127,7 +19122,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 15204-2023</t>
+          <t>A 38098-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19137,14 +19132,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45017</v>
+        <v>46281</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19156,13 +19151,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19205,7 +19195,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 8690-2023</t>
+          <t>A 32760-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19219,10 +19209,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44978</v>
+        <v>46241</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19235,7 +19225,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19278,7 +19268,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 61995-2022</t>
+          <t>A 32768-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19292,10 +19282,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>44918</v>
+        <v>46241</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19307,13 +19297,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I245" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19356,7 +19341,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 4453-2024</t>
+          <t>A 32771-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19370,10 +19355,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45327</v>
+        <v>46241</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19385,13 +19370,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I246" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19434,7 +19414,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 49121-2024</t>
+          <t>A 10414-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19448,10 +19428,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45594</v>
+        <v>45720</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19464,7 +19444,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19507,7 +19487,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 56475-2024</t>
+          <t>A 32764-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19521,10 +19501,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45625</v>
+        <v>46241</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19537,7 +19517,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19580,7 +19560,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 51990-2024</t>
+          <t>A 53487-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19594,10 +19574,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45607</v>
+        <v>45611</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19610,7 +19590,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19653,7 +19633,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 41598-2024</t>
+          <t>A 8173-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19663,14 +19643,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45560</v>
+        <v>45708</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19683,7 +19663,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19726,7 +19706,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 20852-2025</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19736,14 +19716,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45777</v>
+        <v>45708</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19755,13 +19735,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I251" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19804,7 +19779,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 61439-2024</t>
+          <t>A 20478-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19818,10 +19793,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45646</v>
+        <v>45775</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19833,8 +19808,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I252" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19877,7 +19857,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 21951-2025</t>
+          <t>A 29659-2025</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19891,10 +19871,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45784</v>
+        <v>45825</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19906,13 +19886,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I253" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19955,7 +19930,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 37964-2024</t>
+          <t>A 20851-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19965,14 +19940,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45544</v>
+        <v>45777</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19984,8 +19959,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I254" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20028,7 +20008,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 4742-2025</t>
+          <t>A 20854-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20042,10 +20022,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45688</v>
+        <v>45777</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20059,11 +20039,11 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I255" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20106,7 +20086,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 29566-2024</t>
+          <t>A 20853-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20120,10 +20100,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45484</v>
+        <v>45777</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20135,8 +20115,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I256" t="n">
-        <v>21.3</v>
+        <v>2.4</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20179,7 +20164,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 53487-2024</t>
+          <t>A 30527-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20193,10 +20178,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45611</v>
+        <v>45831</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20209,7 +20194,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20252,7 +20237,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 10414-2025</t>
+          <t>A 32712-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20266,10 +20251,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45720</v>
+        <v>45839</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20281,8 +20266,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I258" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20325,7 +20315,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 35909-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20335,14 +20325,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45708</v>
+        <v>45862</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20354,8 +20344,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I259" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20398,7 +20393,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 8173-2025</t>
+          <t>A 35899-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20408,14 +20403,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45708</v>
+        <v>45862</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20427,8 +20422,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I260" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20471,7 +20471,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>S 2061-2022</t>
+          <t>S 2321-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20485,10 +20485,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>44672</v>
+        <v>45105</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20544,7 +20544,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>S 2321-2023</t>
+          <t>S 4661-2022</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20554,14 +20554,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45105</v>
+        <v>44795</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>0.7</v>
+        <v>43.6</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20617,7 +20617,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>S 4661-2022</t>
+          <t>S 396-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20631,10 +20631,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>44795</v>
+        <v>44959</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>43.6</v>
+        <v>78.8</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20690,7 +20690,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>S 396-2023</t>
+          <t>S 2061-2022</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20700,14 +20700,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>44959</v>
+        <v>44672</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>78.8</v>
+        <v>1.6</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20780,7 +20780,7 @@
         <v>45056</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44959</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44893</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>44893</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45072</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45193</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45386</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>44795</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45688</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45817</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45817</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>46013</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46013</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>46065</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>46154</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>

--- a/Översikt LESSEBO.xlsx
+++ b/Översikt LESSEBO.xlsx
@@ -601,7 +601,7 @@
         <v>45349</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>46035</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45954</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45954</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45954</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45267</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>46176</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45072</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45670</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>45625</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>45954</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>45954</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44510</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44518</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44865</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>44586</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44727</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44510</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44842</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>44491</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44529</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44693</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44508</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44522</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44743</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>44460</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>45518</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45625</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>45625</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>44936</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>45459</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45113</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>45637</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45710</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45017</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>45017</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45568</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>45665</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>44846</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>45016</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>44973</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>45037</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>44767</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>44693</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>44865</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>45107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>44830</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>44587</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>45036</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>44910</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>45013</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>44550</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>45111</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>45679</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>45219</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>45225</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45436</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>45625</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>45625</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>45784</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>45322</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>45670</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>45364</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>45233</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>45219</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>45671</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>44978</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>45708</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>45891</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>45890</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>45891</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>45777</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44896</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45625</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45288</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45862</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45931</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45058</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>45862</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>45756</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>45912</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>44741</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>45594</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>45918</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>45918</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>45587</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>45671</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>45219</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>44918</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45684</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>45934</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>45322</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>45934</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>46147</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>45758</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>44867</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45938</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>45775</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>45587</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>45952</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>45327</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>45954</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>45954</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>45954</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45954</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45327</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45215</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>45954</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>45958</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>45551</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>45036</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>45938</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>45173</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>46154</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>45427</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>44468</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>46154</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>46157</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>45756</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>46157</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>46157</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>46157</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>46157</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>46157</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>46157</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>46157</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>46157</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>45202</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45775</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>45775</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>45775</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45776</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>46002</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>46002</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>46008</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>45097</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>44955</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>46169</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>45741</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>46169</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>46169</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>46169</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>45493</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45456</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>45282</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44830</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45161</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>46030</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>46030</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>44798</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>46044</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>46044</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>45058</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45737</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>46175</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45474</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45253</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44586</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>46065</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>45761</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>45761</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45299</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>46076</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>46076</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>46076</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45126</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>45775</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45637</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45741</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45587</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>44509</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>46094</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44818</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>46191</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>46191</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>45775</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45376</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45398</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>44589</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>46127</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45320</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>45139</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>46127</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>46127</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>45063</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44664</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45772</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>46205</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>46205</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>44814</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>45874</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>45883</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>45070</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44893</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45567</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>44708</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>45540</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44741</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>46255</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>45567</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>44818</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>46259</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>46258</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>46255</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>46257</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>46255</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>46218</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>44643</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>45223</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>44536</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>44536</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>46262</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>46262</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45677</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44916</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>44916</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>46267</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>46268</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45035</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45777</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>45607</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>45560</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45646</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45784</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>46279</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45544</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>45688</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45484</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>46281</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>46241</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>46241</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>46241</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45720</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>46241</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45611</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45708</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45708</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45775</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45825</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>45777</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>45777</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45777</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>45831</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45839</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45862</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45862</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>45105</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>44795</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>44959</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>44672</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45056</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>44959</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44893</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>44893</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45072</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45193</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45386</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>44795</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45688</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45817</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45817</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>46013</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46013</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>46065</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>46154</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>

--- a/Översikt LESSEBO.xlsx
+++ b/Översikt LESSEBO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE279"/>
+  <dimension ref="A1:AE278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45349</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>46035</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45954</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45954</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45954</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45267</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>46176</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45072</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45670</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>45625</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>45954</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>45954</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44510</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44518</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44865</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 3741-2022</t>
+          <t>A 24680-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44586</v>
+        <v>44727</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2892,13 +2892,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2941,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 24680-2022</t>
+          <t>A 3741-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2955,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44727</v>
+        <v>44586</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2970,8 +2965,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>44510</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44842</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>44491</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44529</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44693</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44508</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44522</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44743</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 51006-2021</t>
+          <t>A 33240-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44460</v>
+        <v>45518</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>7.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33240-2024</t>
+          <t>A 56456-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45518</v>
+        <v>45625</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.4</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27713-2022</t>
+          <t>A 56459-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44743</v>
+        <v>45625</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56456-2024</t>
+          <t>A 68507-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45625</v>
+        <v>44529</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56459-2024</t>
+          <t>A 24478-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45625</v>
+        <v>45459</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 68507-2021</t>
+          <t>A 1367-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44529</v>
+        <v>44936</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1367-2023</t>
+          <t>A 30966-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44936</v>
+        <v>45113</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24478-2024</t>
+          <t>A 59320-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45459</v>
+        <v>45637</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4216,8 +4216,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30966-2023</t>
+          <t>A 15203-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4270,14 +4275,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45113</v>
+        <v>45017</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4289,8 +4294,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>7</v>
+        <v>0.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4333,7 +4343,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59320-2024</t>
+          <t>A 15204-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4343,14 +4353,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45637</v>
+        <v>45017</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4378,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4428,7 +4438,7 @@
         <v>45710</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4484,7 +4494,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 15203-2023</t>
+          <t>A 43453-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4494,14 +4504,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45017</v>
+        <v>45568</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4513,13 +4523,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4562,7 +4567,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15204-2023</t>
+          <t>A 859-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4572,14 +4577,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45017</v>
+        <v>45665</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4597,7 +4602,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4640,7 +4645,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 43453-2024</t>
+          <t>A 45838-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4654,10 +4659,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45568</v>
+        <v>44846</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4670,7 +4675,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4713,7 +4718,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 859-2025</t>
+          <t>A 27713-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4723,14 +4728,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45665</v>
+        <v>44743</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4742,13 +4747,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4791,7 +4791,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45838-2022</t>
+          <t>A 15180-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44846</v>
+        <v>45016</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15180-2023</t>
+          <t>A 7957-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4878,10 +4878,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45016</v>
+        <v>44973</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4937,7 +4937,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7957-2023</t>
+          <t>A 17836-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44973</v>
+        <v>45037</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5010,7 +5010,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17836-2023</t>
+          <t>A 30914-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45037</v>
+        <v>44767</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 30914-2022</t>
+          <t>A 19501-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44767</v>
+        <v>44693</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5156,7 +5156,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 19501-2022</t>
+          <t>A 50154-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44693</v>
+        <v>44865</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50154-2022</t>
+          <t>A 29767-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44865</v>
+        <v>45107</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29767-2023</t>
+          <t>A 41905-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5316,10 +5316,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45107</v>
+        <v>44830</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5331,8 +5331,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5375,7 +5380,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 41905-2022</t>
+          <t>A 3955-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5389,10 +5394,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44830</v>
+        <v>44587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5404,13 +5409,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3955-2022</t>
+          <t>A 60358-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44587</v>
+        <v>44910</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17517-2023</t>
+          <t>A 20541-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45036</v>
+        <v>45436</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5599,7 +5599,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 60358-2022</t>
+          <t>A 64635-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44910</v>
+        <v>45281</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5672,7 +5672,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 64635-2023</t>
+          <t>A 14584-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45281</v>
+        <v>45013</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5745,7 +5745,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14584-2023</t>
+          <t>A 17517-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5759,10 +5759,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45013</v>
+        <v>45036</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5835,7 +5835,7 @@
         <v>44550</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>45111</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3239-2025</t>
+          <t>A 10047-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45679</v>
+        <v>45364</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5995,11 +5995,11 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6042,7 +6042,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 51191-2023</t>
+          <t>A 36895-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45219</v>
+        <v>45874</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6115,7 +6115,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52525-2023</t>
+          <t>A 3239-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6129,10 +6129,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45225</v>
+        <v>45679</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6144,8 +6144,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6188,7 +6193,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20541-2024</t>
+          <t>A 38303-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6202,10 +6207,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45436</v>
+        <v>45883</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6218,7 +6223,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6261,7 +6266,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 56467-2024</t>
+          <t>A 52525-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6275,10 +6280,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45625</v>
+        <v>45225</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6291,7 +6296,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6334,7 +6339,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 56471-2024</t>
+          <t>A 39884-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6348,10 +6353,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45625</v>
+        <v>45891</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6364,7 +6369,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6407,7 +6412,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21917-2025</t>
+          <t>A 39549-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6421,10 +6426,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45784</v>
+        <v>45890</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6437,7 +6442,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6480,7 +6485,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3876-2024</t>
+          <t>A 56471-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6494,10 +6499,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45322</v>
+        <v>45625</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6510,7 +6515,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6553,7 +6558,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 1490-2025</t>
+          <t>A 39750-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6563,14 +6568,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45670</v>
+        <v>45891</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6582,13 +6587,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6631,7 +6631,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10047-2024</t>
+          <t>A 51191-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45364</v>
+        <v>45219</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6660,13 +6660,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6709,7 +6704,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 54541-2023</t>
+          <t>A 56467-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6719,14 +6714,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45233</v>
+        <v>45625</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6738,13 +6733,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6787,7 +6777,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 51189-2023</t>
+          <t>A 21917-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6801,10 +6791,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45219</v>
+        <v>45784</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6817,7 +6807,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6860,7 +6850,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 1894-2025</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6870,14 +6860,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45671</v>
+        <v>45708</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6890,7 +6880,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6933,7 +6923,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8690-2023</t>
+          <t>A 35904-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6947,10 +6937,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44978</v>
+        <v>45862</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6962,8 +6952,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7006,7 +7001,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 1894-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7016,14 +7011,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45708</v>
+        <v>45671</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7036,7 +7031,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7079,7 +7074,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 39884-2025</t>
+          <t>A 20855-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7093,10 +7088,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45891</v>
+        <v>45777</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7108,8 +7103,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7152,7 +7152,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 39549-2025</t>
+          <t>A 3876-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7166,10 +7166,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45890</v>
+        <v>45322</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 39750-2025</t>
+          <t>A 1490-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7235,14 +7235,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45891</v>
+        <v>45670</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7254,8 +7254,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7298,7 +7303,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20855-2025</t>
+          <t>A 43809-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7312,10 +7317,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45777</v>
+        <v>45912</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7327,13 +7332,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 57519-2022</t>
+          <t>A 47693-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44896</v>
+        <v>45931</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>6.6</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 56475-2024</t>
+          <t>A 44904-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45625</v>
+        <v>45918</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7522,7 +7522,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 65137-2023</t>
+          <t>A 44899-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45288</v>
+        <v>45918</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7595,7 +7595,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 35904-2025</t>
+          <t>A 54541-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7605,14 +7605,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45862</v>
+        <v>45233</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7673,7 +7673,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47693-2025</t>
+          <t>A 51189-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7687,10 +7687,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45931</v>
+        <v>45219</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7746,7 +7746,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20824-2023</t>
+          <t>A 8690-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45058</v>
+        <v>44978</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7836,7 +7836,7 @@
         <v>45862</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17204-2025</t>
+          <t>A 57519-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7911,10 +7911,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45756</v>
+        <v>44896</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7970,7 +7970,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 43809-2025</t>
+          <t>A 56475-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45912</v>
+        <v>45625</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8043,7 +8043,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 27191-2022</t>
+          <t>A 65137-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44741</v>
+        <v>45288</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8116,7 +8116,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 49121-2024</t>
+          <t>A 48429-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45594</v>
+        <v>45934</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8189,7 +8189,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 44904-2025</t>
+          <t>A 48433-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45918</v>
+        <v>45934</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8262,7 +8262,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 44899-2025</t>
+          <t>A 21311-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45918</v>
+        <v>46147</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8335,7 +8335,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 47396-2024</t>
+          <t>A 17729-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45587</v>
+        <v>45758</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8364,8 +8364,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8408,7 +8413,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 1897-2025</t>
+          <t>A 20824-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8422,10 +8427,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45671</v>
+        <v>45058</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8438,7 +8443,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8481,7 +8486,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 51175-2023</t>
+          <t>A 49298-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8495,10 +8500,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45219</v>
+        <v>45938</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8511,7 +8516,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8554,7 +8559,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61995-2022</t>
+          <t>A 20443-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8568,10 +8573,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44918</v>
+        <v>45775</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8585,11 +8590,11 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8632,7 +8637,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 4107-2025</t>
+          <t>A 17204-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8646,10 +8651,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45684</v>
+        <v>45756</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8662,7 +8667,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8705,7 +8710,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 48429-2025</t>
+          <t>A 27191-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8719,10 +8724,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45934</v>
+        <v>44741</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8735,7 +8740,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8778,7 +8783,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 3875-2024</t>
+          <t>A 49121-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8792,10 +8797,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45322</v>
+        <v>45594</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8808,7 +8813,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8851,7 +8856,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 48433-2025</t>
+          <t>A 22318-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8865,10 +8870,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45934</v>
+        <v>46154</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8881,7 +8886,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8924,7 +8929,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 21311-2026</t>
+          <t>A 22423-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8934,14 +8939,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46147</v>
+        <v>46154</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8954,7 +8959,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8997,7 +9002,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 17729-2025</t>
+          <t>A 22718-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9011,10 +9016,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45758</v>
+        <v>46157</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9032,7 +9037,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9075,7 +9080,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 50892-2022</t>
+          <t>A 22756-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9089,10 +9094,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44867</v>
+        <v>46157</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9104,8 +9109,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9148,7 +9158,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 49298-2025</t>
+          <t>A 22758-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9162,10 +9172,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45938</v>
+        <v>46157</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9177,8 +9187,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9221,7 +9236,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 20443-2025</t>
+          <t>A 22766-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9235,10 +9250,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45775</v>
+        <v>46157</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9256,7 +9271,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9299,7 +9314,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 47402-2024</t>
+          <t>A 52031-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9313,10 +9328,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45587</v>
+        <v>45952</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9329,7 +9344,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9372,7 +9387,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 52031-2025</t>
+          <t>A 47396-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9386,10 +9401,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45952</v>
+        <v>45587</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9402,7 +9417,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9445,7 +9460,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 4465-2024</t>
+          <t>A 22719-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9459,10 +9474,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45327</v>
+        <v>46157</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9474,8 +9489,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9518,7 +9538,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 52537-2025</t>
+          <t>A 22720-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9532,10 +9552,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45954</v>
+        <v>46157</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9553,7 +9573,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9596,7 +9616,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 52531-2025</t>
+          <t>A 22764-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9610,10 +9630,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45954</v>
+        <v>46157</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9631,7 +9651,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9674,7 +9694,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 52532-2025</t>
+          <t>A 22768-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9688,10 +9708,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45954</v>
+        <v>46157</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9709,7 +9729,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9752,7 +9772,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 52546-2025</t>
+          <t>A 22770-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9766,10 +9786,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45954</v>
+        <v>46157</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9787,7 +9807,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9830,7 +9850,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 4453-2024</t>
+          <t>A 22723-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9844,10 +9864,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45327</v>
+        <v>46157</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9861,11 +9881,11 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9908,7 +9928,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 50162-2023</t>
+          <t>A 1897-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9918,14 +9938,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45215</v>
+        <v>45671</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9937,13 +9957,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9986,7 +10001,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 52534-2025</t>
+          <t>A 20485-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10000,10 +10015,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45954</v>
+        <v>45775</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10021,7 +10036,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10064,7 +10079,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 53122-2025</t>
+          <t>A 52537-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10078,10 +10093,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45958</v>
+        <v>45954</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10093,8 +10108,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10137,7 +10157,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 39389-2024</t>
+          <t>A 52531-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10151,10 +10171,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45551</v>
+        <v>45954</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10166,8 +10186,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10210,7 +10235,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 17552-2023</t>
+          <t>A 52532-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10224,10 +10249,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45036</v>
+        <v>45954</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10239,8 +10264,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10283,7 +10313,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 49295-2025</t>
+          <t>A 52546-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10297,10 +10327,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45938</v>
+        <v>45954</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10312,8 +10342,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10356,7 +10391,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 40912-2023</t>
+          <t>A 52534-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10370,10 +10405,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45173</v>
+        <v>45954</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10385,8 +10420,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10429,7 +10469,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 22318-2026</t>
+          <t>A 53122-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10443,10 +10483,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46154</v>
+        <v>45958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10459,7 +10499,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10502,7 +10542,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 18968-2024</t>
+          <t>A 51175-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10516,10 +10556,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45427</v>
+        <v>45219</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10532,7 +10572,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10575,7 +10615,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 53341-2021</t>
+          <t>A 20431-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10589,10 +10629,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44468</v>
+        <v>45775</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10604,8 +10644,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10648,7 +10693,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 22423-2026</t>
+          <t>A 20435-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10658,14 +10703,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46154</v>
+        <v>45775</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10677,8 +10722,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10721,7 +10771,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 22718-2026</t>
+          <t>A 61995-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10735,10 +10785,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46157</v>
+        <v>44918</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10752,11 +10802,11 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10799,7 +10849,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 17203-2025</t>
+          <t>A 20681-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10813,10 +10863,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45756</v>
+        <v>45776</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10828,8 +10878,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10872,7 +10927,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 22756-2026</t>
+          <t>A 4107-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10886,10 +10941,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46157</v>
+        <v>45684</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10901,13 +10956,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>8.699999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10950,7 +11000,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 22758-2026</t>
+          <t>A 49295-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10964,10 +11014,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46157</v>
+        <v>45938</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10979,13 +11029,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11028,7 +11073,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 22766-2026</t>
+          <t>A 3875-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11042,10 +11087,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46157</v>
+        <v>45322</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11057,13 +11102,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11106,7 +11146,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 22719-2026</t>
+          <t>A 50892-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11120,10 +11160,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46157</v>
+        <v>44867</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11135,13 +11175,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11184,7 +11219,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 22720-2026</t>
+          <t>A 47402-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11198,10 +11233,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46157</v>
+        <v>45587</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11213,13 +11248,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11262,7 +11292,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 22764-2026</t>
+          <t>A 24275-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11276,10 +11306,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11291,13 +11321,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11340,7 +11365,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 22768-2026</t>
+          <t>A 24271-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11354,10 +11379,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11369,13 +11394,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11418,7 +11438,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 22770-2026</t>
+          <t>A 24272-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11432,10 +11452,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11447,13 +11467,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11496,7 +11511,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 22723-2026</t>
+          <t>A 24269-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11510,10 +11525,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11525,13 +11540,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11574,7 +11584,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 48639-2023</t>
+          <t>A 4465-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11588,10 +11598,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45202</v>
+        <v>45327</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11604,7 +11614,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11647,7 +11657,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 20485-2025</t>
+          <t>A 4453-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11661,10 +11671,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45775</v>
+        <v>45327</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11678,11 +11688,11 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11725,7 +11735,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 20431-2025</t>
+          <t>A 50162-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11735,14 +11745,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45775</v>
+        <v>45215</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11760,7 +11770,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11803,7 +11813,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 20435-2025</t>
+          <t>A 39389-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11817,10 +11827,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45775</v>
+        <v>45551</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11832,13 +11842,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11881,7 +11886,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 20681-2025</t>
+          <t>A 61638-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11895,10 +11900,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45776</v>
+        <v>46002</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11910,13 +11915,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11959,7 +11959,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 61638-2025</t>
+          <t>A 61641-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11976,7 +11976,7 @@
         <v>46002</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11988,8 +11988,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>6.2</v>
+        <v>1.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12032,7 +12037,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 61641-2025</t>
+          <t>A 25169-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12046,10 +12051,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46002</v>
+        <v>46175</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12059,11 +12064,6 @@
       <c r="G148" t="inlineStr">
         <is>
           <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -12110,7 +12110,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 62728-2025</t>
+          <t>A 17552-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12124,10 +12124,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46008</v>
+        <v>45036</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12139,13 +12139,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12188,7 +12183,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 27574-2023</t>
+          <t>A 62728-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12202,10 +12197,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45097</v>
+        <v>46008</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12217,8 +12212,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12261,7 +12261,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 4839-2023</t>
+          <t>A 40912-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12275,10 +12275,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44955</v>
+        <v>45173</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12334,7 +12334,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 24275-2026</t>
+          <t>A 18968-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12348,10 +12348,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46169</v>
+        <v>45427</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12407,7 +12407,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 14549-2025</t>
+          <t>A 53341-2021</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45741</v>
+        <v>44468</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12480,7 +12480,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 24271-2026</t>
+          <t>A 1022-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12494,10 +12494,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46169</v>
+        <v>46030</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12553,7 +12553,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24272-2026</t>
+          <t>A 1016-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46169</v>
+        <v>46030</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12626,7 +12626,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 24269-2026</t>
+          <t>A 17203-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12640,10 +12640,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46169</v>
+        <v>45756</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12699,7 +12699,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 30600-2024</t>
+          <t>A 48639-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12713,10 +12713,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45493</v>
+        <v>45202</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12772,7 +12772,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 24171-2024</t>
+          <t>A 20441-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12786,10 +12786,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45456</v>
+        <v>45775</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12801,8 +12801,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12845,7 +12850,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 64865-2023</t>
+          <t>A 59321-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12859,10 +12864,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45282</v>
+        <v>45637</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12880,7 +12885,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12923,7 +12928,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 41900-2022</t>
+          <t>A 14551-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12937,10 +12942,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44830</v>
+        <v>45741</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12952,13 +12957,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>5.2</v>
+        <v>0.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13001,7 +13001,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 38227-2023</t>
+          <t>A 4236-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13015,10 +13015,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45161</v>
+        <v>46044</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13074,7 +13074,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 1022-2026</t>
+          <t>A 4229-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13088,10 +13088,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46030</v>
+        <v>46044</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13147,7 +13147,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 1016-2026</t>
+          <t>A 27870-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13161,10 +13161,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46030</v>
+        <v>46191</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13220,7 +13220,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 35332-2022</t>
+          <t>A 27873-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13234,10 +13234,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44798</v>
+        <v>46191</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13293,7 +13293,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 4236-2026</t>
+          <t>A 20480-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13307,10 +13307,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46044</v>
+        <v>45775</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13322,8 +13322,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13366,7 +13371,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 4229-2026</t>
+          <t>A 8438-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13380,10 +13385,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46044</v>
+        <v>46065</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13395,8 +13400,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>9.699999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13439,7 +13449,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 20825-2023</t>
+          <t>A 10189-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13453,10 +13463,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45058</v>
+        <v>46076</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13469,7 +13479,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13512,7 +13522,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 13751-2025</t>
+          <t>A 27574-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13526,10 +13536,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45737</v>
+        <v>45097</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13542,7 +13552,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13585,7 +13595,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 25169-2026</t>
+          <t>A 4839-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13599,10 +13609,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46175</v>
+        <v>44955</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13615,7 +13625,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13658,7 +13668,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 27405-2024</t>
+          <t>A 10286-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13672,10 +13682,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45474</v>
+        <v>46076</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13688,7 +13698,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13731,7 +13741,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 59173-2023</t>
+          <t>A 10185-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13745,10 +13755,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45253</v>
+        <v>46076</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13761,7 +13771,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13804,7 +13814,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 3714-2022</t>
+          <t>A 14549-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13818,10 +13828,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44586</v>
+        <v>45741</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13833,13 +13843,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13882,7 +13887,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 8438-2026</t>
+          <t>A 30600-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13896,10 +13901,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46065</v>
+        <v>45493</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13911,13 +13916,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13960,7 +13960,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 18207-2025</t>
+          <t>A 24171-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13974,10 +13974,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45761</v>
+        <v>45456</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13989,13 +13989,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14038,7 +14033,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 18211-2025</t>
+          <t>A 64865-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14052,10 +14047,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45761</v>
+        <v>45282</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14073,7 +14068,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14116,7 +14111,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 642-2024</t>
+          <t>A 41900-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14126,14 +14121,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45299</v>
+        <v>44830</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14151,7 +14146,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14194,7 +14189,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 10189-2026</t>
+          <t>A 38227-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14208,10 +14203,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46076</v>
+        <v>45161</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14224,7 +14219,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14267,7 +14262,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 10286-2026</t>
+          <t>A 13347-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14281,10 +14276,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46076</v>
+        <v>46094</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14296,8 +14291,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14340,7 +14340,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 10185-2026</t>
+          <t>A 30822-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14354,10 +14354,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46076</v>
+        <v>46205</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14413,7 +14413,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 33076-2023</t>
+          <t>A 30826-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14423,14 +14423,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45126</v>
+        <v>46205</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14486,7 +14486,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 20441-2025</t>
+          <t>A 35332-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14500,10 +14500,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45775</v>
+        <v>44798</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14515,13 +14515,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14564,7 +14559,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 59321-2024</t>
+          <t>A 20825-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14578,10 +14573,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45637</v>
+        <v>45058</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14593,13 +14588,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14642,7 +14632,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 14551-2025</t>
+          <t>A 13751-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14656,10 +14646,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45741</v>
+        <v>45737</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14672,7 +14662,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14715,7 +14705,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 47386-2024</t>
+          <t>A 27405-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14729,10 +14719,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45587</v>
+        <v>45474</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14745,7 +14735,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14788,7 +14778,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 63927-2021</t>
+          <t>A 59173-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14802,10 +14792,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44509</v>
+        <v>45253</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14817,13 +14807,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14866,7 +14851,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 13347-2026</t>
+          <t>A 3714-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14880,10 +14865,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46094</v>
+        <v>44586</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14901,7 +14886,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14944,7 +14929,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 39603-2022</t>
+          <t>A 18625-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14958,10 +14943,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44818</v>
+        <v>46127</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14974,7 +14959,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15017,7 +15002,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 27870-2026</t>
+          <t>A 18464-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15031,10 +15016,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46191</v>
+        <v>46127</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15046,8 +15031,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>0.8</v>
+        <v>14.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15090,7 +15080,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 27873-2026</t>
+          <t>A 18466-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15104,10 +15094,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46191</v>
+        <v>46127</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15119,8 +15109,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.8</v>
+        <v>7.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15163,7 +15158,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 20480-2025</t>
+          <t>A 18207-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15177,10 +15172,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45775</v>
+        <v>45761</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15198,7 +15193,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15241,7 +15236,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 11843-2024</t>
+          <t>A 18211-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15255,10 +15250,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45376</v>
+        <v>45761</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15272,11 +15267,11 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15319,7 +15314,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 14940-2024</t>
+          <t>A 642-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15329,14 +15324,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45398</v>
+        <v>45299</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15348,8 +15343,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15392,7 +15392,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 4413-2022</t>
+          <t>A 20056-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15406,10 +15406,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44589</v>
+        <v>45772</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15465,7 +15465,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 18625-2026</t>
+          <t>A 33076-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15475,14 +15475,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46127</v>
+        <v>45126</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15538,7 +15538,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 3605-2024</t>
+          <t>A 47386-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15552,10 +15552,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45320</v>
+        <v>45587</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15611,7 +15611,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 34386-2023</t>
+          <t>A 63927-2021</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15625,10 +15625,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45139</v>
+        <v>44509</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15640,8 +15640,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15684,7 +15689,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 18464-2026</t>
+          <t>A 39603-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15698,10 +15703,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46127</v>
+        <v>44818</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15713,13 +15718,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>14.2</v>
+        <v>1.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15762,7 +15762,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 18466-2026</t>
+          <t>A 34855-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15776,10 +15776,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46127</v>
+        <v>46255</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15793,11 +15793,11 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>7.9</v>
+        <v>2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15840,7 +15840,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 21546-2023</t>
+          <t>A 34894-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15854,10 +15854,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45063</v>
+        <v>46259</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 15864-2022</t>
+          <t>A 34984-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15927,10 +15927,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44664</v>
+        <v>46258</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15986,7 +15986,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 20056-2025</t>
+          <t>A 34820-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16000,10 +16000,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45772</v>
+        <v>46255</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16015,8 +16015,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16059,7 +16064,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 30822-2026</t>
+          <t>A 11843-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16073,10 +16078,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46205</v>
+        <v>45376</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16088,8 +16093,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16132,7 +16142,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 30826-2026</t>
+          <t>A 14940-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16146,10 +16156,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46205</v>
+        <v>45398</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16162,7 +16172,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16205,7 +16215,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 38712-2022</t>
+          <t>A 34661-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16219,10 +16229,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44814</v>
+        <v>46257</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16235,7 +16245,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16278,7 +16288,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 36895-2025</t>
+          <t>A 34806-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16292,10 +16302,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45874</v>
+        <v>46255</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16307,8 +16317,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16351,7 +16366,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 38303-2025</t>
+          <t>A 31252-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16365,10 +16380,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45883</v>
+        <v>46218</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16380,8 +16395,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16424,7 +16444,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 22432-2023</t>
+          <t>A 4413-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16434,14 +16454,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45070</v>
+        <v>44589</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16453,13 +16473,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16502,7 +16517,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 56529-2022</t>
+          <t>A 35568-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16516,10 +16531,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44893</v>
+        <v>46262</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16531,8 +16546,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>9</v>
+        <v>6.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16575,7 +16595,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 43114-2024</t>
+          <t>A 35570-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16589,10 +16609,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45567</v>
+        <v>46262</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16610,7 +16630,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16653,7 +16673,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 21745-2022</t>
+          <t>A 3605-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16667,10 +16687,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44708</v>
+        <v>45320</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16683,7 +16703,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>9.699999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16726,7 +16746,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 37399-2024</t>
+          <t>A 34386-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16740,10 +16760,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45540</v>
+        <v>45139</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16756,7 +16776,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16799,7 +16819,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 27080-2022</t>
+          <t>A 21546-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16813,10 +16833,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44741</v>
+        <v>45063</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16829,7 +16849,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16872,7 +16892,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 34855-2026</t>
+          <t>A 36067-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16886,10 +16906,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46255</v>
+        <v>46267</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16903,11 +16923,11 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16950,7 +16970,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 43206-2024</t>
+          <t>A 15864-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16964,10 +16984,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45567</v>
+        <v>44664</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16980,7 +17000,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17023,7 +17043,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 39436-2022</t>
+          <t>A 36313-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17037,10 +17057,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44818</v>
+        <v>46268</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17053,7 +17073,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17096,7 +17116,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 34894-2026</t>
+          <t>A 38712-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17110,10 +17130,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46259</v>
+        <v>44814</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17126,7 +17146,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17169,7 +17189,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 34984-2026</t>
+          <t>A 22432-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17179,14 +17199,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46258</v>
+        <v>45070</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17198,8 +17218,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17242,7 +17267,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 34820-2026</t>
+          <t>A 56529-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17256,10 +17281,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46255</v>
+        <v>44893</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17271,13 +17296,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>0.6</v>
+        <v>9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17320,7 +17340,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 34661-2026</t>
+          <t>A 43114-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17334,10 +17354,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46257</v>
+        <v>45567</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17349,8 +17369,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17393,7 +17418,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 34806-2026</t>
+          <t>A 37786-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17407,10 +17432,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46255</v>
+        <v>46279</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17422,13 +17447,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17471,7 +17491,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 31252-2026</t>
+          <t>A 21745-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17485,10 +17505,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46218</v>
+        <v>44708</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17500,13 +17520,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>2.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17549,7 +17564,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 13036-2022</t>
+          <t>A 37399-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17563,10 +17578,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44643</v>
+        <v>45540</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17579,7 +17594,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17622,7 +17637,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 52031-2023</t>
+          <t>A 27080-2022</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17636,10 +17651,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45223</v>
+        <v>44741</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17652,7 +17667,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17695,7 +17710,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 70349-2021</t>
+          <t>A 38098-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17709,10 +17724,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44536</v>
+        <v>46281</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17725,7 +17740,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17768,7 +17783,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 70350-2021</t>
+          <t>A 43206-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17782,10 +17797,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44536</v>
+        <v>45567</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17798,7 +17813,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17841,7 +17856,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 35568-2026</t>
+          <t>A 39436-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17855,10 +17870,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46262</v>
+        <v>44818</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17870,13 +17885,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>6.9</v>
+        <v>2.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17919,7 +17929,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 35570-2026</t>
+          <t>A 13036-2022</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17933,10 +17943,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46262</v>
+        <v>44643</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17948,13 +17958,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17997,7 +18002,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 2755-2025</t>
+          <t>A 52031-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18007,14 +18012,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45677</v>
+        <v>45223</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18027,7 +18032,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18070,7 +18075,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 61575-2022</t>
+          <t>A 70349-2021</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18084,10 +18089,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44916</v>
+        <v>44536</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18099,13 +18104,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18148,7 +18148,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 61588-2022</t>
+          <t>A 70350-2021</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18162,10 +18162,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44916</v>
+        <v>44536</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18177,13 +18177,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18226,7 +18221,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 36067-2026</t>
+          <t>A 32764-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18240,10 +18235,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46267</v>
+        <v>46241</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18255,13 +18250,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18304,7 +18294,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 36313-2026</t>
+          <t>A 32768-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18318,10 +18308,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46268</v>
+        <v>46241</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18334,7 +18324,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18377,7 +18367,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 17350-2023</t>
+          <t>A 32771-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18391,10 +18381,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45035</v>
+        <v>46241</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18407,7 +18397,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18450,7 +18440,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 20852-2025</t>
+          <t>A 2755-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18460,14 +18450,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45777</v>
+        <v>45677</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18477,11 +18467,6 @@
       <c r="G234" t="inlineStr">
         <is>
           <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I234" t="n">
@@ -18528,7 +18513,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 51990-2024</t>
+          <t>A 32760-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18542,10 +18527,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45607</v>
+        <v>46241</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18558,7 +18543,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18601,7 +18586,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 41598-2024</t>
+          <t>A 61575-2022</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18615,10 +18600,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45560</v>
+        <v>44916</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18630,8 +18615,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I236" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18674,7 +18664,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 61439-2024</t>
+          <t>A 61588-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18688,10 +18678,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45646</v>
+        <v>44916</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18703,8 +18693,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18747,7 +18742,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 21951-2025</t>
+          <t>A 17350-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18757,14 +18752,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45784</v>
+        <v>45035</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18776,13 +18771,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I238" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18825,7 +18815,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 37786-2026</t>
+          <t>A 20852-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18839,10 +18829,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46279</v>
+        <v>45777</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18854,8 +18844,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I239" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18898,7 +18893,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 37964-2024</t>
+          <t>A 51990-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18908,14 +18903,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45544</v>
+        <v>45607</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18928,7 +18923,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18971,7 +18966,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 4742-2025</t>
+          <t>A 41598-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18985,10 +18980,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45688</v>
+        <v>45560</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19000,13 +18995,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I241" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19049,7 +19039,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 29566-2024</t>
+          <t>A 61439-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19063,10 +19053,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45484</v>
+        <v>45646</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19079,7 +19069,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>21.3</v>
+        <v>4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19122,7 +19112,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 38098-2026</t>
+          <t>A 21951-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19132,14 +19122,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46281</v>
+        <v>45784</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19151,8 +19141,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I243" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19195,7 +19190,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 32760-2026</t>
+          <t>A 37964-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19205,14 +19200,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46241</v>
+        <v>45544</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19225,7 +19220,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19268,7 +19263,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 32768-2026</t>
+          <t>A 4742-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19282,10 +19277,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46241</v>
+        <v>45688</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19297,8 +19292,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I245" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19341,7 +19341,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 32771-2026</t>
+          <t>A 29566-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19355,10 +19355,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46241</v>
+        <v>45484</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.5</v>
+        <v>21.3</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19431,7 +19431,7 @@
         <v>45720</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 32764-2026</t>
+          <t>A 53487-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19501,10 +19501,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46241</v>
+        <v>45611</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19560,7 +19560,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 53487-2024</t>
+          <t>A 8173-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19570,14 +19570,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45611</v>
+        <v>45708</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 8173-2025</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19650,7 +19650,7 @@
         <v>45708</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19706,7 +19706,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 20478-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19716,14 +19716,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45708</v>
+        <v>45775</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19735,8 +19735,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I251" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19779,7 +19784,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 20478-2025</t>
+          <t>A 29659-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19789,14 +19794,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45775</v>
+        <v>45825</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19808,13 +19813,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I252" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 29659-2025</t>
+          <t>A 20851-2025</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19867,14 +19867,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45825</v>
+        <v>45777</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19886,8 +19886,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I253" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19930,7 +19935,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 20851-2025</t>
+          <t>A 20854-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19947,7 +19952,7 @@
         <v>45777</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19965,7 +19970,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20008,7 +20013,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 20854-2025</t>
+          <t>A 20853-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20025,7 +20030,7 @@
         <v>45777</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20043,7 +20048,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20086,7 +20091,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 20853-2025</t>
+          <t>A 30527-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20100,10 +20105,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45777</v>
+        <v>45831</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20115,13 +20120,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I256" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20164,7 +20164,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 30527-2025</t>
+          <t>A 32712-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20178,10 +20178,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45831</v>
+        <v>45839</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20193,8 +20193,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I257" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20237,7 +20242,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 32712-2025</t>
+          <t>A 35909-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20251,10 +20256,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45839</v>
+        <v>45862</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20272,7 +20277,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20315,7 +20320,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 35909-2025</t>
+          <t>A 35899-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20332,7 +20337,7 @@
         <v>45862</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20350,7 +20355,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20393,24 +20398,24 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 35899-2025</t>
+          <t>S 2321-2023</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45862</v>
+        <v>45105</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20422,13 +20427,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I260" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20471,7 +20471,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>S 2321-2023</t>
+          <t>S 4661-2022</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20481,14 +20481,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45105</v>
+        <v>44795</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>0.7</v>
+        <v>43.6</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20544,7 +20544,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>S 4661-2022</t>
+          <t>S 396-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20558,10 +20558,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>44795</v>
+        <v>44959</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>43.6</v>
+        <v>78.8</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20617,7 +20617,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>S 396-2023</t>
+          <t>S 2061-2022</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20627,14 +20627,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>44959</v>
+        <v>44672</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>78.8</v>
+        <v>1.6</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20690,7 +20690,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>S 2061-2022</t>
+          <t>S 1592-2023</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20700,14 +20700,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>44672</v>
+        <v>45056</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.6</v>
+        <v>19.5</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20763,7 +20763,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>S 1592-2023</t>
+          <t>S 366-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20777,10 +20777,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45056</v>
+        <v>44959</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>19.5</v>
+        <v>35.8</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20836,7 +20836,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>S 366-2023</t>
+          <t>S 6799-2022</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20850,10 +20850,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>44959</v>
+        <v>44893</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>35.8</v>
+        <v>28.2</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20909,7 +20909,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>S 6799-2022</t>
+          <t>S 6798-2022</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20926,7 +20926,7 @@
         <v>44893</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>28.2</v>
+        <v>149.8</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20982,7 +20982,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>S 6798-2022</t>
+          <t>S 1806-2023</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20996,10 +20996,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>44893</v>
+        <v>45072</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>149.8</v>
+        <v>61.9</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21055,7 +21055,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>S 1806-2023</t>
+          <t>S 3254-2023</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21069,10 +21069,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45072</v>
+        <v>45193</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>61.9</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21128,7 +21128,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>S 3254-2023</t>
+          <t>S 1019-2024</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21142,10 +21142,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45193</v>
+        <v>45386</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>88.59999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21201,7 +21201,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>S 1019-2024</t>
+          <t>S 4655-2022</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21215,10 +21215,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45386</v>
+        <v>44795</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>14.5</v>
+        <v>19.1</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>S 4655-2022</t>
+          <t>S 312-2025</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21288,10 +21288,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>44795</v>
+        <v>45688</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>19.1</v>
+        <v>25.8</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21347,7 +21347,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>S 312-2025</t>
+          <t>S 1799-2025</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21361,10 +21361,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45688</v>
+        <v>45817</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>25.8</v>
+        <v>21.2</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>S 1799-2025</t>
+          <t>S 1798-2025</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21437,7 +21437,7 @@
         <v>45817</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>21.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21493,7 +21493,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>S 1798-2025</t>
+          <t>S 3564-2025</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21507,10 +21507,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45817</v>
+        <v>46013</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>73.40000000000001</v>
+        <v>55.7</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21566,7 +21566,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>S 3564-2025</t>
+          <t>S 3565-2025</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21583,7 +21583,7 @@
         <v>46013</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>55.7</v>
+        <v>24</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21639,7 +21639,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>S 3565-2025</t>
+          <t>S 375-2026</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21653,10 +21653,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>46013</v>
+        <v>46065</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>24</v>
+        <v>17.6</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21709,10 +21709,10 @@
       </c>
       <c r="V277" s="2" t="inlineStr"/>
     </row>
-    <row r="278" ht="15" customHeight="1">
+    <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>S 375-2026</t>
+          <t>S 1393-2026</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21722,14 +21722,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>46065</v>
+        <v>46154</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>17.6</v>
+        <v>3.4</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -21781,79 +21781,6 @@
         <v>0</v>
       </c>
       <c r="V278" s="2" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>S 1393-2026</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D279" s="1" t="n">
-        <v>46154</v>
-      </c>
-      <c r="E279" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="I279" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J279" t="n">
-        <v>0</v>
-      </c>
-      <c r="K279" t="n">
-        <v>0</v>
-      </c>
-      <c r="L279" t="n">
-        <v>0</v>
-      </c>
-      <c r="M279" t="n">
-        <v>0</v>
-      </c>
-      <c r="N279" t="n">
-        <v>0</v>
-      </c>
-      <c r="O279" t="n">
-        <v>0</v>
-      </c>
-      <c r="P279" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
-      <c r="R279" t="n">
-        <v>0</v>
-      </c>
-      <c r="S279" t="n">
-        <v>0</v>
-      </c>
-      <c r="T279" t="n">
-        <v>0</v>
-      </c>
-      <c r="U279" t="n">
-        <v>0</v>
-      </c>
-      <c r="V279" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LESSEBO.xlsx
+++ b/Översikt LESSEBO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE278"/>
+  <dimension ref="A1:AE280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45349</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>46035</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45954</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45954</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45954</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45267</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>46176</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45072</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45670</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 56472-2024</t>
+          <t>A 52540-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45625</v>
+        <v>45954</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1727,8 +1727,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1761,265 +1766,260 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52540-2025 artfynd.xlsx", "A 52540-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52540-2025 karta.png", "A 52540-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52540-2025 georefererad karta.tif", "A 52540-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52540-2025 FSC-klagomål.docx", "A 52540-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52540-2025 FSC-klagomål mail.docx", "A 52540-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52540-2025 tillsynsbegäran.docx", "A 52540-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52540-2025 tillsynsbegäran mail.docx", "A 52540-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 52539-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>1</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52539-2025 artfynd.xlsx", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52539-2025 karta.png", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52539-2025 georefererad karta.tif", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52539-2025 FSC-klagomål.docx", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52539-2025 FSC-klagomål mail.docx", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52539-2025 tillsynsbegäran.docx", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52539-2025 tillsynsbegäran mail.docx", "A 52539-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 56472-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45625</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 56472-2024 artfynd.xlsx", "A 56472-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 56472-2024 karta.png", "A 56472-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 56472-2024 georefererad karta.tif", "A 56472-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 56472-2024 FSC-klagomål.docx", "A 56472-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 56472-2024 FSC-klagomål mail.docx", "A 56472-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 56472-2024 tillsynsbegäran.docx", "A 56472-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 56472-2024 tillsynsbegäran mail.docx", "A 56472-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 52540-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45954</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52540-2025 artfynd.xlsx", "A 52540-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52540-2025 karta.png", "A 52540-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52540-2025 georefererad karta.tif", "A 52540-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52540-2025 FSC-klagomål.docx", "A 52540-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52540-2025 FSC-klagomål mail.docx", "A 52540-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52540-2025 tillsynsbegäran.docx", "A 52540-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52540-2025 tillsynsbegäran mail.docx", "A 52540-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 52539-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45954</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52539-2025 artfynd.xlsx", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52539-2025 karta.png", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52539-2025 georefererad karta.tif", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52539-2025 FSC-klagomål.docx", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52539-2025 FSC-klagomål mail.docx", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52539-2025 tillsynsbegäran.docx", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52539-2025 tillsynsbegäran mail.docx", "A 52539-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44510</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44518</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44865</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24680-2022</t>
+          <t>A 3741-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44727</v>
+        <v>44586</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2892,8 +2892,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2941,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3741-2022</t>
+          <t>A 24680-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2955,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44586</v>
+        <v>44727</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2965,13 +2970,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>44510</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44842</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>44491</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44529</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19495-2022</t>
+          <t>A 27794-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44693</v>
+        <v>44743</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 63330-2021</t>
+          <t>A 19495-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44508</v>
+        <v>44693</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 66902-2021</t>
+          <t>A 63330-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44522</v>
+        <v>44508</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 27794-2022</t>
+          <t>A 66902-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44743</v>
+        <v>44522</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33240-2024</t>
+          <t>A 63927-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45518</v>
+        <v>44509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3705,8 +3705,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>7.4</v>
+        <v>2.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3749,7 +3754,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 56456-2024</t>
+          <t>A 27713-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3763,10 +3768,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45625</v>
+        <v>44743</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3779,7 +3784,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3822,7 +3827,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56459-2024</t>
+          <t>A 3876-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3836,10 +3841,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45625</v>
+        <v>45322</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3852,7 +3857,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3895,7 +3900,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 68507-2021</t>
+          <t>A 4742-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44529</v>
+        <v>45688</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3924,8 +3929,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3968,7 +3978,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24478-2024</t>
+          <t>A 27080-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3982,10 +3992,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45459</v>
+        <v>44741</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3998,7 +4008,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4041,7 +4051,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 1367-2023</t>
+          <t>A 29566-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4055,10 +4065,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44936</v>
+        <v>45484</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4071,7 +4081,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>21.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4114,7 +4124,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30966-2023</t>
+          <t>A 8655-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4128,10 +4138,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45113</v>
+        <v>45710</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4144,7 +4154,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4187,7 +4197,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59320-2024</t>
+          <t>A 11843-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4201,10 +4211,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45637</v>
+        <v>45376</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4218,11 +4228,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4275,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15203-2023</t>
+          <t>A 41900-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4275,14 +4285,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45017</v>
+        <v>44830</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4300,7 +4310,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.2</v>
+        <v>5.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4343,7 +4353,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15204-2023</t>
+          <t>A 22432-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4357,10 +4367,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45017</v>
+        <v>45070</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4374,11 +4384,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4421,7 +4431,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8655-2025</t>
+          <t>A 17552-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4435,10 +4445,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45710</v>
+        <v>45036</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4451,7 +4461,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4494,7 +4504,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 43453-2024</t>
+          <t>A 51189-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4508,10 +4518,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45568</v>
+        <v>45219</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4524,7 +4534,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4567,7 +4577,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 859-2025</t>
+          <t>A 13751-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4577,14 +4587,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45665</v>
+        <v>45737</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4596,13 +4606,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4645,7 +4650,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45838-2022</t>
+          <t>A 30405-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4659,10 +4664,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44846</v>
+        <v>45111</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4675,7 +4680,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4718,7 +4723,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27713-2022</t>
+          <t>A 59173-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4732,10 +4737,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44743</v>
+        <v>45253</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4748,7 +4753,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4791,7 +4796,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15180-2023</t>
+          <t>A 50892-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4805,10 +4810,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45016</v>
+        <v>44867</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4821,7 +4826,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4864,7 +4869,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7957-2023</t>
+          <t>A 45838-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4878,10 +4883,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44973</v>
+        <v>44846</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4894,7 +4899,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4937,7 +4942,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17836-2023</t>
+          <t>A 20824-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4951,10 +4956,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45037</v>
+        <v>45058</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4967,7 +4972,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5010,7 +5015,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30914-2022</t>
+          <t>A 30600-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5024,10 +5029,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44767</v>
+        <v>45493</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5040,7 +5045,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5083,7 +5088,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19501-2022</t>
+          <t>A 24171-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5097,10 +5102,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44693</v>
+        <v>45456</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5113,7 +5118,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5156,7 +5161,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 50154-2022</t>
+          <t>A 24478-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5170,10 +5175,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44865</v>
+        <v>45459</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5186,7 +5191,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5229,7 +5234,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29767-2023</t>
+          <t>A 39549-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5243,10 +5248,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45107</v>
+        <v>45890</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5259,7 +5264,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5302,7 +5307,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 41905-2022</t>
+          <t>A 15864-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5316,10 +5321,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44830</v>
+        <v>44664</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5331,13 +5336,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5380,7 +5380,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3955-2022</t>
+          <t>A 642-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5390,14 +5390,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44587</v>
+        <v>45299</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5409,8 +5409,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5453,7 +5458,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 60358-2022</t>
+          <t>A 53487-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5467,10 +5472,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44910</v>
+        <v>45611</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5483,7 +5488,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5526,7 +5531,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20541-2024</t>
+          <t>A 64635-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5540,10 +5545,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45436</v>
+        <v>45281</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5556,7 +5561,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5599,7 +5604,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 64635-2023</t>
+          <t>A 39750-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5613,10 +5618,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45281</v>
+        <v>45891</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5629,7 +5634,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5672,7 +5677,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14584-2023</t>
+          <t>A 39884-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5686,10 +5691,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45013</v>
+        <v>45891</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5702,7 +5707,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5745,7 +5750,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17517-2023</t>
+          <t>A 57519-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5759,10 +5764,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45036</v>
+        <v>44896</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5775,7 +5780,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5818,7 +5823,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 73140-2021</t>
+          <t>A 20541-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5832,10 +5837,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44550</v>
+        <v>45436</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5848,7 +5853,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5891,7 +5896,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30405-2023</t>
+          <t>A 10414-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5905,10 +5910,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45111</v>
+        <v>45720</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5921,7 +5926,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5964,7 +5969,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10047-2024</t>
+          <t>A 35904-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5978,10 +5983,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45364</v>
+        <v>45862</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5995,11 +6000,11 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6042,7 +6047,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36895-2025</t>
+          <t>A 47402-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6056,10 +6061,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45874</v>
+        <v>45587</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6072,7 +6077,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6115,7 +6120,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3239-2025</t>
+          <t>A 18968-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6129,10 +6134,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45679</v>
+        <v>45427</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6144,13 +6149,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38303-2025</t>
+          <t>A 43809-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45883</v>
+        <v>45912</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6266,7 +6266,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52525-2023</t>
+          <t>A 50154-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45225</v>
+        <v>44865</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39884-2025</t>
+          <t>A 64865-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45891</v>
+        <v>45282</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6368,8 +6368,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>5.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6412,7 +6417,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39549-2025</t>
+          <t>A 44904-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6426,10 +6431,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45890</v>
+        <v>45918</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6442,7 +6447,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6485,7 +6490,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 56471-2024</t>
+          <t>A 34386-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6499,10 +6504,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45625</v>
+        <v>45139</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6515,7 +6520,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6558,7 +6563,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39750-2025</t>
+          <t>A 44899-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6572,10 +6577,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45891</v>
+        <v>45918</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6588,7 +6593,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6631,7 +6636,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 51191-2023</t>
+          <t>A 56529-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6645,10 +6650,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45219</v>
+        <v>44893</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6661,7 +6666,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6704,7 +6709,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56467-2024</t>
+          <t>A 17350-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6718,10 +6723,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45625</v>
+        <v>45035</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6734,7 +6739,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6777,7 +6782,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 21917-2025</t>
+          <t>A 14940-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6791,10 +6796,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45784</v>
+        <v>45398</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6807,7 +6812,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6867,7 +6872,7 @@
         <v>45708</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6923,7 +6928,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35904-2025</t>
+          <t>A 38227-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6937,10 +6942,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45862</v>
+        <v>45161</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6952,13 +6957,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7001,7 +7001,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 1894-2025</t>
+          <t>A 17836-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45671</v>
+        <v>45037</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7074,7 +7074,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20855-2025</t>
+          <t>A 8173-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7084,14 +7084,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45777</v>
+        <v>45708</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7103,13 +7103,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7152,7 +7147,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3876-2024</t>
+          <t>A 3714-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7166,10 +7161,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45322</v>
+        <v>44586</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7181,8 +7176,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 1490-2025</t>
+          <t>A 65137-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7235,14 +7235,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45670</v>
+        <v>45288</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7254,13 +7254,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7303,7 +7298,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 43809-2025</t>
+          <t>A 33240-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7317,10 +7312,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45912</v>
+        <v>45518</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7333,7 +7328,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7376,7 +7371,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47693-2025</t>
+          <t>A 48429-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7390,10 +7385,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45931</v>
+        <v>45934</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7406,7 +7401,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7449,7 +7444,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44904-2025</t>
+          <t>A 48433-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7463,10 +7458,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45918</v>
+        <v>45934</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7479,7 +7474,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7522,7 +7517,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44899-2025</t>
+          <t>A 39389-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7536,10 +7531,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45918</v>
+        <v>45551</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7552,7 +7547,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7595,7 +7590,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 54541-2023</t>
+          <t>A 43114-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7605,14 +7600,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45233</v>
+        <v>45567</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7630,7 +7625,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7673,7 +7668,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 51189-2023</t>
+          <t>A 60358-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7687,10 +7682,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45219</v>
+        <v>44910</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7703,7 +7698,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7746,7 +7741,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 8690-2023</t>
+          <t>A 4413-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7760,10 +7755,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44978</v>
+        <v>44589</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7776,7 +7771,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7819,7 +7814,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 35894-2025</t>
+          <t>A 17729-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7833,10 +7828,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45862</v>
+        <v>45758</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7854,7 +7849,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7897,7 +7892,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 57519-2022</t>
+          <t>A 20443-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7911,10 +7906,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44896</v>
+        <v>45775</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7926,8 +7921,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7970,7 +7970,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 56475-2024</t>
+          <t>A 49298-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45625</v>
+        <v>45938</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8043,7 +8043,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 65137-2023</t>
+          <t>A 4465-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45288</v>
+        <v>45327</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.4</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8116,7 +8116,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48429-2025</t>
+          <t>A 33076-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8126,14 +8126,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45934</v>
+        <v>45126</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8189,7 +8189,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48433-2025</t>
+          <t>A 70350-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45934</v>
+        <v>44536</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8262,7 +8262,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 21311-2026</t>
+          <t>A 1490-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8272,14 +8272,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46147</v>
+        <v>45670</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8291,8 +8291,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8335,7 +8340,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 17729-2025</t>
+          <t>A 61575-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8349,10 +8354,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45758</v>
+        <v>44916</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8366,11 +8371,11 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8413,7 +8418,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20824-2023</t>
+          <t>A 61588-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8427,10 +8432,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45058</v>
+        <v>44916</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8442,8 +8447,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8486,7 +8496,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 49298-2025</t>
+          <t>A 43453-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8500,10 +8510,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45938</v>
+        <v>45568</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8516,7 +8526,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8559,7 +8569,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20443-2025</t>
+          <t>A 47396-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8573,10 +8583,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45775</v>
+        <v>45587</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8588,13 +8598,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8637,7 +8642,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17204-2025</t>
+          <t>A 14549-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8651,10 +8656,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45756</v>
+        <v>45741</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8667,7 +8672,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8710,7 +8715,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 27191-2022</t>
+          <t>A 27405-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8724,10 +8729,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44741</v>
+        <v>45474</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8740,7 +8745,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8783,7 +8788,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 49121-2024</t>
+          <t>A 7957-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8797,10 +8802,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45594</v>
+        <v>44973</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8856,7 +8861,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22318-2026</t>
+          <t>A 13036-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8870,10 +8875,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46154</v>
+        <v>44643</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8886,7 +8891,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8929,7 +8934,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 22423-2026</t>
+          <t>A 52031-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8939,14 +8944,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46154</v>
+        <v>45952</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8959,7 +8964,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9002,7 +9007,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 22718-2026</t>
+          <t>A 3955-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9016,10 +9021,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46157</v>
+        <v>44587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9031,13 +9036,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9080,7 +9080,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 22756-2026</t>
+          <t>A 52537-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46157</v>
+        <v>45954</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>8.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9158,7 +9158,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 22758-2026</t>
+          <t>A 56456-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9172,10 +9172,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46157</v>
+        <v>45625</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9187,13 +9187,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9236,7 +9231,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 22766-2026</t>
+          <t>A 47386-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9250,10 +9245,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46157</v>
+        <v>45587</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9265,13 +9260,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9314,7 +9304,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 52031-2025</t>
+          <t>A 56459-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9328,10 +9318,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45952</v>
+        <v>45625</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9344,7 +9334,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9387,7 +9377,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 47396-2024</t>
+          <t>A 52531-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9401,10 +9391,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45587</v>
+        <v>45954</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9416,8 +9406,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9460,7 +9455,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 22719-2026</t>
+          <t>A 52532-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9474,10 +9469,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46157</v>
+        <v>45954</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9495,7 +9490,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9538,7 +9533,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 22720-2026</t>
+          <t>A 52546-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9552,10 +9547,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46157</v>
+        <v>45954</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9573,7 +9568,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9616,7 +9611,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 22764-2026</t>
+          <t>A 1897-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9630,10 +9625,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46157</v>
+        <v>45671</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9645,13 +9640,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9694,7 +9684,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 22768-2026</t>
+          <t>A 52534-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9708,10 +9698,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46157</v>
+        <v>45954</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9729,7 +9719,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9772,7 +9762,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22770-2026</t>
+          <t>A 53122-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9786,10 +9776,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46157</v>
+        <v>45958</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9801,13 +9791,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9850,7 +9835,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 22723-2026</t>
+          <t>A 20478-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9864,10 +9849,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46157</v>
+        <v>45775</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9885,7 +9870,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9928,7 +9913,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 1897-2025</t>
+          <t>A 20825-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9942,10 +9927,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45671</v>
+        <v>45058</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9958,7 +9943,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10001,7 +9986,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 20485-2025</t>
+          <t>A 37399-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10015,10 +10000,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45775</v>
+        <v>45540</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10030,13 +10015,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10079,7 +10059,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 52537-2025</t>
+          <t>A 51175-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10093,10 +10073,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45954</v>
+        <v>45219</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10108,13 +10088,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10157,7 +10132,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 52531-2025</t>
+          <t>A 49295-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10171,10 +10146,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45954</v>
+        <v>45938</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10186,13 +10161,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10235,7 +10205,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 52532-2025</t>
+          <t>A 20851-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10249,10 +10219,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45954</v>
+        <v>45777</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10270,7 +10240,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10313,7 +10283,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 52546-2025</t>
+          <t>A 14584-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10327,10 +10297,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45954</v>
+        <v>45013</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10342,13 +10312,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10391,7 +10356,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 52534-2025</t>
+          <t>A 48639-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10405,10 +10370,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45954</v>
+        <v>45202</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10420,13 +10385,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10469,7 +10429,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 53122-2025</t>
+          <t>A 29767-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10483,10 +10443,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45958</v>
+        <v>45107</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10499,7 +10459,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10542,7 +10502,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 51175-2023</t>
+          <t>A 19501-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10556,10 +10516,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45219</v>
+        <v>44693</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10572,7 +10532,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10615,7 +10575,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 20431-2025</t>
+          <t>A 50162-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10625,14 +10585,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45775</v>
+        <v>45215</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10650,7 +10610,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10693,7 +10653,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20435-2025</t>
+          <t>A 51191-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10707,10 +10667,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45775</v>
+        <v>45219</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10722,13 +10682,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10771,7 +10726,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61995-2022</t>
+          <t>A 2755-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10781,14 +10736,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44918</v>
+        <v>45677</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10800,13 +10755,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10849,7 +10799,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 20681-2025</t>
+          <t>A 52525-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10863,10 +10813,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45776</v>
+        <v>45225</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10878,13 +10828,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10927,7 +10872,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 4107-2025</t>
+          <t>A 21745-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10941,10 +10886,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45684</v>
+        <v>44708</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10957,7 +10902,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11000,7 +10945,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 49295-2025</t>
+          <t>A 17517-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11014,10 +10959,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45938</v>
+        <v>45036</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11030,7 +10975,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11073,7 +11018,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3875-2024</t>
+          <t>A 29659-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11083,14 +11028,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45322</v>
+        <v>45825</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11103,7 +11048,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11146,7 +11091,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 50892-2022</t>
+          <t>A 39603-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11160,10 +11105,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44867</v>
+        <v>44818</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11176,7 +11121,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11219,7 +11164,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 47402-2024</t>
+          <t>A 1367-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11233,10 +11178,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45587</v>
+        <v>44936</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11249,7 +11194,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11292,7 +11237,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 24275-2026</t>
+          <t>A 27191-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11306,10 +11251,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46169</v>
+        <v>44741</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11322,7 +11267,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11365,7 +11310,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 24271-2026</t>
+          <t>A 20854-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11379,10 +11324,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46169</v>
+        <v>45777</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11394,8 +11339,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11438,7 +11388,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 24272-2026</t>
+          <t>A 20853-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11452,10 +11402,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46169</v>
+        <v>45777</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11467,8 +11417,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11511,7 +11466,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 24269-2026</t>
+          <t>A 17203-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11525,10 +11480,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46169</v>
+        <v>45756</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11541,7 +11496,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11584,7 +11539,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 4465-2024</t>
+          <t>A 4107-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11598,10 +11553,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45327</v>
+        <v>45684</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11614,7 +11569,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11657,7 +11612,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 4453-2024</t>
+          <t>A 40912-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11671,10 +11626,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45327</v>
+        <v>45173</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11686,13 +11641,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11735,7 +11685,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 50162-2023</t>
+          <t>A 30527-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11745,14 +11695,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45215</v>
+        <v>45831</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11764,13 +11714,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11813,7 +11758,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 39389-2024</t>
+          <t>A 1022-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11827,10 +11772,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45551</v>
+        <v>46030</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11843,7 +11788,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11886,7 +11831,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 61638-2025</t>
+          <t>A 1016-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11900,10 +11845,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46002</v>
+        <v>46030</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11916,7 +11861,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11959,7 +11904,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 61641-2025</t>
+          <t>A 3239-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11973,10 +11918,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46002</v>
+        <v>45679</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11990,11 +11935,11 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12037,7 +11982,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 25169-2026</t>
+          <t>A 54541-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12047,14 +11992,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46175</v>
+        <v>45233</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12066,8 +12011,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12110,7 +12060,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 17552-2023</t>
+          <t>A 61638-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12124,10 +12074,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45036</v>
+        <v>46002</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12140,7 +12090,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12183,7 +12133,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 62728-2025</t>
+          <t>A 61641-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12197,10 +12147,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12218,7 +12168,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12261,7 +12211,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 40912-2023</t>
+          <t>A 3875-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12275,10 +12225,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45173</v>
+        <v>45322</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12291,7 +12241,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12334,7 +12284,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 18968-2024</t>
+          <t>A 18207-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12348,10 +12298,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45427</v>
+        <v>45761</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12363,8 +12313,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12407,7 +12362,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 53341-2021</t>
+          <t>A 18211-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12421,10 +12376,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44468</v>
+        <v>45761</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12436,8 +12391,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12480,7 +12440,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 1022-2026</t>
+          <t>A 41905-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12494,10 +12454,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46030</v>
+        <v>44830</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12509,8 +12469,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12553,7 +12518,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 1016-2026</t>
+          <t>A 62728-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12567,10 +12532,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46030</v>
+        <v>46008</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12582,8 +12547,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12626,7 +12596,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 17203-2025</t>
+          <t>A 32712-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12640,10 +12610,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45756</v>
+        <v>45839</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12655,8 +12625,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12699,7 +12674,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 48639-2023</t>
+          <t>A 39436-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12713,10 +12688,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45202</v>
+        <v>44818</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12729,7 +12704,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12772,7 +12747,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 20441-2025</t>
+          <t>A 4229-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12786,10 +12761,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45775</v>
+        <v>46044</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12801,13 +12776,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12850,7 +12820,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 59321-2024</t>
+          <t>A 4236-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12864,10 +12834,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45637</v>
+        <v>46044</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12879,13 +12849,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12928,7 +12893,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 14551-2025</t>
+          <t>A 17204-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12942,10 +12907,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45741</v>
+        <v>45756</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12958,7 +12923,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13001,7 +12966,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 4236-2026</t>
+          <t>A 35332-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13015,10 +12980,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46044</v>
+        <v>44798</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13031,7 +12996,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13074,7 +13039,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 4229-2026</t>
+          <t>A 32771-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13088,10 +13053,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46044</v>
+        <v>46241</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13104,7 +13069,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>9.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13147,7 +13112,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 27870-2026</t>
+          <t>A 32760-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13161,10 +13126,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46191</v>
+        <v>46241</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13177,7 +13142,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13220,7 +13185,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 27873-2026</t>
+          <t>A 56467-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13234,10 +13199,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46191</v>
+        <v>45625</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13250,7 +13215,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13293,7 +13258,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 20480-2025</t>
+          <t>A 32768-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13307,10 +13272,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45775</v>
+        <v>46241</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13322,13 +13287,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13371,7 +13331,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 8438-2026</t>
+          <t>A 32764-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13385,10 +13345,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46065</v>
+        <v>46241</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13400,13 +13360,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13449,7 +13404,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 10189-2026</t>
+          <t>A 59320-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13463,10 +13418,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46076</v>
+        <v>45637</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13478,8 +13433,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13522,7 +13482,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 27574-2023</t>
+          <t>A 8438-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13536,10 +13496,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45097</v>
+        <v>46065</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13551,8 +13511,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13595,7 +13560,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 4839-2023</t>
+          <t>A 39350-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13609,10 +13574,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44955</v>
+        <v>46288</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13625,7 +13590,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13668,7 +13633,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 10286-2026</t>
+          <t>A 39250-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13682,10 +13647,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46076</v>
+        <v>46288</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13741,7 +13706,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 10185-2026</t>
+          <t>A 10286-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13758,7 +13723,7 @@
         <v>46076</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13771,7 +13736,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13814,7 +13779,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 14549-2025</t>
+          <t>A 10185-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13828,10 +13793,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45741</v>
+        <v>46076</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13844,7 +13809,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13887,7 +13852,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 30600-2024</t>
+          <t>A 10189-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13901,10 +13866,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45493</v>
+        <v>46076</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13917,7 +13882,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13960,7 +13925,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 24171-2024</t>
+          <t>A 70349-2021</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13974,10 +13939,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45456</v>
+        <v>44536</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13990,7 +13955,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14033,7 +13998,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 64865-2023</t>
+          <t>A 13347-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14047,10 +14012,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45282</v>
+        <v>46094</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14064,11 +14029,11 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14111,7 +14076,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 41900-2022</t>
+          <t>A 30914-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14125,10 +14090,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44830</v>
+        <v>44767</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14140,13 +14105,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14189,7 +14149,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 38227-2023</t>
+          <t>A 73140-2021</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14203,10 +14163,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45161</v>
+        <v>44550</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14219,7 +14179,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14262,7 +14222,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 13347-2026</t>
+          <t>A 27574-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14276,10 +14236,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46094</v>
+        <v>45097</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14291,13 +14251,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14340,7 +14295,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 30822-2026</t>
+          <t>A 53341-2021</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14354,10 +14309,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46205</v>
+        <v>44468</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14370,7 +14325,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14413,7 +14368,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 30826-2026</t>
+          <t>A 4839-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14427,10 +14382,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46205</v>
+        <v>44955</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14443,7 +14398,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14486,7 +14441,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 35332-2022</t>
+          <t>A 3605-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14500,10 +14455,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44798</v>
+        <v>45320</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14516,7 +14471,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14559,7 +14514,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 20825-2023</t>
+          <t>A 35909-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14573,10 +14528,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45058</v>
+        <v>45862</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14588,8 +14543,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14632,7 +14592,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 13751-2025</t>
+          <t>A 35899-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14646,10 +14606,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45737</v>
+        <v>45862</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14661,8 +14621,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14705,7 +14670,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 27405-2024</t>
+          <t>A 21546-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14719,10 +14684,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45474</v>
+        <v>45063</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14735,7 +14700,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14778,7 +14743,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 59173-2023</t>
+          <t>A 18464-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14792,10 +14757,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45253</v>
+        <v>46127</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14807,8 +14772,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>2</v>
+        <v>14.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14851,7 +14821,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 3714-2022</t>
+          <t>A 18466-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14865,10 +14835,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44586</v>
+        <v>46127</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14882,11 +14852,11 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4.1</v>
+        <v>7.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14946,7 +14916,7 @@
         <v>46127</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15002,7 +14972,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 18464-2026</t>
+          <t>A 15180-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15016,10 +14986,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46127</v>
+        <v>45016</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15031,13 +15001,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>14.2</v>
+        <v>0.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15080,7 +15045,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 18466-2026</t>
+          <t>A 21917-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15094,10 +15059,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46127</v>
+        <v>45784</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15109,13 +15074,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>7.9</v>
+        <v>1.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15158,7 +15118,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 18207-2025</t>
+          <t>A 20855-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15172,10 +15132,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45761</v>
+        <v>45777</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15193,7 +15153,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15236,7 +15196,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 18211-2025</t>
+          <t>A 859-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15246,14 +15206,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45761</v>
+        <v>45665</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15271,7 +15231,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15314,7 +15274,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 642-2024</t>
+          <t>A 52031-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15324,14 +15284,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45299</v>
+        <v>45223</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15343,13 +15303,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15392,7 +15347,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 20056-2025</t>
+          <t>A 1894-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15406,10 +15361,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45772</v>
+        <v>45671</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15422,7 +15377,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15465,7 +15420,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 33076-2023</t>
+          <t>A 47693-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15475,14 +15430,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45126</v>
+        <v>45931</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15495,7 +15450,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15538,7 +15493,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 47386-2024</t>
+          <t>A 20056-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15552,10 +15507,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45587</v>
+        <v>45772</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15568,7 +15523,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15611,7 +15566,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 63927-2021</t>
+          <t>A 10047-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15625,10 +15580,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44509</v>
+        <v>45364</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15642,11 +15597,11 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15689,7 +15644,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 39603-2022</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15699,14 +15654,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44818</v>
+        <v>45708</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15719,7 +15674,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15762,7 +15717,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 34855-2026</t>
+          <t>A 30966-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15776,10 +15731,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46255</v>
+        <v>45113</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15791,13 +15746,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15840,7 +15790,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 34894-2026</t>
+          <t>A 68507-2021</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15854,10 +15804,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46259</v>
+        <v>44529</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15870,7 +15820,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15913,7 +15863,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 34984-2026</t>
+          <t>A 38712-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15927,10 +15877,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46258</v>
+        <v>44814</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15943,7 +15893,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15986,7 +15936,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 34820-2026</t>
+          <t>A 43206-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16000,10 +15950,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46255</v>
+        <v>45567</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16015,13 +15965,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16064,7 +16009,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 11843-2024</t>
+          <t>A 15203-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16074,14 +16019,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45376</v>
+        <v>45017</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16095,11 +16040,11 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16142,7 +16087,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 14940-2024</t>
+          <t>A 15204-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16152,14 +16097,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45398</v>
+        <v>45017</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16171,8 +16116,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16215,7 +16165,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 34661-2026</t>
+          <t>A 36895-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16229,10 +16179,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46257</v>
+        <v>45874</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16245,7 +16195,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16288,7 +16238,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 34806-2026</t>
+          <t>A 8690-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16302,10 +16252,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46255</v>
+        <v>44978</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16317,13 +16267,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16366,7 +16311,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31252-2026</t>
+          <t>A 61995-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16380,10 +16325,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46218</v>
+        <v>44918</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16401,7 +16346,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16444,7 +16389,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 4413-2022</t>
+          <t>A 4453-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16458,10 +16403,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44589</v>
+        <v>45327</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16473,8 +16418,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16517,7 +16467,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 35568-2026</t>
+          <t>A 56471-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16531,10 +16481,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46262</v>
+        <v>45625</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16546,13 +16496,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>6.9</v>
+        <v>3.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16595,7 +16540,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 35570-2026</t>
+          <t>A 38303-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16609,10 +16554,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46262</v>
+        <v>45883</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16624,13 +16569,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16673,7 +16613,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 3605-2024</t>
+          <t>A 49121-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16687,10 +16627,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45320</v>
+        <v>45594</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16703,7 +16643,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16746,7 +16686,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 34386-2023</t>
+          <t>A 35894-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16760,10 +16700,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45139</v>
+        <v>45862</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16775,8 +16715,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16819,7 +16764,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 21546-2023</t>
+          <t>A 56475-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16833,10 +16778,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45063</v>
+        <v>45625</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16849,7 +16794,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16892,7 +16837,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 36067-2026</t>
+          <t>A 21311-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16906,10 +16851,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46267</v>
+        <v>46147</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16921,13 +16866,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16970,7 +16910,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 15864-2022</t>
+          <t>A 51990-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16984,10 +16924,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44664</v>
+        <v>45607</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17000,7 +16940,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17043,7 +16983,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 36313-2026</t>
+          <t>A 41598-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17057,10 +16997,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46268</v>
+        <v>45560</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17073,7 +17013,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17116,7 +17056,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 38712-2022</t>
+          <t>A 20852-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17130,10 +17070,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44814</v>
+        <v>45777</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17145,8 +17085,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17189,7 +17134,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 22432-2023</t>
+          <t>A 61439-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17199,14 +17144,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45070</v>
+        <v>45646</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17218,13 +17163,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17267,7 +17207,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 56529-2022</t>
+          <t>A 22318-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17281,10 +17221,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44893</v>
+        <v>46154</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17297,7 +17237,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>9</v>
+        <v>1.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17340,7 +17280,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 43114-2024</t>
+          <t>A 21951-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17350,14 +17290,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45567</v>
+        <v>45784</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17371,11 +17311,11 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17418,7 +17358,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 37786-2026</t>
+          <t>A 22423-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17428,14 +17368,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46279</v>
+        <v>46154</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17448,7 +17388,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17491,7 +17431,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 21745-2022</t>
+          <t>A 37964-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17501,14 +17441,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44708</v>
+        <v>45544</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17521,7 +17461,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>9.699999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17564,7 +17504,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 37399-2024</t>
+          <t>A 22764-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17578,10 +17518,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45540</v>
+        <v>46157</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17593,8 +17533,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17637,7 +17582,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 27080-2022</t>
+          <t>A 22768-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17651,10 +17596,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44741</v>
+        <v>46157</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17666,8 +17611,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17710,7 +17660,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 38098-2026</t>
+          <t>A 22770-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17724,10 +17674,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46281</v>
+        <v>46157</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17739,8 +17689,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17783,7 +17738,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 43206-2024</t>
+          <t>A 20431-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17797,10 +17752,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45567</v>
+        <v>45775</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17812,8 +17767,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17856,7 +17816,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 39436-2022</t>
+          <t>A 22723-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17870,10 +17830,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44818</v>
+        <v>46157</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17885,8 +17845,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17929,7 +17894,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 13036-2022</t>
+          <t>A 20681-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17943,10 +17908,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44643</v>
+        <v>45776</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17958,8 +17923,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18002,7 +17972,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 52031-2023</t>
+          <t>A 22718-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18016,10 +17986,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45223</v>
+        <v>46157</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18031,8 +18001,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18075,7 +18050,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 70349-2021</t>
+          <t>A 22766-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18089,10 +18064,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44536</v>
+        <v>46157</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18104,8 +18079,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18148,7 +18128,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 70350-2021</t>
+          <t>A 22756-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18162,10 +18142,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44536</v>
+        <v>46157</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18177,8 +18157,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>0.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18221,7 +18206,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 32764-2026</t>
+          <t>A 22758-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18235,10 +18220,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46241</v>
+        <v>46157</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18250,8 +18235,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18294,7 +18284,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 32768-2026</t>
+          <t>A 20435-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18308,10 +18298,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46241</v>
+        <v>45775</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18323,8 +18313,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18367,7 +18362,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 32771-2026</t>
+          <t>A 20485-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18381,10 +18376,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46241</v>
+        <v>45775</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18396,8 +18391,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18440,7 +18440,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 2755-2025</t>
+          <t>A 22719-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18450,14 +18450,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45677</v>
+        <v>46157</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18469,8 +18469,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18513,7 +18518,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 32760-2026</t>
+          <t>A 22720-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18527,10 +18532,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46241</v>
+        <v>46157</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18542,8 +18547,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18586,7 +18596,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 61575-2022</t>
+          <t>A 24275-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18600,10 +18610,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44916</v>
+        <v>46169</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18615,13 +18625,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I236" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18664,7 +18669,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 61588-2022</t>
+          <t>A 24271-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18678,10 +18683,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44916</v>
+        <v>46169</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18693,13 +18698,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I237" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18742,7 +18742,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 17350-2023</t>
+          <t>A 24272-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18756,10 +18756,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45035</v>
+        <v>46169</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18815,7 +18815,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 20852-2025</t>
+          <t>A 24269-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18829,10 +18829,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45777</v>
+        <v>46169</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18844,13 +18844,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I239" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18893,7 +18888,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 51990-2024</t>
+          <t>A 25169-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18907,10 +18902,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45607</v>
+        <v>46175</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18923,7 +18918,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18966,7 +18961,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 41598-2024</t>
+          <t>A 59321-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18980,10 +18975,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45560</v>
+        <v>45637</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18995,8 +18990,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I241" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19039,7 +19039,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 61439-2024</t>
+          <t>A 20441-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19053,10 +19053,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45646</v>
+        <v>45775</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19068,8 +19068,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I242" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19112,7 +19117,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 21951-2025</t>
+          <t>A 14551-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19122,14 +19127,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45784</v>
+        <v>45741</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19141,13 +19146,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>3.8</v>
+        <v>0.3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19190,7 +19190,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 37964-2024</t>
+          <t>A 27870-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19200,14 +19200,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45544</v>
+        <v>46191</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19263,7 +19263,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 4742-2025</t>
+          <t>A 27873-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19277,10 +19277,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45688</v>
+        <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19292,13 +19292,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I245" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19341,7 +19336,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 29566-2024</t>
+          <t>A 20480-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19355,10 +19350,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45484</v>
+        <v>45775</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19370,8 +19365,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I246" t="n">
-        <v>21.3</v>
+        <v>1.4</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19414,7 +19414,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 10414-2025</t>
+          <t>A 30826-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19428,10 +19428,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45720</v>
+        <v>46205</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19487,7 +19487,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 53487-2024</t>
+          <t>A 30822-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19501,10 +19501,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45611</v>
+        <v>46205</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19560,7 +19560,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 8173-2025</t>
+          <t>A 34661-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19570,14 +19570,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45708</v>
+        <v>46257</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19633,7 +19633,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 34806-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19643,14 +19643,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45708</v>
+        <v>46255</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19662,8 +19662,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I250" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19706,7 +19711,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 20478-2025</t>
+          <t>A 34820-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19720,10 +19725,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45775</v>
+        <v>46255</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19737,11 +19742,11 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I251" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19784,7 +19789,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 29659-2025</t>
+          <t>A 34855-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19794,14 +19799,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45825</v>
+        <v>46255</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19813,8 +19818,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I252" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19857,7 +19867,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 20851-2025</t>
+          <t>A 34894-2026</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19871,10 +19881,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45777</v>
+        <v>46259</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19886,13 +19896,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I253" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19935,7 +19940,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 20854-2025</t>
+          <t>A 34984-2026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19949,10 +19954,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45777</v>
+        <v>46258</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19964,13 +19969,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I254" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20013,7 +20013,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 20853-2025</t>
+          <t>A 35570-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20027,10 +20027,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45777</v>
+        <v>46262</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20091,7 +20091,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 30527-2025</t>
+          <t>A 31252-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20105,10 +20105,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45831</v>
+        <v>46218</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20120,8 +20120,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I256" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20164,7 +20169,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 32712-2025</t>
+          <t>A 35568-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20178,10 +20183,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45839</v>
+        <v>46262</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20199,7 +20204,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>2</v>
+        <v>6.9</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20242,7 +20247,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 35909-2025</t>
+          <t>A 36067-2026</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20256,10 +20261,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45862</v>
+        <v>46267</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20277,7 +20282,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20320,7 +20325,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 35899-2025</t>
+          <t>A 36313-2026</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20334,10 +20339,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45862</v>
+        <v>46268</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20349,13 +20354,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I259" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20398,24 +20398,24 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>S 2321-2023</t>
+          <t>A 37786-2026</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45105</v>
+        <v>46279</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20471,24 +20471,24 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>S 4661-2022</t>
+          <t>A 38098-2026</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>44795</v>
+        <v>46281</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>43.6</v>
+        <v>0.5</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20544,7 +20544,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>S 396-2023</t>
+          <t>S 2061-2022</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20554,14 +20554,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>44959</v>
+        <v>44672</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>78.8</v>
+        <v>1.6</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20617,7 +20617,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>S 2061-2022</t>
+          <t>S 2321-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20631,10 +20631,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>44672</v>
+        <v>45105</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20690,7 +20690,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>S 1592-2023</t>
+          <t>S 4661-2022</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20704,10 +20704,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45056</v>
+        <v>44795</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>19.5</v>
+        <v>43.6</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20763,7 +20763,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>S 366-2023</t>
+          <t>S 396-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20780,7 +20780,7 @@
         <v>44959</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>35.8</v>
+        <v>78.8</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20836,7 +20836,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>S 6799-2022</t>
+          <t>S 1592-2023</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20850,10 +20850,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>44893</v>
+        <v>45056</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>28.2</v>
+        <v>19.5</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20909,7 +20909,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>S 6798-2022</t>
+          <t>S 366-2023</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20923,10 +20923,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>44893</v>
+        <v>44959</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>149.8</v>
+        <v>35.8</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20982,7 +20982,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>S 1806-2023</t>
+          <t>S 6799-2022</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20996,10 +20996,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45072</v>
+        <v>44893</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>61.9</v>
+        <v>28.2</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21055,7 +21055,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>S 3254-2023</t>
+          <t>S 6798-2022</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21069,10 +21069,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45193</v>
+        <v>44893</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>88.59999999999999</v>
+        <v>149.8</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21128,7 +21128,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>S 1019-2024</t>
+          <t>S 1806-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21142,10 +21142,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45386</v>
+        <v>45072</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>14.5</v>
+        <v>61.9</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21201,7 +21201,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>S 4655-2022</t>
+          <t>S 3254-2023</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21215,10 +21215,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>44795</v>
+        <v>45193</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>19.1</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>S 312-2025</t>
+          <t>S 1019-2024</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21288,10 +21288,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45688</v>
+        <v>45386</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>25.8</v>
+        <v>14.5</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21347,7 +21347,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>S 1799-2025</t>
+          <t>S 4655-2022</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21361,10 +21361,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45817</v>
+        <v>44795</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>21.2</v>
+        <v>19.1</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21420,7 +21420,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>S 1798-2025</t>
+          <t>S 312-2025</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21434,10 +21434,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45817</v>
+        <v>45688</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>73.40000000000001</v>
+        <v>25.8</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21493,7 +21493,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>S 3564-2025</t>
+          <t>S 1799-2025</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21507,10 +21507,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>46013</v>
+        <v>45817</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>55.7</v>
+        <v>21.2</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21566,7 +21566,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>S 3565-2025</t>
+          <t>S 1798-2025</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21580,10 +21580,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>46013</v>
+        <v>45817</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>24</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21639,148 +21639,294 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
+          <t>S 3564-2025</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D277" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E277" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I277" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" t="n">
+        <v>0</v>
+      </c>
+      <c r="L277" t="n">
+        <v>0</v>
+      </c>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+      <c r="N277" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" t="n">
+        <v>0</v>
+      </c>
+      <c r="P277" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>0</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0</v>
+      </c>
+      <c r="S277" t="n">
+        <v>0</v>
+      </c>
+      <c r="T277" t="n">
+        <v>0</v>
+      </c>
+      <c r="U277" t="n">
+        <v>0</v>
+      </c>
+      <c r="V277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278" ht="15" customHeight="1">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>S 3565-2025</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D278" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E278" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I278" t="n">
+        <v>24</v>
+      </c>
+      <c r="J278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" t="n">
+        <v>0</v>
+      </c>
+      <c r="L278" t="n">
+        <v>0</v>
+      </c>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>0</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="n">
+        <v>0</v>
+      </c>
+      <c r="T278" t="n">
+        <v>0</v>
+      </c>
+      <c r="U278" t="n">
+        <v>0</v>
+      </c>
+      <c r="V278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279" ht="15" customHeight="1">
+      <c r="A279" t="inlineStr">
+        <is>
           <t>S 375-2026</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
+      <c r="C279" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D277" s="1" t="n">
+      <c r="D279" s="1" t="n">
         <v>46065</v>
       </c>
-      <c r="E277" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="I277" t="n">
+      <c r="E279" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I279" t="n">
         <v>17.6</v>
       </c>
-      <c r="J277" t="n">
-        <v>0</v>
-      </c>
-      <c r="K277" t="n">
-        <v>0</v>
-      </c>
-      <c r="L277" t="n">
-        <v>0</v>
-      </c>
-      <c r="M277" t="n">
-        <v>0</v>
-      </c>
-      <c r="N277" t="n">
-        <v>0</v>
-      </c>
-      <c r="O277" t="n">
-        <v>0</v>
-      </c>
-      <c r="P277" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
-      <c r="R277" t="n">
-        <v>0</v>
-      </c>
-      <c r="S277" t="n">
-        <v>0</v>
-      </c>
-      <c r="T277" t="n">
-        <v>0</v>
-      </c>
-      <c r="U277" t="n">
-        <v>0</v>
-      </c>
-      <c r="V277" s="2" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
+      <c r="J279" t="n">
+        <v>0</v>
+      </c>
+      <c r="K279" t="n">
+        <v>0</v>
+      </c>
+      <c r="L279" t="n">
+        <v>0</v>
+      </c>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0</v>
+      </c>
+      <c r="P279" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>0</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0</v>
+      </c>
+      <c r="S279" t="n">
+        <v>0</v>
+      </c>
+      <c r="T279" t="n">
+        <v>0</v>
+      </c>
+      <c r="U279" t="n">
+        <v>0</v>
+      </c>
+      <c r="V279" s="2" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
         <is>
           <t>S 1393-2026</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
+      <c r="C280" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D278" s="1" t="n">
+      <c r="D280" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="E278" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="I278" t="n">
+      <c r="E280" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I280" t="n">
         <v>3.4</v>
       </c>
-      <c r="J278" t="n">
-        <v>0</v>
-      </c>
-      <c r="K278" t="n">
-        <v>0</v>
-      </c>
-      <c r="L278" t="n">
-        <v>0</v>
-      </c>
-      <c r="M278" t="n">
-        <v>0</v>
-      </c>
-      <c r="N278" t="n">
-        <v>0</v>
-      </c>
-      <c r="O278" t="n">
-        <v>0</v>
-      </c>
-      <c r="P278" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
-      <c r="R278" t="n">
-        <v>0</v>
-      </c>
-      <c r="S278" t="n">
-        <v>0</v>
-      </c>
-      <c r="T278" t="n">
-        <v>0</v>
-      </c>
-      <c r="U278" t="n">
-        <v>0</v>
-      </c>
-      <c r="V278" s="2" t="inlineStr"/>
+      <c r="J280" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" t="n">
+        <v>0</v>
+      </c>
+      <c r="L280" t="n">
+        <v>0</v>
+      </c>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>0</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" t="n">
+        <v>0</v>
+      </c>
+      <c r="T280" t="n">
+        <v>0</v>
+      </c>
+      <c r="U280" t="n">
+        <v>0</v>
+      </c>
+      <c r="V280" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LESSEBO.xlsx
+++ b/Översikt LESSEBO.xlsx
@@ -601,7 +601,7 @@
         <v>45349</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>46035</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45954</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45954</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45954</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45267</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>46176</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45072</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45670</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52540-2025</t>
+          <t>A 56472-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45954</v>
+        <v>45625</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1727,13 +1727,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1766,260 +1761,265 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 56472-2024 artfynd.xlsx", "A 56472-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 56472-2024 karta.png", "A 56472-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 56472-2024 georefererad karta.tif", "A 56472-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 56472-2024 FSC-klagomål.docx", "A 56472-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 56472-2024 FSC-klagomål mail.docx", "A 56472-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 56472-2024 tillsynsbegäran.docx", "A 56472-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 56472-2024 tillsynsbegäran mail.docx", "A 56472-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 52540-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
         <v>4</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>4</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52540-2025 artfynd.xlsx", "A 52540-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52540-2025 karta.png", "A 52540-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52540-2025 georefererad karta.tif", "A 52540-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52540-2025 FSC-klagomål.docx", "A 52540-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52540-2025 FSC-klagomål mail.docx", "A 52540-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52540-2025 tillsynsbegäran.docx", "A 52540-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52540-2025 tillsynsbegäran mail.docx", "A 52540-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 52539-2025</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>0.7</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>1</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52539-2025 artfynd.xlsx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52539-2025 karta.png", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52539-2025 georefererad karta.tif", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52539-2025 FSC-klagomål.docx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52539-2025 FSC-klagomål mail.docx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52539-2025 tillsynsbegäran.docx", "A 52539-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52539-2025 tillsynsbegäran mail.docx", "A 52539-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 56472-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45625</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 56472-2024 artfynd.xlsx", "A 56472-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 56472-2024 karta.png", "A 56472-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 56472-2024 georefererad karta.tif", "A 56472-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 56472-2024 FSC-klagomål.docx", "A 56472-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 56472-2024 FSC-klagomål mail.docx", "A 56472-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 56472-2024 tillsynsbegäran.docx", "A 56472-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 56472-2024 tillsynsbegäran mail.docx", "A 56472-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44510</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44518</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44865</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 3741-2022</t>
+          <t>A 24680-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44586</v>
+        <v>44727</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2892,13 +2892,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2941,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 24680-2022</t>
+          <t>A 3741-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2955,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44727</v>
+        <v>44586</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2970,8 +2965,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>44510</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 45095-2022</t>
+          <t>A 59408-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44842</v>
+        <v>44491</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3189,13 +3189,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3238,7 +3233,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59408-2021</t>
+          <t>A 45095-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3252,10 +3247,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44491</v>
+        <v>44842</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3267,8 +3262,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>44529</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 27794-2022</t>
+          <t>A 19495-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44743</v>
+        <v>44693</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19495-2022</t>
+          <t>A 63330-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44693</v>
+        <v>44508</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 63330-2021</t>
+          <t>A 66902-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44508</v>
+        <v>44522</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 66902-2021</t>
+          <t>A 27794-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44522</v>
+        <v>44743</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 63927-2021</t>
+          <t>A 27713-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44509</v>
+        <v>44743</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3705,13 +3705,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3754,7 +3749,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 27713-2022</t>
+          <t>A 56456-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3768,10 +3763,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44743</v>
+        <v>45625</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3784,7 +3779,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3827,7 +3822,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3876-2024</t>
+          <t>A 56459-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3841,10 +3836,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45322</v>
+        <v>45625</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3857,7 +3852,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3900,7 +3895,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 4742-2025</t>
+          <t>A 68507-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3914,10 +3909,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45688</v>
+        <v>44529</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3929,13 +3924,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3978,7 +3968,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27080-2022</t>
+          <t>A 24478-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3992,10 +3982,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44741</v>
+        <v>45459</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4008,7 +3998,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4051,7 +4041,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29566-2024</t>
+          <t>A 1367-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4065,10 +4055,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45484</v>
+        <v>44936</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4081,7 +4071,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>21.3</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4124,7 +4114,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8655-2025</t>
+          <t>A 30966-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4138,10 +4128,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45710</v>
+        <v>45113</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4154,7 +4144,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4197,7 +4187,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11843-2024</t>
+          <t>A 33240-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4211,10 +4201,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45376</v>
+        <v>45518</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4226,13 +4216,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>7.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4275,7 +4260,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 41900-2022</t>
+          <t>A 59320-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4289,10 +4274,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44830</v>
+        <v>45637</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4310,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4353,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22432-2023</t>
+          <t>A 8655-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4363,14 +4348,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45070</v>
+        <v>45710</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4382,13 +4367,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4431,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17552-2023</t>
+          <t>A 43453-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4445,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45036</v>
+        <v>45568</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4461,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4504,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 51189-2023</t>
+          <t>A 859-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4514,14 +4494,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45219</v>
+        <v>45665</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4533,8 +4513,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4577,7 +4562,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13751-2025</t>
+          <t>A 45838-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4591,10 +4576,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45737</v>
+        <v>44846</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4607,7 +4592,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4650,7 +4635,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30405-2023</t>
+          <t>A 15203-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4660,14 +4645,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45111</v>
+        <v>45017</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4679,8 +4664,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.3</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4723,7 +4713,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59173-2023</t>
+          <t>A 15204-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4733,14 +4723,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45253</v>
+        <v>45017</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4752,8 +4742,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4796,7 +4791,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 50892-2022</t>
+          <t>A 15180-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4810,10 +4805,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44867</v>
+        <v>45016</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4826,7 +4821,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4869,7 +4864,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45838-2022</t>
+          <t>A 7957-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4883,10 +4878,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44846</v>
+        <v>44973</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4899,7 +4894,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4942,7 +4937,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20824-2023</t>
+          <t>A 17836-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4956,10 +4951,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45058</v>
+        <v>45037</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4972,7 +4967,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5015,7 +5010,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30600-2024</t>
+          <t>A 30914-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5029,10 +5024,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45493</v>
+        <v>44767</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5045,7 +5040,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5088,7 +5083,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24171-2024</t>
+          <t>A 19501-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5102,10 +5097,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45456</v>
+        <v>44693</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5118,7 +5113,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5161,7 +5156,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 24478-2024</t>
+          <t>A 50154-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5175,10 +5170,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45459</v>
+        <v>44865</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5191,7 +5186,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5234,7 +5229,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 39549-2025</t>
+          <t>A 29767-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5248,10 +5243,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45890</v>
+        <v>45107</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5264,7 +5259,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5307,7 +5302,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15864-2022</t>
+          <t>A 41905-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5321,10 +5316,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44664</v>
+        <v>44830</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5336,8 +5331,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5380,7 +5380,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 642-2024</t>
+          <t>A 3955-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5390,14 +5390,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45299</v>
+        <v>44587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5409,13 +5409,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5458,7 +5453,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 53487-2024</t>
+          <t>A 60358-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5472,10 +5467,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45611</v>
+        <v>44910</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5488,7 +5483,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5531,7 +5526,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 64635-2023</t>
+          <t>A 17517-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5545,10 +5540,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45281</v>
+        <v>45036</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5561,7 +5556,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5604,7 +5599,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39750-2025</t>
+          <t>A 20541-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5618,10 +5613,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45891</v>
+        <v>45436</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5634,7 +5629,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5677,7 +5672,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 39884-2025</t>
+          <t>A 20056-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5691,10 +5686,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45891</v>
+        <v>45772</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5707,7 +5702,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5750,7 +5745,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 57519-2022</t>
+          <t>A 64635-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5764,10 +5759,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44896</v>
+        <v>45281</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5780,7 +5775,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5823,7 +5818,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20541-2024</t>
+          <t>A 14584-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5837,10 +5832,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45436</v>
+        <v>45013</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5853,7 +5848,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5896,7 +5891,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10414-2025</t>
+          <t>A 73140-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5910,10 +5905,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45720</v>
+        <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5926,7 +5921,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5969,7 +5964,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35904-2025</t>
+          <t>A 30405-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5983,10 +5978,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45862</v>
+        <v>45111</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5998,13 +5993,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6047,7 +6037,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 47402-2024</t>
+          <t>A 10047-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6061,10 +6051,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45587</v>
+        <v>45364</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6076,8 +6066,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6120,7 +6115,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18968-2024</t>
+          <t>A 36895-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6134,10 +6129,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45427</v>
+        <v>45874</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6150,7 +6145,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6193,7 +6188,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 43809-2025</t>
+          <t>A 38303-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6207,10 +6202,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45912</v>
+        <v>45883</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6223,7 +6218,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6266,7 +6261,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50154-2022</t>
+          <t>A 3239-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6280,10 +6275,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44865</v>
+        <v>45679</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6295,8 +6290,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64865-2023</t>
+          <t>A 52525-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45282</v>
+        <v>45225</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6368,13 +6368,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6417,7 +6412,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 44904-2025</t>
+          <t>A 39884-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6431,10 +6426,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45918</v>
+        <v>45891</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6447,7 +6442,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6490,7 +6485,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34386-2023</t>
+          <t>A 39549-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6504,10 +6499,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45139</v>
+        <v>45890</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6520,7 +6515,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6563,7 +6558,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44899-2025</t>
+          <t>A 39750-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6577,10 +6572,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45918</v>
+        <v>45891</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6593,7 +6588,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6636,7 +6631,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 56529-2022</t>
+          <t>A 51191-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6650,10 +6645,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44893</v>
+        <v>45219</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6666,7 +6661,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>9</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6709,7 +6704,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17350-2023</t>
+          <t>A 56467-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6723,10 +6718,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45035</v>
+        <v>45625</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6739,7 +6734,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6782,7 +6777,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14940-2024</t>
+          <t>A 35904-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6796,10 +6791,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45398</v>
+        <v>45862</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6811,8 +6806,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6855,7 +6855,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 56471-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6865,14 +6865,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45708</v>
+        <v>45625</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6928,7 +6928,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38227-2023</t>
+          <t>A 21917-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45161</v>
+        <v>45784</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7001,7 +7001,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17836-2023</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7011,14 +7011,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45037</v>
+        <v>45708</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7074,7 +7074,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 8173-2025</t>
+          <t>A 3876-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7084,14 +7084,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45708</v>
+        <v>45322</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7147,7 +7147,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3714-2022</t>
+          <t>A 1490-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7157,14 +7157,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44586</v>
+        <v>45670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7178,11 +7178,11 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 65137-2023</t>
+          <t>A 43809-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45288</v>
+        <v>45912</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7298,7 +7298,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33240-2024</t>
+          <t>A 54541-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7308,14 +7308,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45518</v>
+        <v>45233</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7327,8 +7327,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>7.4</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7371,7 +7376,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 48429-2025</t>
+          <t>A 51189-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7385,10 +7390,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45934</v>
+        <v>45219</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7401,7 +7406,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7444,7 +7449,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 48433-2025</t>
+          <t>A 44904-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7458,10 +7463,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45934</v>
+        <v>45918</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7474,7 +7479,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7517,7 +7522,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 39389-2024</t>
+          <t>A 44899-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7531,10 +7536,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45551</v>
+        <v>45918</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7547,7 +7552,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7590,7 +7595,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 43114-2024</t>
+          <t>A 8690-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7604,10 +7609,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45567</v>
+        <v>44978</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7619,13 +7624,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7668,7 +7668,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60358-2022</t>
+          <t>A 57519-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44910</v>
+        <v>44896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 4413-2022</t>
+          <t>A 56475-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44589</v>
+        <v>45625</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7814,7 +7814,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17729-2025</t>
+          <t>A 65137-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7828,10 +7828,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45758</v>
+        <v>45288</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7843,13 +7843,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7892,7 +7887,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 20443-2025</t>
+          <t>A 1894-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7906,10 +7901,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45775</v>
+        <v>45671</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7921,13 +7916,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7970,7 +7960,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 49298-2025</t>
+          <t>A 20855-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7984,10 +7974,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45938</v>
+        <v>45777</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7999,8 +7989,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8043,7 +8038,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 4465-2024</t>
+          <t>A 48429-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8057,10 +8052,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45327</v>
+        <v>45934</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8073,7 +8068,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8116,7 +8111,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 33076-2023</t>
+          <t>A 48433-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8126,14 +8121,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45126</v>
+        <v>45934</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8146,7 +8141,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8189,7 +8184,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 70350-2021</t>
+          <t>A 20824-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8203,10 +8198,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44536</v>
+        <v>45058</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8219,7 +8214,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8262,7 +8257,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1490-2025</t>
+          <t>A 17204-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8272,14 +8267,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45670</v>
+        <v>45756</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8291,13 +8286,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8340,7 +8330,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 61575-2022</t>
+          <t>A 17729-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8354,10 +8344,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44916</v>
+        <v>45758</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8371,11 +8361,11 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8418,7 +8408,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61588-2022</t>
+          <t>A 49298-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8432,10 +8422,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44916</v>
+        <v>45938</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8445,11 +8435,6 @@
       <c r="G100" t="inlineStr">
         <is>
           <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -8496,7 +8481,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 43453-2024</t>
+          <t>A 20443-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8510,10 +8495,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45568</v>
+        <v>45775</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8525,8 +8510,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8569,7 +8559,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 47396-2024</t>
+          <t>A 27191-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8583,10 +8573,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45587</v>
+        <v>44741</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8599,7 +8589,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8642,7 +8632,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 14549-2025</t>
+          <t>A 49121-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8656,10 +8646,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45741</v>
+        <v>45594</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8715,7 +8705,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 27405-2024</t>
+          <t>A 47396-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8729,10 +8719,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45474</v>
+        <v>45587</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8745,7 +8735,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8788,7 +8778,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 7957-2023</t>
+          <t>A 1897-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8802,10 +8792,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44973</v>
+        <v>45671</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8818,7 +8808,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8861,7 +8851,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 13036-2022</t>
+          <t>A 52031-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8875,10 +8865,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44643</v>
+        <v>45952</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8891,7 +8881,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8934,7 +8924,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 52031-2025</t>
+          <t>A 51175-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8948,10 +8938,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45952</v>
+        <v>45219</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8964,7 +8954,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9007,7 +8997,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 3955-2022</t>
+          <t>A 47693-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9021,10 +9011,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44587</v>
+        <v>45931</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9037,7 +9027,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9097,7 +9087,7 @@
         <v>45954</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9158,7 +9148,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56456-2024</t>
+          <t>A 61995-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9172,10 +9162,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45625</v>
+        <v>44918</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9187,8 +9177,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9231,7 +9226,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47386-2024</t>
+          <t>A 52531-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9245,10 +9240,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45587</v>
+        <v>45954</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9260,8 +9255,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9304,7 +9304,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 56459-2024</t>
+          <t>A 52532-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45625</v>
+        <v>45954</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9333,8 +9333,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9377,7 +9382,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 52531-2025</t>
+          <t>A 52546-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9394,7 +9399,7 @@
         <v>45954</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9412,7 +9417,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9455,7 +9460,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 52532-2025</t>
+          <t>A 52534-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9472,7 +9477,7 @@
         <v>45954</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9490,7 +9495,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9533,7 +9538,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 52546-2025</t>
+          <t>A 53122-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9547,10 +9552,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9562,13 +9567,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9611,7 +9611,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 1897-2025</t>
+          <t>A 4107-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9625,10 +9625,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45671</v>
+        <v>45684</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 52534-2025</t>
+          <t>A 35894-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9698,10 +9698,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45954</v>
+        <v>45862</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 53122-2025</t>
+          <t>A 3875-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45958</v>
+        <v>45322</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9835,7 +9835,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20478-2025</t>
+          <t>A 49295-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9849,10 +9849,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45775</v>
+        <v>45938</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9864,13 +9864,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9913,7 +9908,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 20825-2023</t>
+          <t>A 50892-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9927,10 +9922,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45058</v>
+        <v>44867</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9943,7 +9938,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9986,7 +9981,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 37399-2024</t>
+          <t>A 47402-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10000,10 +9995,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45540</v>
+        <v>45587</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10016,7 +10011,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10059,7 +10054,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 51175-2023</t>
+          <t>A 4465-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10073,10 +10068,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45219</v>
+        <v>45327</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10089,7 +10084,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10132,7 +10127,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 49295-2025</t>
+          <t>A 4453-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10146,10 +10141,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45938</v>
+        <v>45327</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10161,8 +10156,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>7.4</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10205,7 +10205,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 20851-2025</t>
+          <t>A 50162-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10215,14 +10215,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45777</v>
+        <v>45215</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10283,7 +10283,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 14584-2023</t>
+          <t>A 21311-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10297,10 +10297,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45013</v>
+        <v>46147</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10356,7 +10356,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 48639-2023</t>
+          <t>A 39389-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10370,10 +10370,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45202</v>
+        <v>45551</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10429,7 +10429,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 29767-2023</t>
+          <t>A 17552-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10443,10 +10443,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45107</v>
+        <v>45036</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10502,7 +10502,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 19501-2022</t>
+          <t>A 22318-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10516,10 +10516,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44693</v>
+        <v>46154</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10575,7 +10575,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 50162-2023</t>
+          <t>A 61638-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10585,14 +10585,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45215</v>
+        <v>46002</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10604,13 +10604,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10653,7 +10648,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 51191-2023</t>
+          <t>A 61641-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10667,10 +10662,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45219</v>
+        <v>46002</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10682,8 +10677,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10726,7 +10726,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 2755-2025</t>
+          <t>A 22423-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10740,10 +10740,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45677</v>
+        <v>46154</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10799,7 +10799,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 52525-2023</t>
+          <t>A 40912-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10813,10 +10813,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45225</v>
+        <v>45173</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10872,7 +10872,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 21745-2022</t>
+          <t>A 22718-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10886,10 +10886,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44708</v>
+        <v>46157</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10901,8 +10901,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>9.699999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10945,7 +10950,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 17517-2023</t>
+          <t>A 22756-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10959,10 +10964,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45036</v>
+        <v>46157</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10974,8 +10979,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11018,7 +11028,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 29659-2025</t>
+          <t>A 22758-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11028,14 +11038,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45825</v>
+        <v>46157</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11047,8 +11057,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11091,7 +11106,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 39603-2022</t>
+          <t>A 22766-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11105,10 +11120,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44818</v>
+        <v>46157</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11120,8 +11135,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11164,7 +11184,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 1367-2023</t>
+          <t>A 22719-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11178,10 +11198,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44936</v>
+        <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11193,8 +11213,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11237,7 +11262,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 27191-2022</t>
+          <t>A 22720-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11251,10 +11276,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44741</v>
+        <v>46157</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11266,8 +11291,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11310,7 +11340,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 20854-2025</t>
+          <t>A 22764-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11324,10 +11354,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45777</v>
+        <v>46157</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11345,7 +11375,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11388,7 +11418,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 20853-2025</t>
+          <t>A 22768-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11402,10 +11432,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45777</v>
+        <v>46157</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11423,7 +11453,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11466,7 +11496,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 17203-2025</t>
+          <t>A 22770-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11480,10 +11510,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45756</v>
+        <v>46157</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11495,8 +11525,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11539,7 +11574,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 4107-2025</t>
+          <t>A 22723-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11553,10 +11588,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45684</v>
+        <v>46157</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11568,8 +11603,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11612,7 +11652,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 40912-2023</t>
+          <t>A 62728-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11626,10 +11666,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45173</v>
+        <v>46008</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11641,8 +11681,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11685,7 +11730,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 30527-2025</t>
+          <t>A 20485-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11699,10 +11744,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45831</v>
+        <v>45775</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11712,6 +11757,11 @@
       <c r="G144" t="inlineStr">
         <is>
           <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I144" t="n">
@@ -11758,7 +11808,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 1022-2026</t>
+          <t>A 18968-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11772,10 +11822,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46030</v>
+        <v>45427</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11788,7 +11838,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11831,7 +11881,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 1016-2026</t>
+          <t>A 53341-2021</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11845,10 +11895,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46030</v>
+        <v>44468</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11861,7 +11911,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11904,7 +11954,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 3239-2025</t>
+          <t>A 20431-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11918,10 +11968,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45679</v>
+        <v>45775</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11935,11 +11985,11 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11982,7 +12032,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 54541-2023</t>
+          <t>A 17203-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11992,14 +12042,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45233</v>
+        <v>45756</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12011,13 +12061,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12060,7 +12105,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 61638-2025</t>
+          <t>A 20435-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12074,10 +12119,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46002</v>
+        <v>45775</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12089,8 +12134,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12133,7 +12183,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 61641-2025</t>
+          <t>A 20681-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12147,10 +12197,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46002</v>
+        <v>45776</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12168,7 +12218,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12211,7 +12261,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 3875-2024</t>
+          <t>A 48639-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12225,10 +12275,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45322</v>
+        <v>45202</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12241,7 +12291,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12284,7 +12334,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 18207-2025</t>
+          <t>A 1022-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12298,10 +12348,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45761</v>
+        <v>46030</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12313,13 +12363,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12362,7 +12407,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 18211-2025</t>
+          <t>A 1016-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12376,10 +12421,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45761</v>
+        <v>46030</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12391,13 +12436,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12440,7 +12480,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 41905-2022</t>
+          <t>A 4236-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12454,10 +12494,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44830</v>
+        <v>46044</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12469,13 +12509,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12518,7 +12553,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 62728-2025</t>
+          <t>A 4229-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12532,10 +12567,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46008</v>
+        <v>46044</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12547,13 +12582,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>2.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12596,7 +12626,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 32712-2025</t>
+          <t>A 24275-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12610,10 +12640,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45839</v>
+        <v>46169</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12625,13 +12655,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12674,7 +12699,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 39436-2022</t>
+          <t>A 24271-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12688,10 +12713,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44818</v>
+        <v>46169</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12704,7 +12729,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12747,7 +12772,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 4229-2026</t>
+          <t>A 24272-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12761,10 +12786,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46044</v>
+        <v>46169</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12777,7 +12802,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>9.699999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12820,7 +12845,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 4236-2026</t>
+          <t>A 24269-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12834,10 +12859,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46044</v>
+        <v>46169</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12850,7 +12875,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12893,7 +12918,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 17204-2025</t>
+          <t>A 27574-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12907,10 +12932,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45756</v>
+        <v>45097</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12923,7 +12948,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12966,7 +12991,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 35332-2022</t>
+          <t>A 4839-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12980,10 +13005,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44798</v>
+        <v>44955</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13039,7 +13064,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 32771-2026</t>
+          <t>A 14549-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13053,10 +13078,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46241</v>
+        <v>45741</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13069,7 +13094,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13112,7 +13137,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 32760-2026</t>
+          <t>A 8438-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13126,10 +13151,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46241</v>
+        <v>46065</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13141,8 +13166,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13185,7 +13215,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 56467-2024</t>
+          <t>A 30600-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13199,10 +13229,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45625</v>
+        <v>45493</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13215,7 +13245,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13258,7 +13288,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 32768-2026</t>
+          <t>A 24171-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13272,10 +13302,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46241</v>
+        <v>45456</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13288,7 +13318,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13331,7 +13361,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 32764-2026</t>
+          <t>A 64865-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13345,10 +13375,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46241</v>
+        <v>45282</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13360,8 +13390,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13404,7 +13439,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 59320-2024</t>
+          <t>A 41900-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13418,10 +13453,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45637</v>
+        <v>44830</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13439,7 +13474,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13482,7 +13517,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 8438-2026</t>
+          <t>A 38227-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13496,10 +13531,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46065</v>
+        <v>45161</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13511,13 +13546,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13560,7 +13590,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 39350-2026</t>
+          <t>A 10189-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13574,10 +13604,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46288</v>
+        <v>46076</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13590,7 +13620,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13633,7 +13663,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 39250-2026</t>
+          <t>A 10286-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13647,10 +13677,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46288</v>
+        <v>46076</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13706,7 +13736,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 10286-2026</t>
+          <t>A 10185-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13723,7 +13753,7 @@
         <v>46076</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13736,7 +13766,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13779,7 +13809,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 10185-2026</t>
+          <t>A 25169-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13793,10 +13823,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46076</v>
+        <v>46175</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13809,7 +13839,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13852,7 +13882,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 10189-2026</t>
+          <t>A 13347-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13866,10 +13896,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46076</v>
+        <v>46094</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13881,8 +13911,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13925,7 +13960,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 70349-2021</t>
+          <t>A 35332-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13939,10 +13974,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44536</v>
+        <v>44798</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13955,7 +13990,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13998,7 +14033,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 13347-2026</t>
+          <t>A 20825-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14012,10 +14047,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46094</v>
+        <v>45058</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14025,11 +14060,6 @@
       <c r="G175" t="inlineStr">
         <is>
           <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I175" t="n">
@@ -14076,7 +14106,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 30914-2022</t>
+          <t>A 13751-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14090,10 +14120,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44767</v>
+        <v>45737</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14106,7 +14136,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14149,7 +14179,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 73140-2021</t>
+          <t>A 20441-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14163,10 +14193,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44550</v>
+        <v>45775</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14178,8 +14208,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14222,7 +14257,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 27574-2023</t>
+          <t>A 59321-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14236,10 +14271,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45097</v>
+        <v>45637</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14251,8 +14286,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14295,7 +14335,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 53341-2021</t>
+          <t>A 14551-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14309,10 +14349,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44468</v>
+        <v>45741</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14325,7 +14365,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14368,7 +14408,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 4839-2023</t>
+          <t>A 27405-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14382,10 +14422,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44955</v>
+        <v>45474</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14398,7 +14438,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14441,7 +14481,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 3605-2024</t>
+          <t>A 59173-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14455,10 +14495,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45320</v>
+        <v>45253</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14471,7 +14511,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14514,7 +14554,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 35909-2025</t>
+          <t>A 3714-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14528,10 +14568,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45862</v>
+        <v>44586</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14545,11 +14585,11 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14592,7 +14632,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 35899-2025</t>
+          <t>A 18207-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14606,10 +14646,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45862</v>
+        <v>45761</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14627,7 +14667,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14670,7 +14710,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 21546-2023</t>
+          <t>A 18211-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14684,10 +14724,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45063</v>
+        <v>45761</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14699,8 +14739,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14743,7 +14788,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 18464-2026</t>
+          <t>A 27870-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14757,10 +14802,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46127</v>
+        <v>46191</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14772,13 +14817,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>14.2</v>
+        <v>0.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14821,7 +14861,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 18466-2026</t>
+          <t>A 27873-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14835,10 +14875,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46127</v>
+        <v>46191</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14850,13 +14890,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>7.9</v>
+        <v>1.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14899,7 +14934,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 18625-2026</t>
+          <t>A 642-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14909,14 +14944,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46127</v>
+        <v>45299</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14928,8 +14963,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14972,7 +15012,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 15180-2023</t>
+          <t>A 18625-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14986,10 +15026,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45016</v>
+        <v>46127</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15002,7 +15042,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15045,7 +15085,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 21917-2025</t>
+          <t>A 20480-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15059,10 +15099,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45784</v>
+        <v>45775</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15074,8 +15114,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15118,7 +15163,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 20855-2025</t>
+          <t>A 18464-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15132,10 +15177,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45777</v>
+        <v>46127</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15153,7 +15198,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.7</v>
+        <v>14.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15196,7 +15241,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 859-2025</t>
+          <t>A 18466-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15206,14 +15251,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45665</v>
+        <v>46127</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15231,7 +15276,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.5</v>
+        <v>7.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15274,7 +15319,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 52031-2023</t>
+          <t>A 33076-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15284,14 +15329,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45223</v>
+        <v>45126</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15304,7 +15349,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15347,7 +15392,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 1894-2025</t>
+          <t>A 47386-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15361,10 +15406,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45671</v>
+        <v>45587</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15377,7 +15422,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15420,7 +15465,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 47693-2025</t>
+          <t>A 63927-2021</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15434,10 +15479,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45931</v>
+        <v>44509</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15449,8 +15494,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15493,7 +15543,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 20056-2025</t>
+          <t>A 39603-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15507,10 +15557,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45772</v>
+        <v>44818</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15523,7 +15573,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15566,7 +15616,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 10047-2024</t>
+          <t>A 30822-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15580,10 +15630,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45364</v>
+        <v>46205</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15595,13 +15645,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15644,7 +15689,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 30826-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15654,14 +15699,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45708</v>
+        <v>46205</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15674,7 +15719,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15717,7 +15762,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 30966-2023</t>
+          <t>A 11843-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15731,10 +15776,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45113</v>
+        <v>45376</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15746,8 +15791,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15790,7 +15840,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 68507-2021</t>
+          <t>A 14940-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15804,10 +15854,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44529</v>
+        <v>45398</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15820,7 +15870,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15863,7 +15913,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 38712-2022</t>
+          <t>A 4413-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15877,10 +15927,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44814</v>
+        <v>44589</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15893,7 +15943,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15936,7 +15986,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 43206-2024</t>
+          <t>A 3605-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15950,10 +16000,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45567</v>
+        <v>45320</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15966,7 +16016,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16009,7 +16059,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 15203-2023</t>
+          <t>A 34386-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16019,14 +16069,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45017</v>
+        <v>45139</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16038,13 +16088,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16087,7 +16132,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 15204-2023</t>
+          <t>A 21546-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16097,14 +16142,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45017</v>
+        <v>45063</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16116,13 +16161,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16165,7 +16205,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 36895-2025</t>
+          <t>A 15864-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16179,10 +16219,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45874</v>
+        <v>44664</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16195,7 +16235,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16238,7 +16278,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 8690-2023</t>
+          <t>A 34855-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16252,10 +16292,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44978</v>
+        <v>46255</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16267,8 +16307,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16311,7 +16356,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 61995-2022</t>
+          <t>A 34894-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16325,10 +16370,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44918</v>
+        <v>46259</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16340,13 +16385,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16389,7 +16429,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 4453-2024</t>
+          <t>A 38712-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16403,10 +16443,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45327</v>
+        <v>44814</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16418,13 +16458,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16467,7 +16502,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 56471-2024</t>
+          <t>A 34984-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16481,10 +16516,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45625</v>
+        <v>46258</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16497,7 +16532,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16540,7 +16575,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 38303-2025</t>
+          <t>A 34820-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16554,10 +16589,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45883</v>
+        <v>46255</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16569,8 +16604,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16613,7 +16653,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 49121-2024</t>
+          <t>A 34661-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16627,10 +16667,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45594</v>
+        <v>46257</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16643,7 +16683,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16686,7 +16726,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 35894-2025</t>
+          <t>A 34806-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16700,10 +16740,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45862</v>
+        <v>46255</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16717,11 +16757,11 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16764,7 +16804,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 56475-2024</t>
+          <t>A 22432-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16774,14 +16814,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45625</v>
+        <v>45070</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16793,8 +16833,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16837,7 +16882,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 21311-2026</t>
+          <t>A 56529-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16851,10 +16896,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46147</v>
+        <v>44893</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16867,7 +16912,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16910,7 +16955,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 51990-2024</t>
+          <t>A 31252-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16924,10 +16969,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45607</v>
+        <v>46218</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16939,8 +16984,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16983,7 +17033,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 41598-2024</t>
+          <t>A 43114-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16997,10 +17047,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45560</v>
+        <v>45567</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17012,8 +17062,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17056,7 +17111,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 20852-2025</t>
+          <t>A 35568-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17070,10 +17125,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45777</v>
+        <v>46262</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17091,7 +17146,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17134,7 +17189,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 61439-2024</t>
+          <t>A 35570-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17148,10 +17203,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45646</v>
+        <v>46262</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17163,8 +17218,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17207,7 +17267,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 22318-2026</t>
+          <t>A 21745-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17221,10 +17281,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46154</v>
+        <v>44708</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17237,7 +17297,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17280,7 +17340,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 21951-2025</t>
+          <t>A 37399-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17290,14 +17350,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45784</v>
+        <v>45540</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17309,13 +17369,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17358,7 +17413,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 22423-2026</t>
+          <t>A 36067-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17368,14 +17423,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46154</v>
+        <v>46267</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17387,8 +17442,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17431,7 +17491,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 37964-2024</t>
+          <t>A 36313-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17441,14 +17501,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45544</v>
+        <v>46268</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17461,7 +17521,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17504,7 +17564,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 22764-2026</t>
+          <t>A 27080-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17518,10 +17578,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46157</v>
+        <v>44741</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17533,13 +17593,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17582,7 +17637,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 22768-2026</t>
+          <t>A 43206-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17596,10 +17651,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46157</v>
+        <v>45567</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17611,13 +17666,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17660,7 +17710,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 22770-2026</t>
+          <t>A 39436-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17674,10 +17724,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46157</v>
+        <v>44818</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17689,13 +17739,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17738,7 +17783,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 20431-2025</t>
+          <t>A 37786-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17752,10 +17797,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45775</v>
+        <v>46279</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17767,13 +17812,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17816,7 +17856,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 22723-2026</t>
+          <t>A 13036-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17830,10 +17870,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46157</v>
+        <v>44643</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17845,13 +17885,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17894,7 +17929,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 20681-2025</t>
+          <t>A 52031-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17908,10 +17943,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45776</v>
+        <v>45223</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17923,13 +17958,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17972,7 +18002,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 22718-2026</t>
+          <t>A 70349-2021</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17986,10 +18016,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46157</v>
+        <v>44536</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18001,13 +18031,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18050,7 +18075,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 22766-2026</t>
+          <t>A 70350-2021</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18064,10 +18089,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46157</v>
+        <v>44536</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18079,13 +18104,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18128,7 +18148,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 22756-2026</t>
+          <t>A 2755-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18138,14 +18158,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46157</v>
+        <v>45677</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18157,13 +18177,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>8.699999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18206,7 +18221,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 22758-2026</t>
+          <t>A 61575-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18220,10 +18235,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46157</v>
+        <v>44916</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18237,11 +18252,11 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18284,7 +18299,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 20435-2025</t>
+          <t>A 61588-2022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18298,10 +18313,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45775</v>
+        <v>44916</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18315,11 +18330,11 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18362,7 +18377,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 20485-2025</t>
+          <t>A 38098-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18376,10 +18391,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45775</v>
+        <v>46281</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18391,13 +18406,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18440,7 +18450,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 22719-2026</t>
+          <t>A 17350-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18454,10 +18464,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46157</v>
+        <v>45035</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18469,13 +18479,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18518,7 +18523,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 22720-2026</t>
+          <t>A 20852-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18532,10 +18537,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46157</v>
+        <v>45777</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18553,7 +18558,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18596,7 +18601,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 24275-2026</t>
+          <t>A 51990-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18610,10 +18615,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46169</v>
+        <v>45607</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18626,7 +18631,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18669,7 +18674,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 24271-2026</t>
+          <t>A 41598-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18683,10 +18688,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46169</v>
+        <v>45560</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18699,7 +18704,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18742,7 +18747,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 24272-2026</t>
+          <t>A 61439-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18756,10 +18761,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46169</v>
+        <v>45646</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18772,7 +18777,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18815,7 +18820,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 24269-2026</t>
+          <t>A 21951-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18825,14 +18830,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46169</v>
+        <v>45784</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18844,8 +18849,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I239" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18888,7 +18898,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 25169-2026</t>
+          <t>A 37964-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18898,14 +18908,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46175</v>
+        <v>45544</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18918,7 +18928,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18961,7 +18971,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 59321-2024</t>
+          <t>A 4742-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18975,10 +18985,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45637</v>
+        <v>45688</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18992,11 +19002,11 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19039,7 +19049,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 20441-2025</t>
+          <t>A 29566-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19053,10 +19063,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45775</v>
+        <v>45484</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19068,13 +19078,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I242" t="n">
-        <v>2</v>
+        <v>21.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19117,7 +19122,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 14551-2025</t>
+          <t>A 32764-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19131,10 +19136,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45741</v>
+        <v>46241</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19147,7 +19152,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19190,7 +19195,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 27870-2026</t>
+          <t>A 32768-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19204,10 +19209,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46191</v>
+        <v>46241</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19220,7 +19225,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19263,7 +19268,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 27873-2026</t>
+          <t>A 32771-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19277,10 +19282,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46191</v>
+        <v>46241</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19293,7 +19298,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19336,7 +19341,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 20480-2025</t>
+          <t>A 32760-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19350,10 +19355,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45775</v>
+        <v>46241</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19365,13 +19370,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I246" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19414,7 +19414,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 30826-2026</t>
+          <t>A 10414-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19428,10 +19428,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46205</v>
+        <v>45720</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19487,7 +19487,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 30822-2026</t>
+          <t>A 39350-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19501,10 +19501,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46205</v>
+        <v>46288</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19560,7 +19560,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 34661-2026</t>
+          <t>A 53487-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19574,10 +19574,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46257</v>
+        <v>45611</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19633,7 +19633,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 34806-2026</t>
+          <t>A 39250-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19647,10 +19647,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46255</v>
+        <v>46288</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19662,13 +19662,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I250" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19711,7 +19706,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 34820-2026</t>
+          <t>A 8173-2025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19721,14 +19716,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46255</v>
+        <v>45708</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19740,13 +19735,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I251" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19789,7 +19779,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 34855-2026</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19799,14 +19789,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46255</v>
+        <v>45708</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19818,13 +19808,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I252" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19867,7 +19852,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 34894-2026</t>
+          <t>A 20478-2025</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19881,10 +19866,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>46259</v>
+        <v>45775</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19896,8 +19881,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I253" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19940,7 +19930,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 34984-2026</t>
+          <t>A 29659-2025</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19950,14 +19940,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46258</v>
+        <v>45825</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19970,7 +19960,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20013,7 +20003,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 35570-2026</t>
+          <t>A 20851-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20027,10 +20017,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46262</v>
+        <v>45777</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20048,7 +20038,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20091,7 +20081,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 31252-2026</t>
+          <t>A 20854-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20105,10 +20095,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46218</v>
+        <v>45777</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20122,11 +20112,11 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I256" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20169,7 +20159,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 35568-2026</t>
+          <t>A 20853-2025</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20183,10 +20173,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46262</v>
+        <v>45777</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20204,7 +20194,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>6.9</v>
+        <v>2.4</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20247,7 +20237,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 36067-2026</t>
+          <t>A 30527-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20261,10 +20251,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>46267</v>
+        <v>45831</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20276,13 +20266,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I258" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20325,7 +20310,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 36313-2026</t>
+          <t>A 32712-2025</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20339,10 +20324,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46268</v>
+        <v>45839</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20354,8 +20339,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I259" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20398,7 +20388,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 37786-2026</t>
+          <t>A 35909-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20412,10 +20402,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>46279</v>
+        <v>45862</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20427,8 +20417,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I260" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20471,7 +20466,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 38098-2026</t>
+          <t>A 35899-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20485,10 +20480,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46281</v>
+        <v>45862</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20500,8 +20495,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I261" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20544,7 +20544,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>S 2061-2022</t>
+          <t>S 2321-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20558,10 +20558,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>44672</v>
+        <v>45105</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20617,7 +20617,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>S 2321-2023</t>
+          <t>S 4661-2022</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20627,14 +20627,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45105</v>
+        <v>44795</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>0.7</v>
+        <v>43.6</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20690,7 +20690,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>S 4661-2022</t>
+          <t>S 396-2023</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20704,10 +20704,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>44795</v>
+        <v>44959</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>43.6</v>
+        <v>78.8</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20763,7 +20763,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>S 396-2023</t>
+          <t>S 2061-2022</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20773,14 +20773,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>44959</v>
+        <v>44672</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>78.8</v>
+        <v>1.6</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
         <v>45056</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44959</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>44893</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>44893</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45072</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45193</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>45386</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>44795</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45688</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45817</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45817</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46013</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>46013</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>46065</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>46154</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>

--- a/Översikt LESSEBO.xlsx
+++ b/Översikt LESSEBO.xlsx
@@ -601,7 +601,7 @@
         <v>45349</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>46035</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45954</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45954</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45954</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45267</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>46176</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45072</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1488-2025</t>
+          <t>A 52540-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1603,14 +1603,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45670</v>
+        <v>45954</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1622,14 +1622,19 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1656,370 +1661,365 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52540-2025 artfynd.xlsx", "A 52540-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52540-2025 karta.png", "A 52540-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52540-2025 georefererad karta.tif", "A 52540-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52540-2025 FSC-klagomål.docx", "A 52540-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52540-2025 FSC-klagomål mail.docx", "A 52540-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52540-2025 tillsynsbegäran.docx", "A 52540-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52540-2025 tillsynsbegäran mail.docx", "A 52540-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 52539-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52539-2025 artfynd.xlsx", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52539-2025 karta.png", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52539-2025 georefererad karta.tif", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52539-2025 FSC-klagomål.docx", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52539-2025 FSC-klagomål mail.docx", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52539-2025 tillsynsbegäran.docx", "A 52539-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52539-2025 tillsynsbegäran mail.docx", "A 52539-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 1488-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45670</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Korallrot</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 1488-2025 artfynd.xlsx", "A 1488-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 1488-2025 karta.png", "A 1488-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 1488-2025 georefererad karta.tif", "A 1488-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 1488-2025 FSC-klagomål.docx", "A 1488-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 1488-2025 FSC-klagomål mail.docx", "A 1488-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 1488-2025 tillsynsbegäran.docx", "A 1488-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 1488-2025 tillsynsbegäran mail.docx", "A 1488-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 56472-2024</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>45625</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>5</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U14" t="n">
         <v>1</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Fläcknycklar</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 56472-2024 artfynd.xlsx", "A 56472-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 56472-2024 karta.png", "A 56472-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 56472-2024 georefererad karta.tif", "A 56472-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 56472-2024 FSC-klagomål.docx", "A 56472-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 56472-2024 FSC-klagomål mail.docx", "A 56472-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 56472-2024 tillsynsbegäran.docx", "A 56472-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 56472-2024 tillsynsbegäran mail.docx", "A 56472-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 52540-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45954</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52540-2025 artfynd.xlsx", "A 52540-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52540-2025 karta.png", "A 52540-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52540-2025 georefererad karta.tif", "A 52540-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52540-2025 FSC-klagomål.docx", "A 52540-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52540-2025 FSC-klagomål mail.docx", "A 52540-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52540-2025 tillsynsbegäran.docx", "A 52540-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52540-2025 tillsynsbegäran mail.docx", "A 52540-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 52539-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45954</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/artfynd/A 52539-2025 artfynd.xlsx", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor/A 52539-2025 karta.png", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/kartor_geotiff/A 52539-2025 georefererad karta.tif", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomål/A 52539-2025 FSC-klagomål.docx", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/klagomålsmail/A 52539-2025 FSC-klagomål mail.docx", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsyn/A 52539-2025 tillsynsbegäran.docx", "A 52539-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0761/tillsynsmail/A 52539-2025 tillsynsbegäran mail.docx", "A 52539-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44510</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44518</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44865</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24680-2022</t>
+          <t>A 3741-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44727</v>
+        <v>44586</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2892,8 +2892,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2936,7 +2941,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3741-2022</t>
+          <t>A 24680-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2950,10 +2955,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44586</v>
+        <v>44727</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2965,13 +2970,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>44510</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44491</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44842</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44529</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44693</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44508</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44522</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44743</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 27713-2022</t>
+          <t>A 3876-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44743</v>
+        <v>45322</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 56456-2024</t>
+          <t>A 27080-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45625</v>
+        <v>44741</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56459-2024</t>
+          <t>A 27713-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45625</v>
+        <v>44743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 68507-2021</t>
+          <t>A 11843-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44529</v>
+        <v>45376</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3924,8 +3924,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3968,7 +3973,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24478-2024</t>
+          <t>A 51189-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3982,10 +3987,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45459</v>
+        <v>45219</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3998,7 +4003,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4041,7 +4046,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 1367-2023</t>
+          <t>A 59173-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4055,10 +4060,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44936</v>
+        <v>45253</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4071,7 +4076,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4114,7 +4119,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30966-2023</t>
+          <t>A 24171-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4128,10 +4133,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45113</v>
+        <v>45456</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4144,7 +4149,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4187,7 +4192,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33240-2024</t>
+          <t>A 24478-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4201,10 +4206,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45518</v>
+        <v>45459</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4217,7 +4222,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.4</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4260,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59320-2024</t>
+          <t>A 64635-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45637</v>
+        <v>45281</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4289,13 +4294,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8655-2025</t>
+          <t>A 57519-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45710</v>
+        <v>44896</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>6.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43453-2024</t>
+          <t>A 20541-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45568</v>
+        <v>45436</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 859-2025</t>
+          <t>A 1022-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4494,14 +4494,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45665</v>
+        <v>46030</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4513,13 +4513,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4562,7 +4557,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45838-2022</t>
+          <t>A 1016-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4576,10 +4571,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44846</v>
+        <v>46030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4592,7 +4587,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4635,7 +4630,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15203-2023</t>
+          <t>A 18968-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4645,14 +4640,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45017</v>
+        <v>45427</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4664,13 +4659,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4713,7 +4703,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15204-2023</t>
+          <t>A 53487-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4723,14 +4713,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45017</v>
+        <v>45611</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4742,13 +4732,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4791,7 +4776,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15180-2023</t>
+          <t>A 39549-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4805,10 +4790,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45016</v>
+        <v>45890</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4821,7 +4806,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>7.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4864,7 +4849,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7957-2023</t>
+          <t>A 10414-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4878,10 +4863,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44973</v>
+        <v>45720</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4894,7 +4879,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4937,7 +4922,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 17836-2023</t>
+          <t>A 39750-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4951,10 +4936,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45037</v>
+        <v>45891</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4967,7 +4952,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5010,7 +4995,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30914-2022</t>
+          <t>A 39884-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5024,10 +5009,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44767</v>
+        <v>45891</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5040,7 +5025,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5083,7 +5068,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19501-2022</t>
+          <t>A 56529-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5097,10 +5082,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44693</v>
+        <v>44893</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5113,7 +5098,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5156,7 +5141,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 50154-2022</t>
+          <t>A 38227-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5170,10 +5155,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44865</v>
+        <v>45161</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5186,7 +5171,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5229,7 +5214,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29767-2023</t>
+          <t>A 4229-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5243,10 +5228,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45107</v>
+        <v>46044</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5259,7 +5244,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5302,7 +5287,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 41905-2022</t>
+          <t>A 35904-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5316,10 +5301,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44830</v>
+        <v>45862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5337,7 +5322,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5380,7 +5365,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3955-2022</t>
+          <t>A 4236-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5394,10 +5379,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44587</v>
+        <v>46044</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5410,7 +5395,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5453,7 +5438,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 60358-2022</t>
+          <t>A 3714-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5467,10 +5452,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44910</v>
+        <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5482,8 +5467,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5526,7 +5516,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17517-2023</t>
+          <t>A 43809-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5540,10 +5530,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45036</v>
+        <v>45912</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5556,7 +5546,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5599,7 +5589,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20541-2024</t>
+          <t>A 33240-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5613,10 +5603,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45436</v>
+        <v>45518</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5629,7 +5619,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>7.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5672,7 +5662,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20056-2025</t>
+          <t>A 44904-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5686,10 +5676,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45772</v>
+        <v>45918</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5702,7 +5692,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5745,7 +5735,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64635-2023</t>
+          <t>A 39389-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5759,10 +5749,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45281</v>
+        <v>45551</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5775,7 +5765,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5818,7 +5808,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14584-2023</t>
+          <t>A 44899-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5832,10 +5822,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45013</v>
+        <v>45918</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5848,7 +5838,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5891,7 +5881,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 73140-2021</t>
+          <t>A 60358-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5905,10 +5895,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44550</v>
+        <v>44910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5921,7 +5911,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5964,7 +5954,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30405-2023</t>
+          <t>A 8438-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5978,10 +5968,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45111</v>
+        <v>46065</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5993,8 +5983,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6037,7 +6032,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10047-2024</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6047,14 +6042,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45364</v>
+        <v>45708</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6066,13 +6061,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6115,7 +6105,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36895-2025</t>
+          <t>A 8173-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6125,14 +6115,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45874</v>
+        <v>45708</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6145,7 +6135,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6188,7 +6178,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38303-2025</t>
+          <t>A 10286-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6202,10 +6192,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45883</v>
+        <v>46076</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6218,7 +6208,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6261,7 +6251,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 3239-2025</t>
+          <t>A 10185-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6275,10 +6265,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45679</v>
+        <v>46076</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6290,13 +6280,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6339,7 +6324,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52525-2023</t>
+          <t>A 10189-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6353,10 +6338,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45225</v>
+        <v>46076</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6369,7 +6354,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6412,7 +6397,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39884-2025</t>
+          <t>A 61575-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6426,10 +6411,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45891</v>
+        <v>44916</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6441,8 +6426,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6485,7 +6475,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39549-2025</t>
+          <t>A 61588-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6499,10 +6489,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45890</v>
+        <v>44916</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6514,8 +6504,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6558,7 +6553,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39750-2025</t>
+          <t>A 43453-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6572,10 +6567,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45891</v>
+        <v>45568</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6588,7 +6583,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6631,7 +6626,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 51191-2023</t>
+          <t>A 47396-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6645,10 +6640,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45219</v>
+        <v>45587</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6661,7 +6656,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6704,7 +6699,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56467-2024</t>
+          <t>A 48429-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6718,10 +6713,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45625</v>
+        <v>45934</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6734,7 +6729,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6777,7 +6772,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35904-2025</t>
+          <t>A 48433-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6791,10 +6786,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45862</v>
+        <v>45934</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6806,13 +6801,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6855,7 +6845,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56471-2024</t>
+          <t>A 7957-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6869,10 +6859,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45625</v>
+        <v>44973</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6885,7 +6875,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6928,7 +6918,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21917-2025</t>
+          <t>A 17729-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6942,10 +6932,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45784</v>
+        <v>45758</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6955,6 +6945,11 @@
       <c r="G80" t="inlineStr">
         <is>
           <t>LESSEBO</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -7001,7 +6996,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 20443-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7011,14 +7006,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45708</v>
+        <v>45775</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7030,8 +7025,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7074,7 +7074,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3876-2024</t>
+          <t>A 49298-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7088,10 +7088,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45322</v>
+        <v>45938</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7147,7 +7147,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 1490-2025</t>
+          <t>A 47386-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7157,14 +7157,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45670</v>
+        <v>45587</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7176,13 +7176,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7225,7 +7220,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 43809-2025</t>
+          <t>A 13347-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7239,10 +7234,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45912</v>
+        <v>46094</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7254,8 +7249,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7298,7 +7298,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 54541-2023</t>
+          <t>A 37399-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7308,14 +7308,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45233</v>
+        <v>45540</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7327,13 +7327,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7376,7 +7371,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 51189-2023</t>
+          <t>A 51175-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7393,7 +7388,7 @@
         <v>45219</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7406,7 +7401,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7449,7 +7444,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44904-2025</t>
+          <t>A 52031-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7463,10 +7458,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45918</v>
+        <v>45952</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7522,7 +7517,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44899-2025</t>
+          <t>A 52537-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7536,10 +7531,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45918</v>
+        <v>45954</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7551,8 +7546,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7595,7 +7595,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 8690-2023</t>
+          <t>A 52531-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7609,10 +7609,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44978</v>
+        <v>45954</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7624,8 +7624,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7668,7 +7673,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 57519-2022</t>
+          <t>A 52532-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7682,10 +7687,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44896</v>
+        <v>45954</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7697,8 +7702,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7741,7 +7751,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 56475-2024</t>
+          <t>A 52546-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7755,10 +7765,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45625</v>
+        <v>45954</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7770,8 +7780,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7814,7 +7829,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 65137-2023</t>
+          <t>A 52534-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7828,10 +7843,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45288</v>
+        <v>45954</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7843,8 +7858,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7887,7 +7907,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 1894-2025</t>
+          <t>A 53122-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7901,10 +7921,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45671</v>
+        <v>45958</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7917,7 +7937,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7960,7 +7980,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 20855-2025</t>
+          <t>A 14584-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7974,10 +7994,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45777</v>
+        <v>45013</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7989,13 +8009,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8038,7 +8053,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48429-2025</t>
+          <t>A 29767-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8052,10 +8067,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45934</v>
+        <v>45107</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8068,7 +8083,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8111,7 +8126,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48433-2025</t>
+          <t>A 18464-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8125,10 +8140,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45934</v>
+        <v>46127</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8140,8 +8155,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>14.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8184,7 +8204,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 20824-2023</t>
+          <t>A 18466-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8198,10 +8218,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45058</v>
+        <v>46127</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8213,8 +8233,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>7.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8257,7 +8282,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 17204-2025</t>
+          <t>A 19501-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8271,10 +8296,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45756</v>
+        <v>44693</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8287,7 +8312,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8330,7 +8355,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 17729-2025</t>
+          <t>A 18625-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8344,10 +8369,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45758</v>
+        <v>46127</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8359,13 +8384,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8408,7 +8428,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 49298-2025</t>
+          <t>A 49295-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8425,7 +8445,7 @@
         <v>45938</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8438,7 +8458,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8481,7 +8501,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20443-2025</t>
+          <t>A 51191-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8495,10 +8515,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45775</v>
+        <v>45219</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8510,13 +8530,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8559,7 +8574,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 27191-2022</t>
+          <t>A 52525-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8573,10 +8588,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44741</v>
+        <v>45225</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8589,7 +8604,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8632,7 +8647,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 49121-2024</t>
+          <t>A 17517-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8646,10 +8661,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45594</v>
+        <v>45036</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8662,7 +8677,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8705,7 +8720,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 47396-2024</t>
+          <t>A 1367-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8719,10 +8734,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45587</v>
+        <v>44936</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8735,7 +8750,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8778,7 +8793,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 1897-2025</t>
+          <t>A 21917-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8792,10 +8807,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45671</v>
+        <v>45784</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8808,7 +8823,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8851,7 +8866,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52031-2025</t>
+          <t>A 4107-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8865,10 +8880,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45952</v>
+        <v>45684</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8881,7 +8896,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8924,7 +8939,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 51175-2023</t>
+          <t>A 20855-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8938,10 +8953,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45219</v>
+        <v>45777</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8953,8 +8968,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8997,7 +9017,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 47693-2025</t>
+          <t>A 1894-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9011,10 +9031,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45931</v>
+        <v>45671</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9027,7 +9047,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9070,7 +9090,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 52537-2025</t>
+          <t>A 47693-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9084,10 +9104,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45954</v>
+        <v>45931</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9099,13 +9119,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9148,7 +9163,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61995-2022</t>
+          <t>A 20056-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9162,10 +9177,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44918</v>
+        <v>45772</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9177,13 +9192,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9226,7 +9236,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 52531-2025</t>
+          <t>A 61638-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9240,10 +9250,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45954</v>
+        <v>46002</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9255,13 +9265,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>6.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9304,7 +9309,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 52532-2025</t>
+          <t>A 61641-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9318,10 +9323,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45954</v>
+        <v>46002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9339,7 +9344,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9382,7 +9387,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 52546-2025</t>
+          <t>A 20478-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9396,10 +9401,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45954</v>
+        <v>45775</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9417,7 +9422,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9460,7 +9465,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 52534-2025</t>
+          <t>A 63927-2021</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9474,10 +9479,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45954</v>
+        <v>44509</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9495,7 +9500,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9538,7 +9543,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 53122-2025</t>
+          <t>A 62728-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9552,10 +9557,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45958</v>
+        <v>46008</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9567,8 +9572,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9611,7 +9621,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 4107-2025</t>
+          <t>A 36895-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9625,10 +9635,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45684</v>
+        <v>45874</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9641,7 +9651,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9684,7 +9694,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 35894-2025</t>
+          <t>A 8655-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9698,10 +9708,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45862</v>
+        <v>45710</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9713,13 +9723,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9762,7 +9767,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 3875-2024</t>
+          <t>A 20851-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9776,10 +9781,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45322</v>
+        <v>45777</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9791,8 +9796,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9835,7 +9845,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 49295-2025</t>
+          <t>A 56471-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9849,10 +9859,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45938</v>
+        <v>45625</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9865,7 +9875,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9908,7 +9918,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 50892-2022</t>
+          <t>A 38303-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9922,10 +9932,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44867</v>
+        <v>45883</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9938,7 +9948,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9981,7 +9991,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 47402-2024</t>
+          <t>A 41900-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9995,10 +10005,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45587</v>
+        <v>44830</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10010,8 +10020,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10054,7 +10069,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4465-2024</t>
+          <t>A 22432-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10064,14 +10079,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45327</v>
+        <v>45070</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10083,8 +10098,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10127,7 +10147,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 4453-2024</t>
+          <t>A 29659-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10137,14 +10157,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45327</v>
+        <v>45825</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10156,13 +10176,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10205,7 +10220,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 50162-2023</t>
+          <t>A 20854-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10215,14 +10230,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45215</v>
+        <v>45777</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10240,7 +10255,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10283,7 +10298,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21311-2026</t>
+          <t>A 20853-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10297,10 +10312,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46147</v>
+        <v>45777</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10312,8 +10327,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10356,7 +10376,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 39389-2024</t>
+          <t>A 17552-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10370,10 +10390,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45551</v>
+        <v>45036</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10386,7 +10406,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10429,7 +10449,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 17552-2023</t>
+          <t>A 35894-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10443,10 +10463,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45036</v>
+        <v>45862</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10458,8 +10478,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10502,7 +10527,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 22318-2026</t>
+          <t>A 13751-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10516,10 +10541,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46154</v>
+        <v>45737</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10532,7 +10557,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10575,7 +10600,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61638-2025</t>
+          <t>A 30405-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10589,10 +10614,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46002</v>
+        <v>45111</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10605,7 +10630,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10648,7 +10673,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61641-2025</t>
+          <t>A 21311-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10662,10 +10687,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46002</v>
+        <v>46147</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10675,11 +10700,6 @@
       <c r="G130" t="inlineStr">
         <is>
           <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -10726,7 +10746,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 22423-2026</t>
+          <t>A 30527-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10736,14 +10756,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46154</v>
+        <v>45831</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10756,7 +10776,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10799,7 +10819,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 40912-2023</t>
+          <t>A 22318-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10813,10 +10833,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45173</v>
+        <v>46154</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10829,7 +10849,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10872,7 +10892,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 22718-2026</t>
+          <t>A 50892-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10886,10 +10906,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46157</v>
+        <v>44867</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10901,13 +10921,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10950,7 +10965,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 22756-2026</t>
+          <t>A 45838-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10964,10 +10979,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46157</v>
+        <v>44846</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10979,13 +10994,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>8.699999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11028,7 +11038,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 22758-2026</t>
+          <t>A 22423-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11038,14 +11048,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11057,13 +11067,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11106,7 +11111,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 22766-2026</t>
+          <t>A 20824-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11120,10 +11125,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46157</v>
+        <v>45058</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11135,13 +11140,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11184,7 +11184,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 22719-2026</t>
+          <t>A 22764-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11201,7 +11201,7 @@
         <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11262,7 +11262,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 22720-2026</t>
+          <t>A 22768-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11279,7 +11279,7 @@
         <v>46157</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 22764-2026</t>
+          <t>A 22770-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11357,7 +11357,7 @@
         <v>46157</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 22768-2026</t>
+          <t>A 30600-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11432,10 +11432,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46157</v>
+        <v>45493</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11447,13 +11447,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11496,7 +11491,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 22770-2026</t>
+          <t>A 20431-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11510,10 +11505,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46157</v>
+        <v>45775</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11531,7 +11526,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11591,7 +11586,7 @@
         <v>46157</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11652,7 +11647,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 62728-2025</t>
+          <t>A 20681-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11666,10 +11661,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46008</v>
+        <v>45776</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11687,7 +11682,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11730,7 +11725,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 20485-2025</t>
+          <t>A 22718-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11744,10 +11739,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45775</v>
+        <v>46157</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11765,7 +11760,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11808,7 +11803,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 18968-2024</t>
+          <t>A 22766-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11822,10 +11817,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45427</v>
+        <v>46157</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11837,8 +11832,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11881,7 +11881,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 53341-2021</t>
+          <t>A 22756-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11895,10 +11895,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44468</v>
+        <v>46157</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11910,8 +11910,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11954,7 +11959,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 20431-2025</t>
+          <t>A 22758-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11968,10 +11973,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45775</v>
+        <v>46157</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11989,7 +11994,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12032,7 +12037,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 17203-2025</t>
+          <t>A 20435-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12046,10 +12051,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45756</v>
+        <v>45775</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12061,8 +12066,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12105,7 +12115,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 20435-2025</t>
+          <t>A 20485-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12122,7 +12132,7 @@
         <v>45775</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12140,7 +12150,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12183,7 +12193,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 20681-2025</t>
+          <t>A 22719-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12197,10 +12207,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45776</v>
+        <v>46157</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12218,7 +12228,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12261,7 +12271,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 48639-2023</t>
+          <t>A 22720-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12275,10 +12285,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45202</v>
+        <v>46157</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12290,8 +12300,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12334,7 +12349,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 1022-2026</t>
+          <t>A 15864-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12348,10 +12363,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46030</v>
+        <v>44664</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12364,7 +12379,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12407,7 +12422,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 1016-2026</t>
+          <t>A 32712-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12421,10 +12436,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46030</v>
+        <v>45839</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12436,8 +12451,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12480,7 +12500,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 4236-2026</t>
+          <t>A 642-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12490,14 +12510,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46044</v>
+        <v>45299</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12509,8 +12529,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12553,7 +12578,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 4229-2026</t>
+          <t>A 47402-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12567,10 +12592,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46044</v>
+        <v>45587</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12583,7 +12608,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>9.699999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12643,7 +12668,7 @@
         <v>46169</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12716,7 +12741,7 @@
         <v>46169</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12789,7 +12814,7 @@
         <v>46169</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12862,7 +12887,7 @@
         <v>46169</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12918,7 +12943,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 27574-2023</t>
+          <t>A 35909-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12932,10 +12957,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45097</v>
+        <v>45862</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12947,8 +12972,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12991,7 +13021,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 4839-2023</t>
+          <t>A 35899-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13005,10 +13035,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44955</v>
+        <v>45862</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13020,8 +13050,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13064,7 +13099,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 14549-2025</t>
+          <t>A 25169-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13078,10 +13113,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45741</v>
+        <v>46175</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13094,7 +13129,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13137,7 +13172,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 8438-2026</t>
+          <t>A 50154-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13151,10 +13186,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46065</v>
+        <v>44865</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13166,13 +13201,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13215,7 +13245,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 30600-2024</t>
+          <t>A 64865-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13229,10 +13259,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45493</v>
+        <v>45282</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13244,8 +13274,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13288,7 +13323,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 24171-2024</t>
+          <t>A 34386-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13302,10 +13337,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45456</v>
+        <v>45139</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13318,7 +13353,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13361,7 +13396,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 64865-2023</t>
+          <t>A 17350-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13375,10 +13410,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45282</v>
+        <v>45035</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13390,13 +13425,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13439,7 +13469,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 41900-2022</t>
+          <t>A 14940-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13453,10 +13483,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44830</v>
+        <v>45398</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13468,13 +13498,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13517,7 +13542,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 38227-2023</t>
+          <t>A 17836-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13531,10 +13556,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45161</v>
+        <v>45037</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13590,7 +13615,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 10189-2026</t>
+          <t>A 65137-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13604,10 +13629,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46076</v>
+        <v>45288</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13620,7 +13645,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13663,7 +13688,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 10286-2026</t>
+          <t>A 59321-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13677,10 +13702,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46076</v>
+        <v>45637</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13692,8 +13717,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13736,7 +13766,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 10185-2026</t>
+          <t>A 20441-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13750,10 +13780,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46076</v>
+        <v>45775</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13765,8 +13795,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13809,7 +13844,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 25169-2026</t>
+          <t>A 14551-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13823,10 +13858,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46175</v>
+        <v>45741</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13839,7 +13874,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13882,7 +13917,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 13347-2026</t>
+          <t>A 43114-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13896,10 +13931,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46094</v>
+        <v>45567</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13913,11 +13948,11 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13960,7 +13995,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 35332-2022</t>
+          <t>A 4413-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13974,10 +14009,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44798</v>
+        <v>44589</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13990,7 +14025,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14033,7 +14068,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 20825-2023</t>
+          <t>A 27870-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14047,10 +14082,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45058</v>
+        <v>46191</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14063,7 +14098,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14106,7 +14141,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 13751-2025</t>
+          <t>A 27873-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14120,10 +14155,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45737</v>
+        <v>46191</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14136,7 +14171,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14179,7 +14214,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 20441-2025</t>
+          <t>A 20480-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14196,7 +14231,7 @@
         <v>45775</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14214,7 +14249,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14257,7 +14292,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 59321-2024</t>
+          <t>A 4465-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14271,10 +14306,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45637</v>
+        <v>45327</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14286,13 +14321,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14335,7 +14365,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 14551-2025</t>
+          <t>A 33076-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14345,14 +14375,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45741</v>
+        <v>45126</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14365,7 +14395,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14408,7 +14438,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 27405-2024</t>
+          <t>A 70350-2021</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14422,10 +14452,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45474</v>
+        <v>44536</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14438,7 +14468,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14481,7 +14511,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 59173-2023</t>
+          <t>A 1490-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14491,14 +14521,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45253</v>
+        <v>45670</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14510,8 +14540,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14554,7 +14589,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 3714-2022</t>
+          <t>A 14549-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14568,10 +14603,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44586</v>
+        <v>45741</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14583,13 +14618,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14632,7 +14662,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 18207-2025</t>
+          <t>A 27405-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14646,10 +14676,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45761</v>
+        <v>45474</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14661,13 +14691,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14710,7 +14735,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 18211-2025</t>
+          <t>A 13036-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14724,10 +14749,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45761</v>
+        <v>44643</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14739,13 +14764,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14788,7 +14808,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 27870-2026</t>
+          <t>A 10047-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14802,10 +14822,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46191</v>
+        <v>45364</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14817,8 +14837,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14861,7 +14886,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 27873-2026</t>
+          <t>A 3955-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14875,10 +14900,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46191</v>
+        <v>44587</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14891,7 +14916,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14934,7 +14959,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 642-2024</t>
+          <t>A 30826-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14944,14 +14969,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45299</v>
+        <v>46205</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14963,13 +14988,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15012,7 +15032,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 18625-2026</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15022,14 +15042,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46127</v>
+        <v>45708</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15042,7 +15062,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15085,7 +15105,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 20480-2025</t>
+          <t>A 30822-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15099,10 +15119,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45775</v>
+        <v>46205</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15114,13 +15134,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15163,7 +15178,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 18464-2026</t>
+          <t>A 56456-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15177,10 +15192,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46127</v>
+        <v>45625</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15192,13 +15207,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>14.2</v>
+        <v>1.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15241,7 +15251,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 18466-2026</t>
+          <t>A 56459-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15255,10 +15265,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46127</v>
+        <v>45625</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15270,13 +15280,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>7.9</v>
+        <v>2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15319,7 +15324,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 33076-2023</t>
+          <t>A 1897-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15329,14 +15334,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45126</v>
+        <v>45671</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15349,7 +15354,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15392,7 +15397,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 47386-2024</t>
+          <t>A 20825-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15406,10 +15411,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45587</v>
+        <v>45058</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15422,7 +15427,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15465,7 +15470,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 63927-2021</t>
+          <t>A 34661-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15479,10 +15484,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44509</v>
+        <v>46257</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15494,13 +15499,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15543,7 +15543,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 39603-2022</t>
+          <t>A 34806-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15557,10 +15557,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44818</v>
+        <v>46255</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15572,8 +15572,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15616,7 +15621,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 30822-2026</t>
+          <t>A 34820-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15630,10 +15635,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46205</v>
+        <v>46255</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15645,8 +15650,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15689,7 +15699,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 30826-2026</t>
+          <t>A 34855-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15703,10 +15713,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46205</v>
+        <v>46255</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15718,8 +15728,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15762,7 +15777,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 11843-2024</t>
+          <t>A 48639-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15776,10 +15791,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45376</v>
+        <v>45202</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15791,13 +15806,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15840,7 +15850,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 14940-2024</t>
+          <t>A 34894-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15854,10 +15864,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45398</v>
+        <v>46259</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15870,7 +15880,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15913,7 +15923,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 4413-2022</t>
+          <t>A 50162-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15923,14 +15933,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44589</v>
+        <v>45215</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15942,8 +15952,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15986,7 +16001,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 3605-2024</t>
+          <t>A 34984-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16000,10 +16015,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45320</v>
+        <v>46258</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16016,7 +16031,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16059,7 +16074,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 34386-2023</t>
+          <t>A 35570-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16073,10 +16088,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45139</v>
+        <v>46262</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16088,8 +16103,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16132,7 +16152,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 21546-2023</t>
+          <t>A 2755-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16142,14 +16162,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45063</v>
+        <v>45677</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16162,7 +16182,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16205,7 +16225,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 15864-2022</t>
+          <t>A 31252-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16219,10 +16239,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44664</v>
+        <v>46218</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16234,8 +16254,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16278,7 +16303,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 34855-2026</t>
+          <t>A 21745-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16292,10 +16317,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46255</v>
+        <v>44708</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16307,13 +16332,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16356,7 +16376,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 34894-2026</t>
+          <t>A 35568-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16370,10 +16390,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16385,8 +16405,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>2.4</v>
+        <v>6.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16429,7 +16454,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 38712-2022</t>
+          <t>A 39603-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16443,10 +16468,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44814</v>
+        <v>44818</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16459,7 +16484,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16502,7 +16527,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 34984-2026</t>
+          <t>A 27191-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16516,10 +16541,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46258</v>
+        <v>44741</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16532,7 +16557,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16575,7 +16600,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 34820-2026</t>
+          <t>A 17203-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16589,10 +16614,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46255</v>
+        <v>45756</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16604,13 +16629,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16653,7 +16673,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 34661-2026</t>
+          <t>A 40912-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16667,10 +16687,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46257</v>
+        <v>45173</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16683,7 +16703,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16726,7 +16746,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 34806-2026</t>
+          <t>A 3239-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16740,10 +16760,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46255</v>
+        <v>45679</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16757,11 +16777,11 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16804,7 +16824,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 22432-2023</t>
+          <t>A 54541-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16818,10 +16838,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45070</v>
+        <v>45233</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16835,11 +16855,11 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16882,7 +16902,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 56529-2022</t>
+          <t>A 3875-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16896,10 +16916,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44893</v>
+        <v>45322</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16912,7 +16932,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16955,7 +16975,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 31252-2026</t>
+          <t>A 36067-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16969,10 +16989,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46218</v>
+        <v>46267</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16986,11 +17006,11 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17033,7 +17053,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 43114-2024</t>
+          <t>A 36313-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17047,10 +17067,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45567</v>
+        <v>46268</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17062,13 +17082,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17111,7 +17126,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 35568-2026</t>
+          <t>A 18207-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17125,10 +17140,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46262</v>
+        <v>45761</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17146,7 +17161,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>6.9</v>
+        <v>1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17189,7 +17204,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 35570-2026</t>
+          <t>A 18211-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17203,10 +17218,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46262</v>
+        <v>45761</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17224,7 +17239,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17267,7 +17282,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 21745-2022</t>
+          <t>A 41905-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17281,10 +17296,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44708</v>
+        <v>44830</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17296,8 +17311,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>9.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17340,7 +17360,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 37399-2024</t>
+          <t>A 39436-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17354,10 +17374,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45540</v>
+        <v>44818</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17370,7 +17390,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17413,7 +17433,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 36067-2026</t>
+          <t>A 17204-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17427,10 +17447,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46267</v>
+        <v>45756</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17442,13 +17462,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17491,7 +17506,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 36313-2026</t>
+          <t>A 35332-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17505,10 +17520,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46268</v>
+        <v>44798</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17521,7 +17536,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17564,7 +17579,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 27080-2022</t>
+          <t>A 37786-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17578,10 +17593,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44741</v>
+        <v>46279</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17594,7 +17609,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17637,7 +17652,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 43206-2024</t>
+          <t>A 56467-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17651,10 +17666,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45567</v>
+        <v>45625</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17667,7 +17682,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17710,7 +17725,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 39436-2022</t>
+          <t>A 38098-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17724,10 +17739,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44818</v>
+        <v>46281</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17740,7 +17755,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17783,7 +17798,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 37786-2026</t>
+          <t>A 59320-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17797,10 +17812,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46279</v>
+        <v>45637</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17812,8 +17827,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17856,7 +17876,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 13036-2022</t>
+          <t>A 32771-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17870,10 +17890,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44643</v>
+        <v>46241</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17929,7 +17949,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 52031-2023</t>
+          <t>A 32760-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17943,10 +17963,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45223</v>
+        <v>46241</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17959,7 +17979,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18002,7 +18022,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 70349-2021</t>
+          <t>A 32768-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18016,10 +18036,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44536</v>
+        <v>46241</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18032,7 +18052,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18075,7 +18095,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 70350-2021</t>
+          <t>A 32764-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18089,10 +18109,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44536</v>
+        <v>46241</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18105,7 +18125,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18148,7 +18168,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 2755-2025</t>
+          <t>A 70349-2021</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18158,14 +18178,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45677</v>
+        <v>44536</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18178,7 +18198,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18221,7 +18241,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 61575-2022</t>
+          <t>A 39350-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18235,10 +18255,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44916</v>
+        <v>46288</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18250,13 +18270,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18299,7 +18314,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 61588-2022</t>
+          <t>A 39250-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18313,10 +18328,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44916</v>
+        <v>46288</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18328,13 +18343,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18377,7 +18387,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 38098-2026</t>
+          <t>A 30914-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18391,10 +18401,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46281</v>
+        <v>44767</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18407,7 +18417,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18450,7 +18460,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 17350-2023</t>
+          <t>A 73140-2021</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18464,10 +18474,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45035</v>
+        <v>44550</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18480,7 +18490,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18523,7 +18533,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 20852-2025</t>
+          <t>A 27574-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18537,10 +18547,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45777</v>
+        <v>45097</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18550,11 +18560,6 @@
       <c r="G235" t="inlineStr">
         <is>
           <t>LESSEBO</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I235" t="n">
@@ -18601,7 +18606,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 51990-2024</t>
+          <t>A 53341-2021</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18615,10 +18620,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45607</v>
+        <v>44468</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18631,7 +18636,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18674,7 +18679,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 41598-2024</t>
+          <t>A 4839-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18688,10 +18693,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45560</v>
+        <v>44955</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18704,7 +18709,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18747,7 +18752,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 61439-2024</t>
+          <t>A 3605-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18761,10 +18766,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45646</v>
+        <v>45320</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18777,7 +18782,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18820,7 +18825,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 21951-2025</t>
+          <t>A 21546-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18830,14 +18835,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45784</v>
+        <v>45063</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18849,13 +18854,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I239" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18898,7 +18898,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 37964-2024</t>
+          <t>A 15180-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18908,14 +18908,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45544</v>
+        <v>45016</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18971,7 +18971,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 4742-2025</t>
+          <t>A 859-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18981,14 +18981,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45688</v>
+        <v>45665</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19002,11 +19002,11 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I241" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19049,7 +19049,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 29566-2024</t>
+          <t>A 52031-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19063,10 +19063,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45484</v>
+        <v>45223</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>21.3</v>
+        <v>0.6</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19122,7 +19122,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 32764-2026</t>
+          <t>A 30966-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19136,10 +19136,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46241</v>
+        <v>45113</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19195,7 +19195,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 32768-2026</t>
+          <t>A 68507-2021</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19209,10 +19209,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46241</v>
+        <v>44529</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19268,7 +19268,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 32771-2026</t>
+          <t>A 38712-2022</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19282,10 +19282,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46241</v>
+        <v>44814</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19341,7 +19341,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 32760-2026</t>
+          <t>A 43206-2024</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19355,10 +19355,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46241</v>
+        <v>45567</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19414,7 +19414,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 10414-2025</t>
+          <t>A 15203-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19424,14 +19424,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45720</v>
+        <v>45017</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19443,8 +19443,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I247" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19487,7 +19492,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 39350-2026</t>
+          <t>A 15204-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19497,14 +19502,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46288</v>
+        <v>45017</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19516,8 +19521,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I248" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19560,7 +19570,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 53487-2024</t>
+          <t>A 8690-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19574,10 +19584,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45611</v>
+        <v>44978</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19590,7 +19600,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19633,7 +19643,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 39250-2026</t>
+          <t>A 61995-2022</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19647,10 +19657,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46288</v>
+        <v>44918</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19662,8 +19672,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I250" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19706,7 +19721,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 8173-2025</t>
+          <t>A 4453-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19716,14 +19731,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45708</v>
+        <v>45327</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19735,8 +19750,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I251" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19779,7 +19799,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 49121-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19789,14 +19809,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45708</v>
+        <v>45594</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19809,7 +19829,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19852,7 +19872,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 20478-2025</t>
+          <t>A 56475-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19866,10 +19886,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45775</v>
+        <v>45625</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19881,13 +19901,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I253" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19930,7 +19945,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 29659-2025</t>
+          <t>A 51990-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19940,14 +19955,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45825</v>
+        <v>45607</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19960,7 +19975,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20003,7 +20018,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 20851-2025</t>
+          <t>A 41598-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20017,10 +20032,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45777</v>
+        <v>45560</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20032,13 +20047,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I255" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20081,7 +20091,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 20854-2025</t>
+          <t>A 20852-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20098,7 +20108,7 @@
         <v>45777</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20159,7 +20169,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 20853-2025</t>
+          <t>A 61439-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20173,10 +20183,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45777</v>
+        <v>45646</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20188,13 +20198,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I257" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20237,7 +20242,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 30527-2025</t>
+          <t>A 21951-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20247,14 +20252,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45831</v>
+        <v>45784</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20266,8 +20271,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I258" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20310,7 +20320,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 32712-2025</t>
+          <t>A 37964-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20320,14 +20330,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45839</v>
+        <v>45544</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20339,13 +20349,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I259" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20388,7 +20393,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 35909-2025</t>
+          <t>A 4742-2025</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20402,10 +20407,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45862</v>
+        <v>45688</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20419,11 +20424,11 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I260" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20466,7 +20471,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 35899-2025</t>
+          <t>A 29566-2024</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20480,10 +20485,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45862</v>
+        <v>45484</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20495,13 +20500,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I261" t="n">
-        <v>1.4</v>
+        <v>21.3</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20544,7 +20544,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>S 2321-2023</t>
+          <t>S 2061-2022</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20558,10 +20558,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45105</v>
+        <v>44672</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20617,7 +20617,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>S 4661-2022</t>
+          <t>S 2321-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20627,14 +20627,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>44795</v>
+        <v>45105</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>43.6</v>
+        <v>0.7</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20690,7 +20690,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>S 396-2023</t>
+          <t>S 4661-2022</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20704,10 +20704,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>44959</v>
+        <v>44795</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>78.8</v>
+        <v>43.6</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20763,7 +20763,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>S 2061-2022</t>
+          <t>S 396-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20773,14 +20773,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>44672</v>
+        <v>44959</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1.6</v>
+        <v>78.8</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
         <v>45056</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44959</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>44893</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>44893</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45072</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45193</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>45386</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>44795</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45688</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45817</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45817</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46013</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>46013</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>46065</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>46154</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>

--- a/Översikt LESSEBO.xlsx
+++ b/Översikt LESSEBO.xlsx
@@ -601,7 +601,7 @@
         <v>45349</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>46035</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45954</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45954</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45954</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45267</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>46176</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45072</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45954</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>45954</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>45670</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45625</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44510</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44518</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44865</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>44586</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44727</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44510</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44491</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44842</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44529</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44693</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44508</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44522</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44743</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45322</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44741</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45376</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45219</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45253</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45456</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45459</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45281</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44896</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45436</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46030</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45427</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45611</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45890</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45720</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45891</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45891</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44893</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>45161</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46044</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>46044</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45912</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>45518</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>45918</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45551</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45918</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>46065</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>45708</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>45708</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>46076</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>46076</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>46076</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44916</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44916</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>45568</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>45587</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>45934</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>45934</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>44973</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>45758</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45775</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45938</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>45587</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>46094</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>45540</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>45219</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>45952</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>45954</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45954</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45954</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>45954</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>45954</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>45958</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45013</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45107</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>46127</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>46127</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44693</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>46127</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>45938</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45219</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>45225</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>45036</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>44936</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>45784</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45684</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>45777</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>45671</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45931</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>45772</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>46002</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>46002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>45775</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>44509</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>46008</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>45874</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>45710</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>45777</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45625</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45883</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>44830</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>45070</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45825</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45777</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45777</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>45036</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>45862</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>45737</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>45111</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>46147</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>45831</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>46154</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>44867</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>44846</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>46154</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>45058</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>46157</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>46157</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>45493</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>45775</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>46157</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45776</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>46157</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>46157</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>46157</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>46157</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>45775</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>45775</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>46157</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>46157</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>44664</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45839</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>45299</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>45587</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>46169</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>46169</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>46169</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>46169</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45862</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>45862</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>46175</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44865</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45282</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45139</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45035</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45398</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45037</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45288</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>45637</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45775</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>45741</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>45567</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44589</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>46191</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>46191</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45775</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45327</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45126</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44536</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45670</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45741</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>45474</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>44643</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45364</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>44587</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>46205</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45708</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>46205</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45625</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45625</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>45671</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>45058</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>46257</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>46255</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>46255</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>46255</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45202</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>46259</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45215</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>46258</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>46262</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>45677</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>46218</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44708</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>46262</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>44818</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>44741</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45756</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45173</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45679</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45233</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45322</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>46267</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>46268</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45761</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>45761</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>44830</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>44818</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>45756</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>44798</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>46279</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>45625</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>46281</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>45637</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>46241</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>46241</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>46241</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>46241</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>44536</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>46288</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>46288</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>44767</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>44550</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>45097</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>44468</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>44955</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>45320</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>45063</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45016</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>45665</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45223</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45113</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>44529</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>44814</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45567</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45017</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45017</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>44978</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>44918</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45327</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45594</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45625</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45607</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>45560</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>45777</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45646</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45784</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45544</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45688</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>45484</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>44672</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45105</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>44795</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44959</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45056</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44959</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>44893</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>44893</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45072</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45193</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>45386</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>44795</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45688</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45817</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45817</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46013</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>46013</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>46065</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>46154</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>

--- a/Översikt LESSEBO.xlsx
+++ b/Översikt LESSEBO.xlsx
@@ -601,7 +601,7 @@
         <v>45349</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>46035</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45954</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45954</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45954</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45267</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>46176</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45072</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45954</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>45954</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>45670</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45625</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44510</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44518</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44865</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>44586</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44727</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>44510</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44491</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44842</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44529</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44693</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44508</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44522</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44743</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45322</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44741</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44743</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45376</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45219</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>45253</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45456</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45459</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45281</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44896</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45436</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46030</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>46030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45427</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45611</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>45890</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45720</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45891</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45891</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44893</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
         <v>45161</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>46044</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>45862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>46044</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45912</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>45518</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>45918</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45551</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45918</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>46065</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>45708</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>45708</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>46076</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>46076</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>46076</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44916</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44916</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>45568</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>45587</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>45934</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>45934</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>44973</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>45758</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45775</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45938</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>45587</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>46094</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>45540</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>45219</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>45952</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>45954</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45954</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45954</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>45954</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>45954</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>45958</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45013</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45107</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>46127</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>46127</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44693</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>46127</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>45938</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45219</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>45225</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>45036</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>44936</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>45784</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45684</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>45777</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>45671</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45931</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>45772</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>46002</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>46002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>45775</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>44509</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>46008</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>45874</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>45710</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>45777</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45625</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45883</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>44830</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>45070</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45825</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45777</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45777</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>45036</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>45862</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>45737</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>45111</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>46147</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>45831</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>46154</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>44867</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>44846</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>46154</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>45058</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>46157</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>46157</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>45493</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>45775</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>46157</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45776</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>46157</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>46157</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>46157</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>46157</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>45775</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>45775</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>46157</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>46157</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>44664</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45839</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>45299</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>45587</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>46169</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>46169</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>46169</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>46169</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45862</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>45862</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>46175</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44865</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45282</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45139</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45035</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45398</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45037</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45288</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>45637</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45775</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>45741</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>45567</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44589</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>46191</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>46191</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45775</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45327</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45126</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44536</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>45670</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45741</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>45474</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>44643</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45364</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>44587</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>46205</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45708</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>46205</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45625</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45625</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>45671</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>45058</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>46257</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>46255</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>46255</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>46255</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45202</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>46259</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45215</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>46258</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>46262</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>45677</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>46218</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44708</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>46262</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>44818</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>44741</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45756</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45173</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45679</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45233</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45322</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>46267</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>46268</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45761</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>45761</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>44830</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>44818</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>45756</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>44798</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>46279</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>45625</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>46281</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>45637</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>46241</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>46241</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>46241</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>46241</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>44536</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>46288</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>46288</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>44767</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>44550</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>45097</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>44468</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>44955</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>45320</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>45063</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45016</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>45665</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45223</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45113</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>44529</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>44814</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45567</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45017</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45017</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>44978</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>44918</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45327</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45594</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45625</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45607</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>45560</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>45777</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45646</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45784</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45544</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45688</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>45484</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>44672</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45105</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>44795</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44959</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45056</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44959</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>44893</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>44893</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45072</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45193</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>45386</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>44795</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45688</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45817</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45817</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46013</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>46013</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>46065</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>46154</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>

--- a/Översikt LESSEBO.xlsx
+++ b/Översikt LESSEBO.xlsx
@@ -601,7 +601,7 @@
         <v>45349</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>46035</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>45954</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>45954</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45954</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45267</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>46176</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45072</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>45954</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>45954</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>45670</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45625</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>46211</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>44840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44510</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>44518</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44865</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 3741-2022</t>
+          <t>A 24680-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44586</v>
+        <v>44727</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2892,13 +2892,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2941,7 +2936,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 24680-2022</t>
+          <t>A 3741-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2955,10 +2950,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44727</v>
+        <v>44586</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2970,8 +2965,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>44510</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>44588</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59408-2021</t>
+          <t>A 45095-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44491</v>
+        <v>44842</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3189,8 +3189,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3233,7 +3238,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45095-2022</t>
+          <t>A 59408-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3247,10 +3252,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44842</v>
+        <v>44491</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3262,13 +3267,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>44529</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44693</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44508</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>44522</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44743</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3876-2024</t>
+          <t>A 33240-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45322</v>
+        <v>45518</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>7.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 27080-2022</t>
+          <t>A 27713-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44741</v>
+        <v>44743</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27713-2022</t>
+          <t>A 56456-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44743</v>
+        <v>45625</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11843-2024</t>
+          <t>A 56459-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45376</v>
+        <v>45625</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3924,13 +3924,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3973,7 +3968,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51189-2023</t>
+          <t>A 24478-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3987,10 +3982,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45219</v>
+        <v>45459</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4003,7 +3998,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4046,7 +4041,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59173-2023</t>
+          <t>A 1367-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4060,10 +4055,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45253</v>
+        <v>44936</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4076,7 +4071,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4119,7 +4114,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24171-2024</t>
+          <t>A 30966-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4133,10 +4128,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45456</v>
+        <v>45113</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4149,7 +4144,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4192,7 +4187,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 24478-2024</t>
+          <t>A 59320-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45459</v>
+        <v>45637</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4221,8 +4216,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 64635-2023</t>
+          <t>A 68507-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45281</v>
+        <v>44529</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57519-2022</t>
+          <t>A 29566-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44896</v>
+        <v>45484</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.6</v>
+        <v>21.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 20541-2024</t>
+          <t>A 61638-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45436</v>
+        <v>46002</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>6.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1022-2026</t>
+          <t>A 61641-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46030</v>
+        <v>46002</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4513,8 +4513,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4557,7 +4562,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1016-2026</t>
+          <t>A 15203-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4567,14 +4572,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46030</v>
+        <v>45017</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4586,8 +4591,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4630,7 +4640,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18968-2024</t>
+          <t>A 15204-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4640,14 +4650,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45427</v>
+        <v>45017</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4659,8 +4669,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4703,7 +4718,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 53487-2024</t>
+          <t>A 8655-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4717,10 +4732,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45611</v>
+        <v>45710</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4733,7 +4748,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4776,7 +4791,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 39549-2025</t>
+          <t>A 10047-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4790,10 +4805,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45890</v>
+        <v>45364</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4805,8 +4820,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4849,7 +4869,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10414-2025</t>
+          <t>A 62728-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4863,10 +4883,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45720</v>
+        <v>46008</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4878,8 +4898,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4922,7 +4947,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 39750-2025</t>
+          <t>A 10414-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4936,10 +4961,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45891</v>
+        <v>45720</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4952,7 +4977,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4995,7 +5020,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39884-2025</t>
+          <t>A 43453-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5009,10 +5034,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45891</v>
+        <v>45568</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5025,7 +5050,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5068,7 +5093,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 56529-2022</t>
+          <t>A 39884-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5082,10 +5107,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44893</v>
+        <v>45891</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5098,7 +5123,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>9</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5141,7 +5166,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38227-2023</t>
+          <t>A 39549-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5155,10 +5180,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45161</v>
+        <v>45890</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5171,7 +5196,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>7.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5214,7 +5239,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 4229-2026</t>
+          <t>A 39750-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5228,10 +5253,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46044</v>
+        <v>45891</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5244,7 +5269,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>9.699999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5287,7 +5312,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35904-2025</t>
+          <t>A 53487-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5301,10 +5326,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45862</v>
+        <v>45611</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5316,13 +5341,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5365,7 +5385,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4236-2026</t>
+          <t>A 8173-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5375,14 +5395,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46044</v>
+        <v>45708</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5395,7 +5415,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5438,7 +5458,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3714-2022</t>
+          <t>A 859-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5448,14 +5468,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44586</v>
+        <v>45665</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5469,11 +5489,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5516,7 +5536,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 43809-2025</t>
+          <t>A 8174-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5526,14 +5546,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45912</v>
+        <v>45708</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5546,7 +5566,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5589,7 +5609,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33240-2024</t>
+          <t>A 35904-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5603,10 +5623,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45518</v>
+        <v>45862</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5618,8 +5638,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5662,7 +5687,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44904-2025</t>
+          <t>A 45838-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5676,10 +5701,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45918</v>
+        <v>44846</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5692,7 +5717,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5735,7 +5760,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39389-2024</t>
+          <t>A 15180-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5749,10 +5774,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45551</v>
+        <v>45016</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5765,7 +5790,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5808,7 +5833,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44899-2025</t>
+          <t>A 43809-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5822,10 +5847,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45918</v>
+        <v>45912</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5838,7 +5863,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5881,7 +5906,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60358-2022</t>
+          <t>A 20478-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5895,10 +5920,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44910</v>
+        <v>45775</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5910,8 +5935,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5954,7 +5984,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8438-2026</t>
+          <t>A 44904-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5968,10 +5998,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46065</v>
+        <v>45918</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5983,13 +6013,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6032,7 +6057,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8174-2025</t>
+          <t>A 44899-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6042,14 +6067,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45708</v>
+        <v>45918</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6062,7 +6087,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6105,7 +6130,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8173-2025</t>
+          <t>A 29659-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6115,14 +6140,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45708</v>
+        <v>45825</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6135,7 +6160,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6178,7 +6203,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 10286-2026</t>
+          <t>A 20851-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6192,10 +6217,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46076</v>
+        <v>45777</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6207,8 +6232,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6251,7 +6281,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 10185-2026</t>
+          <t>A 20854-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6265,10 +6295,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46076</v>
+        <v>45777</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6280,8 +6310,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6324,7 +6359,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10189-2026</t>
+          <t>A 20853-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6338,10 +6373,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46076</v>
+        <v>45777</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6353,8 +6388,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6397,7 +6437,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61575-2022</t>
+          <t>A 30527-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6411,10 +6451,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44916</v>
+        <v>45831</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6426,13 +6466,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6475,7 +6510,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61588-2022</t>
+          <t>A 7957-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6489,10 +6524,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44916</v>
+        <v>44973</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6504,13 +6539,8 @@
           <t>LESSEBO</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6553,7 +6583,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 43453-2024</t>
+          <t>A 32712-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6567,10 +6597,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45568</v>
+        <v>45839</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6582,8 +6612,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6626,7 +6661,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 47396-2024</t>
+          <t>A 48429-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6640,10 +6675,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45587</v>
+        <v>45934</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6656,7 +6691,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6699,7 +6734,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48429-2025</t>
+          <t>A 48433-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6716,7 +6751,7 @@
         <v>45934</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6729,7 +6764,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6772,7 +6807,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48433-2025</t>
+          <t>A 17729-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6786,10 +6821,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45934</v>
+        <v>45758</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6801,8 +6836,13 @@
           <t>LESSEBO</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6845,7 +6885,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7957-2023</t>
+          <t>A 49298-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6859,10 +6899,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44973</v>
+        <v>45938</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6875,7 +6915,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6918,7 +6958,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 17729-2025</t>
+          <t>A 20443-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6932,10 +6972,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45758</v>
+        <v>45775</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6953,7 +6993,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6996,7 +7036,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
 